--- a/reiting.xlsx
+++ b/reiting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0816871E-D483-444F-BC93-4A3565ACD88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BB3E1D-35F0-4A01-8264-49268F8260F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4125" yWindow="225" windowWidth="16365" windowHeight="10695" activeTab="3" xr2:uid="{65B562F7-4CCD-46A4-AA6C-D53DA83FA9FC}"/>
+    <workbookView xWindow="4125" yWindow="225" windowWidth="16365" windowHeight="10695" activeTab="1" xr2:uid="{65B562F7-4CCD-46A4-AA6C-D53DA83FA9FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Predmet" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="153">
   <si>
     <t>Школа</t>
   </si>
@@ -190,9 +190,6 @@
   </si>
   <si>
     <t>Жас Дарын</t>
-  </si>
-  <si>
-    <t>Внеклассная работа (1-5 балл)</t>
   </si>
   <si>
     <t>Организация отдыха учеников</t>
@@ -905,22 +902,6 @@
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -943,10 +924,26 @@
       <alignment horizontal="left" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1364,43 +1361,43 @@
       <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39" t="s">
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39" t="s">
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39" t="s">
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39" t="s">
+      <c r="U3" s="45"/>
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
     </row>
     <row r="4" spans="1:32" s="2" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
@@ -2440,7 +2437,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE53200-8515-411C-B25E-E6DF6273D5A7}">
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -2454,172 +2451,319 @@
     <col min="29" max="29" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="1" spans="1:30" s="2" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="V1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="W1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="X1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD1" s="3"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E2" s="11">
+        <v>1</v>
+      </c>
+      <c r="F2" s="11">
+        <v>2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>3</v>
+      </c>
+      <c r="H2" s="11">
+        <v>5</v>
+      </c>
+      <c r="I2" s="11">
+        <v>5</v>
+      </c>
+      <c r="J2" s="12">
+        <f>SUM(E2+F2+G2+H2+I2)</f>
+        <v>16</v>
+      </c>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="13">
+        <f>SUM(K2+L2+M2+N2+O2+P2+Q2)</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="14">
+        <f>SUM(S2+T2+U2+V2+W2+X2)</f>
+        <v>0</v>
+      </c>
+      <c r="Z2" s="12">
+        <f t="shared" ref="Z2:Z14" si="0">SUM(J2)</f>
+        <v>16</v>
+      </c>
+      <c r="AA2" s="13">
+        <f t="shared" ref="AA2:AA14" si="1">SUM(R2)</f>
+        <v>0</v>
+      </c>
+      <c r="AB2" s="14">
+        <f t="shared" ref="AB2:AB14" si="2">SUM(Y2)</f>
+        <v>0</v>
+      </c>
+      <c r="AC2" s="16">
+        <f>SUM(J2+R2+Y2)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
       <c r="B3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="11">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="F3" s="11">
+        <v>8</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J14" si="3">SUM(E3+F3+G3+H3+I3)</f>
+        <v>12.5</v>
+      </c>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="13">
+        <f t="shared" ref="R3:R14" si="4">SUM(K3+L3+M3+N3+O3+P3+Q3)</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="14">
+        <f t="shared" ref="Y3:Y14" si="5">SUM(S3+T3+U3+V3+W3+X3)</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="12">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="AA3" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB3" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC3" s="16">
+        <f t="shared" ref="AC3:AC14" si="6">SUM(J3+R3+Y3)</f>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
-      <c r="E3" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-    </row>
-    <row r="4" spans="1:30" s="2" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="9" t="s">
+      <c r="B4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E4" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="F4" s="11">
         <v>9</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA4" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB4" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC4" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD4" s="3"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="12">
+        <f t="shared" si="3"/>
+        <v>13.7</v>
+      </c>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="12">
+        <f t="shared" si="0"/>
+        <v>13.7</v>
+      </c>
+      <c r="AA4" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB4" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC4" s="16">
+        <f t="shared" si="6"/>
+        <v>13.7</v>
+      </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
       <c r="B5" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="D5" s="11">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="E5" s="11">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="F5" s="11">
-        <v>2</v>
-      </c>
-      <c r="G5" s="11">
-        <v>3</v>
-      </c>
-      <c r="H5" s="11">
-        <v>5</v>
-      </c>
-      <c r="I5" s="11">
-        <v>5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
       <c r="J5" s="12">
-        <f>SUM(E5+F5+G5+H5+I5)</f>
-        <v>16</v>
+        <f t="shared" si="3"/>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
@@ -2629,7 +2773,7 @@
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
       <c r="R5" s="13">
-        <f>SUM(K5+L5+M5+N5+O5+P5+Q5)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S5" s="11"/>
@@ -2639,49 +2783,51 @@
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="14">
-        <f>SUM(S5+T5+U5+V5+W5+X5)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z5" s="12">
-        <f t="shared" ref="Z5:Z17" si="0">SUM(J5)</f>
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>9.8000000000000007</v>
       </c>
       <c r="AA5" s="13">
-        <f t="shared" ref="AA5:AA17" si="1">SUM(R5)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB5" s="14">
-        <f t="shared" ref="AB5:AB17" si="2">SUM(Y5)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC5" s="16">
-        <f>SUM(J5+R5+Y5)</f>
-        <v>16</v>
+        <f t="shared" si="6"/>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
       <c r="B6" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D6" s="11">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E6" s="11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F6" s="11">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="12">
-        <f t="shared" ref="J6:J17" si="3">SUM(E6+F6+G6+H6+I6)</f>
-        <v>12.5</v>
+        <f t="shared" si="3"/>
+        <v>7.7</v>
       </c>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -2691,7 +2837,7 @@
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
       <c r="R6" s="13">
-        <f t="shared" ref="R6:R17" si="4">SUM(K6+L6+M6+N6+O6+P6+Q6)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S6" s="11"/>
@@ -2701,12 +2847,12 @@
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="14">
-        <f t="shared" ref="Y6:Y17" si="5">SUM(S6+T6+U6+V6+W6+X6)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z6" s="12">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA6" s="13">
         <f t="shared" si="1"/>
@@ -2717,33 +2863,35 @@
         <v>0</v>
       </c>
       <c r="AC6" s="16">
-        <f t="shared" ref="AC6:AC17" si="6">SUM(J6+R6+Y6)</f>
-        <v>12.5</v>
+        <f t="shared" si="6"/>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
       <c r="B7" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D7" s="11">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="E7" s="11">
         <v>4.7</v>
       </c>
       <c r="F7" s="11">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="12">
         <f t="shared" si="3"/>
-        <v>13.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -2768,7 +2916,7 @@
       </c>
       <c r="Z7" s="12">
         <f t="shared" si="0"/>
-        <v>13.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AA7" s="13">
         <f t="shared" si="1"/>
@@ -2780,32 +2928,34 @@
       </c>
       <c r="AC7" s="16">
         <f t="shared" si="6"/>
-        <v>13.7</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
       <c r="B8" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" s="11">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E8" s="11">
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F8" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="12">
         <f t="shared" si="3"/>
-        <v>9.8000000000000007</v>
+        <v>11.6</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -2830,7 +2980,7 @@
       </c>
       <c r="Z8" s="12">
         <f t="shared" si="0"/>
-        <v>9.8000000000000007</v>
+        <v>11.6</v>
       </c>
       <c r="AA8" s="13">
         <f t="shared" si="1"/>
@@ -2842,32 +2992,34 @@
       </c>
       <c r="AC8" s="16">
         <f t="shared" si="6"/>
-        <v>9.8000000000000007</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
       <c r="B9" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="11">
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E9" s="11">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" s="11">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="12">
         <f t="shared" si="3"/>
-        <v>7.7</v>
+        <v>14.5</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -2892,7 +3044,7 @@
       </c>
       <c r="Z9" s="12">
         <f t="shared" si="0"/>
-        <v>7.7</v>
+        <v>14.5</v>
       </c>
       <c r="AA9" s="13">
         <f t="shared" si="1"/>
@@ -2904,13 +3056,15 @@
       </c>
       <c r="AC9" s="16">
         <f t="shared" si="6"/>
-        <v>7.7</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
       <c r="B10" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>48</v>
@@ -2919,17 +3073,17 @@
         <v>0.9</v>
       </c>
       <c r="E10" s="11">
-        <v>4.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F10" s="11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="12">
         <f t="shared" si="3"/>
-        <v>8.6999999999999993</v>
+        <v>12.1</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
@@ -2954,7 +3108,7 @@
       </c>
       <c r="Z10" s="12">
         <f t="shared" si="0"/>
-        <v>8.6999999999999993</v>
+        <v>12.1</v>
       </c>
       <c r="AA10" s="13">
         <f t="shared" si="1"/>
@@ -2966,32 +3120,34 @@
       </c>
       <c r="AC10" s="16">
         <f t="shared" si="6"/>
-        <v>8.6999999999999993</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
       <c r="B11" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>49</v>
       </c>
       <c r="D11" s="11">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E11" s="11">
-        <v>4.5999999999999996</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F11" s="11">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="J11" s="12">
         <f t="shared" si="3"/>
-        <v>11.6</v>
+        <v>15.9</v>
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
@@ -3016,7 +3172,7 @@
       </c>
       <c r="Z11" s="12">
         <f t="shared" si="0"/>
-        <v>11.6</v>
+        <v>15.9</v>
       </c>
       <c r="AA11" s="13">
         <f t="shared" si="1"/>
@@ -3028,32 +3184,34 @@
       </c>
       <c r="AC11" s="16">
         <f t="shared" si="6"/>
-        <v>11.6</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
       <c r="B12" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" s="11">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E12" s="11">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F12" s="11">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="12">
         <f t="shared" si="3"/>
-        <v>14.5</v>
+        <v>7.3</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -3078,7 +3236,7 @@
       </c>
       <c r="Z12" s="12">
         <f t="shared" si="0"/>
-        <v>14.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA12" s="13">
         <f t="shared" si="1"/>
@@ -3090,32 +3248,34 @@
       </c>
       <c r="AC12" s="16">
         <f t="shared" si="6"/>
-        <v>14.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
       <c r="B13" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D13" s="11">
-        <v>0.9</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E13" s="11">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F13" s="11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="12">
         <f t="shared" si="3"/>
-        <v>12.1</v>
+        <v>14.4</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -3140,7 +3300,7 @@
       </c>
       <c r="Z13" s="12">
         <f t="shared" si="0"/>
-        <v>12.1</v>
+        <v>14.4</v>
       </c>
       <c r="AA13" s="13">
         <f t="shared" si="1"/>
@@ -3152,32 +3312,34 @@
       </c>
       <c r="AC13" s="16">
         <f t="shared" si="6"/>
-        <v>12.1</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
+      <c r="A14" s="11">
+        <v>13</v>
+      </c>
       <c r="B14" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D14" s="11">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="E14" s="11">
-        <v>4.9000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F14" s="11">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="12">
         <f t="shared" si="3"/>
-        <v>15.9</v>
+        <v>12.3</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
@@ -3202,7 +3364,7 @@
       </c>
       <c r="Z14" s="12">
         <f t="shared" si="0"/>
-        <v>15.9</v>
+        <v>12.3</v>
       </c>
       <c r="AA14" s="13">
         <f t="shared" si="1"/>
@@ -3214,202 +3376,10 @@
       </c>
       <c r="AC14" s="16">
         <f t="shared" si="6"/>
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="11">
-        <v>0.6</v>
-      </c>
-      <c r="E15" s="11">
-        <v>4.3</v>
-      </c>
-      <c r="F15" s="11">
-        <v>3</v>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="12">
-        <f t="shared" si="3"/>
-        <v>7.3</v>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="13">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="12">
-        <f t="shared" si="0"/>
-        <v>7.3</v>
-      </c>
-      <c r="AA15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB15" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC15" s="16">
-        <f t="shared" si="6"/>
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="11">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E16" s="11">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F16" s="11">
-        <v>10</v>
-      </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="12">
-        <f t="shared" si="3"/>
-        <v>14.4</v>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="13">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="12">
-        <f t="shared" si="0"/>
-        <v>14.4</v>
-      </c>
-      <c r="AA16" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB16" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC16" s="16">
-        <f t="shared" si="6"/>
-        <v>14.4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="11">
-        <v>1</v>
-      </c>
-      <c r="E17" s="11">
-        <v>4.3</v>
-      </c>
-      <c r="F17" s="11">
-        <v>8</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="12">
-        <f t="shared" si="3"/>
         <v>12.3</v>
       </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="13">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z17" s="12">
-        <f t="shared" si="0"/>
-        <v>12.3</v>
-      </c>
-      <c r="AA17" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB17" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC17" s="16">
-        <f t="shared" si="6"/>
-        <v>12.3</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="K3:R3"/>
-    <mergeCell ref="S3:Y3"/>
-    <mergeCell ref="Z3:AC3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3429,28 +3399,28 @@
     </row>
     <row r="3" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -3461,7 +3431,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4">
         <f>SUM(D4+E4)</f>
@@ -3491,7 +3461,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C20" si="0">SUM(D5+E5)</f>
@@ -3521,7 +3491,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -3551,7 +3521,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -3581,7 +3551,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -3611,7 +3581,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -3641,7 +3611,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -3671,7 +3641,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -3701,7 +3671,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -3731,7 +3701,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -3761,7 +3731,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -3791,7 +3761,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -3821,7 +3791,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -3851,7 +3821,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -3881,7 +3851,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -3911,7 +3881,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -3941,7 +3911,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -4022,105 +3992,105 @@
     <col min="14" max="14" width="10.85546875" style="25" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="25" customWidth="1"/>
     <col min="16" max="16" width="10.85546875" style="25" customWidth="1"/>
-    <col min="17" max="17" width="32.5703125" style="47" customWidth="1"/>
+    <col min="17" max="17" width="32.5703125" style="41" customWidth="1"/>
     <col min="18" max="16384" width="9.140625" style="17"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="8" spans="1:18" ht="56.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="D8" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="E8" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="F8" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="F8" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="43" t="s">
+      <c r="H8" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="H8" s="43" t="s">
+      <c r="I8" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="J8" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="J8" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="K8" s="20" t="s">
+      <c r="L8" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="L8" s="43" t="s">
+    </row>
+    <row r="9" spans="1:18" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="51"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="21" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="21" t="s">
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="J9" s="49"/>
+      <c r="K9" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="44"/>
-      <c r="K9" s="21" t="s">
+      <c r="L9" s="49"/>
+    </row>
+    <row r="10" spans="1:18" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="50">
+        <v>1</v>
+      </c>
+      <c r="B10" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="L9" s="44"/>
-    </row>
-    <row r="10" spans="1:18" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="40">
-        <v>1</v>
-      </c>
-      <c r="B10" s="40" t="s">
+      <c r="C10" s="46"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+    </row>
+    <row r="11" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="52"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="52"/>
-    </row>
-    <row r="11" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="22" t="s">
-        <v>115</v>
-      </c>
       <c r="D11" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E11" s="23">
         <v>5</v>
@@ -4157,10 +4127,10 @@
       <c r="P11" s="4"/>
     </row>
     <row r="12" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41"/>
+      <c r="A12" s="52"/>
+      <c r="B12" s="52"/>
       <c r="C12" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" s="23">
         <v>4</v>
@@ -4197,20 +4167,20 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O12" s="46" t="str">
+      <c r="O12" s="40" t="str">
         <f>IF(OR(N12&lt;N11,AND(N12&lt;=3,N12&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта төмендеді</v>
       </c>
       <c r="P12" s="4"/>
     </row>
     <row r="13" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41"/>
+      <c r="A13" s="52"/>
+      <c r="B13" s="52"/>
       <c r="C13" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E13" s="23">
         <v>5</v>
@@ -4244,16 +4214,16 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O13" s="46" t="str">
+      <c r="O13" s="40" t="str">
         <f t="shared" ref="O13:O17" si="2">IF(OR(N13&lt;N12,AND(N13&lt;=3,N13&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41"/>
+      <c r="A14" s="52"/>
+      <c r="B14" s="52"/>
       <c r="C14" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D14" s="23">
         <v>5</v>
@@ -4290,16 +4260,16 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O14" s="46" t="str">
+      <c r="O14" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="41"/>
-      <c r="B15" s="41"/>
+      <c r="A15" s="52"/>
+      <c r="B15" s="52"/>
       <c r="C15" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D15" s="23">
         <v>5</v>
@@ -4336,48 +4306,48 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O15" s="46" t="str">
+      <c r="O15" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q15" s="48" t="str">
+      <c r="Q15" s="42" t="str">
         <f>IF(N12&lt;N11, "2-тоқсанда ынта төмендеді", IF(N13&lt;N12, "3-тоқсанда ынта төмендеді", IF(N14&lt;N13, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>2-тоқсанда ынта төмендеді</v>
       </c>
-      <c r="R15" s="45"/>
+      <c r="R15" s="39"/>
     </row>
     <row r="16" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="41"/>
-      <c r="B16" s="41"/>
+      <c r="A16" s="52"/>
+      <c r="B16" s="52"/>
       <c r="C16" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H16" s="23">
         <v>3</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J16" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M16" s="25" t="str">
         <f t="shared" si="0"/>
@@ -4387,44 +4357,44 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O16" s="46" t="str">
+      <c r="O16" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="R16" s="45"/>
+      <c r="R16" s="39"/>
     </row>
     <row r="17" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="42"/>
-      <c r="B17" s="42"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="51"/>
       <c r="C17" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H17" s="23">
         <v>3</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J17" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M17" s="25" t="str">
         <f t="shared" si="0"/>
@@ -4434,11 +4404,11 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O17" s="46" t="str">
+      <c r="O17" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q17" s="47" t="str">
+      <c r="Q17" s="41" t="str">
         <f>IF(O12:O17="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N15&lt;=3, N17&lt;=3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
@@ -4446,27 +4416,27 @@
       </c>
     </row>
     <row r="18" spans="1:17" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="40">
+      <c r="A18" s="50">
         <v>2</v>
       </c>
-      <c r="B18" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" s="51" t="str">
+      <c r="B18" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="46" t="str">
         <f>IF(O12:O18="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N15&gt;3, N17&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
       <c r="N18" s="29">
         <v>3</v>
       </c>
@@ -4475,7 +4445,7 @@
         <f>ROUNDDOWN(N18, 0)</f>
         <v>3</v>
       </c>
-      <c r="Q18" s="50" t="str">
+      <c r="Q18" s="44" t="str">
         <f>IF(O12:O18="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N15&gt;3, N17&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
@@ -4483,13 +4453,13 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="41"/>
-      <c r="B19" s="41"/>
+      <c r="A19" s="52"/>
+      <c r="B19" s="52"/>
       <c r="C19" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E19" s="23">
         <v>5</v>
@@ -4525,10 +4495,10 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="41"/>
-      <c r="B20" s="41"/>
+      <c r="A20" s="52"/>
+      <c r="B20" s="52"/>
       <c r="C20" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D20" s="23">
         <v>5</v>
@@ -4565,19 +4535,19 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="O20" s="46" t="str">
+      <c r="O20" s="40" t="str">
         <f>IF(OR(N20&lt;N19,AND(N20&lt;=3,N20&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="41"/>
-      <c r="B21" s="41"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="52"/>
       <c r="C21" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E21" s="23">
         <v>5</v>
@@ -4611,16 +4581,16 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="O21" s="46" t="str">
+      <c r="O21" s="40" t="str">
         <f t="shared" ref="O21:O25" si="5">IF(OR(N21&lt;N20,AND(N21&lt;=3,N21&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="41"/>
-      <c r="B22" s="41"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="52"/>
       <c r="C22" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D22" s="23">
         <v>5</v>
@@ -4657,16 +4627,16 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="O22" s="46" t="str">
+      <c r="O22" s="40" t="str">
         <f t="shared" si="5"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="41"/>
-      <c r="B23" s="41"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D23" s="23">
         <v>5</v>
@@ -4703,47 +4673,47 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="O23" s="46" t="str">
+      <c r="O23" s="40" t="str">
         <f t="shared" si="5"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q23" s="48" t="str">
+      <c r="Q23" s="42" t="str">
         <f>IF(N20&lt;N19, "2-тоқсанда ынта төмендеді", IF(N21&lt;N20, "3-тоқсанда ынта төмендеді", IF(N22&lt;N21, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>4-тоқсанда ынта төмендеді</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="41"/>
-      <c r="B24" s="41"/>
+      <c r="A24" s="52"/>
+      <c r="B24" s="52"/>
       <c r="C24" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H24" s="23">
         <v>5</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J24" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M24" s="25" t="str">
         <f t="shared" si="3"/>
@@ -4753,43 +4723,43 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="O24" s="46" t="str">
+      <c r="O24" s="40" t="str">
         <f t="shared" si="5"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="42"/>
-      <c r="B25" s="42"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="51"/>
       <c r="C25" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H25" s="23">
         <v>5</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J25" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M25" s="25" t="str">
         <f t="shared" si="3"/>
@@ -4799,33 +4769,33 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="O25" s="46" t="str">
+      <c r="O25" s="40" t="str">
         <f t="shared" si="5"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="40">
+      <c r="A26" s="50">
         <v>3</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="51" t="str">
+      <c r="B26" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="46" t="str">
         <f>IF(O20:O26="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N23&gt;3, N25&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="52"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
       <c r="N26" s="29">
         <f>AVERAGE(D23:L25)</f>
         <v>5</v>
@@ -4837,13 +4807,13 @@
       </c>
     </row>
     <row r="27" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="41"/>
-      <c r="B27" s="41"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E27" s="23">
         <v>5</v>
@@ -4879,10 +4849,10 @@
       </c>
     </row>
     <row r="28" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="41"/>
-      <c r="B28" s="41"/>
+      <c r="A28" s="52"/>
+      <c r="B28" s="52"/>
       <c r="C28" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D28" s="23">
         <v>5</v>
@@ -4919,19 +4889,19 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="O28" s="46" t="str">
+      <c r="O28" s="40" t="str">
         <f>IF(OR(N28&lt;N27,AND(N28&lt;=3,N28&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="41"/>
-      <c r="B29" s="41"/>
+      <c r="A29" s="52"/>
+      <c r="B29" s="52"/>
       <c r="C29" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E29" s="23">
         <v>5</v>
@@ -4965,16 +4935,16 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="O29" s="46" t="str">
+      <c r="O29" s="40" t="str">
         <f t="shared" ref="O29:O33" si="8">IF(OR(N29&lt;N28,AND(N29&lt;=3,N29&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="41"/>
-      <c r="B30" s="41"/>
+      <c r="A30" s="52"/>
+      <c r="B30" s="52"/>
       <c r="C30" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D30" s="23">
         <v>5</v>
@@ -5011,16 +4981,16 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="O30" s="46" t="str">
+      <c r="O30" s="40" t="str">
         <f t="shared" si="8"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="41"/>
-      <c r="B31" s="41"/>
+      <c r="A31" s="52"/>
+      <c r="B31" s="52"/>
       <c r="C31" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D31" s="23">
         <v>5</v>
@@ -5057,47 +5027,47 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="O31" s="46" t="str">
+      <c r="O31" s="40" t="str">
         <f t="shared" si="8"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q31" s="48" t="str">
+      <c r="Q31" s="42" t="str">
         <f>IF(N28&lt;N27, "2-тоқсанда ынта төмендеді", IF(N29&lt;N28, "3-тоқсанда ынта төмендеді", IF(N30&lt;N29, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="41"/>
-      <c r="B32" s="41"/>
+      <c r="A32" s="52"/>
+      <c r="B32" s="52"/>
       <c r="C32" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H32" s="23">
         <v>5</v>
       </c>
       <c r="I32" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J32" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K32" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M32" s="25" t="str">
         <f t="shared" si="6"/>
@@ -5107,43 +5077,43 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="O32" s="46" t="str">
+      <c r="O32" s="40" t="str">
         <f t="shared" si="8"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="42"/>
-      <c r="B33" s="42"/>
+      <c r="A33" s="51"/>
+      <c r="B33" s="51"/>
       <c r="C33" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G33" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H33" s="23">
         <v>5</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J33" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M33" s="25" t="str">
         <f t="shared" si="6"/>
@@ -5153,33 +5123,33 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="O33" s="46" t="str">
+      <c r="O33" s="40" t="str">
         <f t="shared" si="8"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="40">
-        <v>4</v>
-      </c>
-      <c r="B34" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="C34" s="51" t="str">
+      <c r="A34" s="50">
+        <v>4</v>
+      </c>
+      <c r="B34" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="46" t="str">
         <f>IF(O28:O34="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N31&gt;3, N33&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="52"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="47"/>
+      <c r="L34" s="47"/>
       <c r="N34" s="27">
         <f>AVERAGE(D31:L33)</f>
         <v>5</v>
@@ -5191,88 +5161,88 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="41"/>
-      <c r="B35" s="41"/>
+      <c r="A35" s="52"/>
+      <c r="B35" s="52"/>
       <c r="C35" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G35" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J35" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N35" s="28"/>
       <c r="O35" s="28"/>
     </row>
     <row r="36" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="41"/>
-      <c r="B36" s="41"/>
+      <c r="A36" s="52"/>
+      <c r="B36" s="52"/>
       <c r="C36" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G36" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J36" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K36" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N36" s="28"/>
-      <c r="O36" s="46" t="str">
+      <c r="O36" s="40" t="str">
         <f>IF(OR(N36&lt;N35,AND(N36&lt;=3,N36&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="41"/>
-      <c r="B37" s="41"/>
+      <c r="A37" s="52"/>
+      <c r="B37" s="52"/>
       <c r="C37" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E37" s="23">
         <v>4</v>
@@ -5306,55 +5276,55 @@
         <f>IF(MIN(D37:L37)=5, "5", IF(MIN(D37:L37)&gt;=4, "4", IF(MIN(D37:L37)=3, "3")))</f>
         <v>3</v>
       </c>
-      <c r="O37" s="46" t="str">
+      <c r="O37" s="40" t="str">
         <f t="shared" ref="O37:O41" si="9">IF(OR(N37&lt;N36,AND(N37&lt;=3,N37&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="41"/>
-      <c r="B38" s="41"/>
+      <c r="A38" s="52"/>
+      <c r="B38" s="52"/>
       <c r="C38" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F38" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G38" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H38" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I38" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J38" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L38" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N38" s="28"/>
-      <c r="O38" s="46" t="str">
+      <c r="O38" s="40" t="str">
         <f t="shared" si="9"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="41"/>
-      <c r="B39" s="41"/>
+      <c r="A39" s="52"/>
+      <c r="B39" s="52"/>
       <c r="C39" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D39" s="23">
         <v>4</v>
@@ -5391,115 +5361,115 @@
         <f>IF(MIN(D39:L39)=5, "5", IF(MIN(D39:L39)&gt;=4, "4", IF(MIN(D39:L39)=3, "3")))</f>
         <v>3</v>
       </c>
-      <c r="O39" s="46" t="str">
+      <c r="O39" s="40" t="str">
         <f t="shared" si="9"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q39" s="48" t="str">
+      <c r="Q39" s="42" t="str">
         <f>IF(N36&lt;N35, "2-тоқсанда ынта төмендеді", IF(N37&lt;N36, "3-тоқсанда ынта төмендеді", IF(N38&lt;N37, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>4-тоқсанда ынта төмендеді</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="41"/>
-      <c r="B40" s="41"/>
+      <c r="A40" s="52"/>
+      <c r="B40" s="52"/>
       <c r="C40" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F40" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G40" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I40" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J40" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L40" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N40" s="28"/>
-      <c r="O40" s="46" t="str">
+      <c r="O40" s="40" t="str">
         <f t="shared" si="9"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="42"/>
-      <c r="B41" s="42"/>
+      <c r="A41" s="51"/>
+      <c r="B41" s="51"/>
       <c r="C41" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F41" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G41" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I41" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J41" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K41" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L41" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N41" s="27"/>
-      <c r="O41" s="46" t="str">
+      <c r="O41" s="40" t="str">
         <f t="shared" si="9"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="40">
-        <v>5</v>
-      </c>
-      <c r="B42" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="C42" s="51" t="str">
+      <c r="A42" s="50">
+        <v>5</v>
+      </c>
+      <c r="B42" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="46" t="str">
         <f>IF(O36:O42="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N39&gt;3, N41&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="52"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="47"/>
+      <c r="K42" s="47"/>
+      <c r="L42" s="47"/>
       <c r="N42" s="29">
         <f>AVERAGE(D39:L41)</f>
         <v>3.8888888888888888</v>
@@ -5511,13 +5481,13 @@
       </c>
     </row>
     <row r="43" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="41"/>
-      <c r="B43" s="41"/>
+      <c r="A43" s="52"/>
+      <c r="B43" s="52"/>
       <c r="C43" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E43" s="23">
         <v>4</v>
@@ -5553,10 +5523,10 @@
       </c>
     </row>
     <row r="44" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="41"/>
-      <c r="B44" s="41"/>
+      <c r="A44" s="52"/>
+      <c r="B44" s="52"/>
       <c r="C44" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D44" s="23">
         <v>4</v>
@@ -5593,19 +5563,19 @@
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="O44" s="46" t="str">
+      <c r="O44" s="40" t="str">
         <f>IF(OR(N44&lt;N43,AND(N44&lt;=3,N44&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="41"/>
-      <c r="B45" s="41"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="52"/>
       <c r="C45" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E45" s="23">
         <v>5</v>
@@ -5639,16 +5609,16 @@
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="O45" s="46" t="str">
+      <c r="O45" s="40" t="str">
         <f t="shared" ref="O45:O49" si="12">IF(OR(N45&lt;N44,AND(N45&lt;=3,N45&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="41"/>
-      <c r="B46" s="41"/>
+      <c r="A46" s="52"/>
+      <c r="B46" s="52"/>
       <c r="C46" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D46" s="23">
         <v>5</v>
@@ -5685,16 +5655,16 @@
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="O46" s="46" t="str">
+      <c r="O46" s="40" t="str">
         <f t="shared" si="12"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="41"/>
-      <c r="B47" s="41"/>
+      <c r="A47" s="52"/>
+      <c r="B47" s="52"/>
       <c r="C47" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D47" s="23">
         <v>5</v>
@@ -5731,47 +5701,47 @@
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="O47" s="46" t="str">
+      <c r="O47" s="40" t="str">
         <f t="shared" si="12"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q47" s="48" t="str">
+      <c r="Q47" s="42" t="str">
         <f>IF(N44&lt;N43, "2-тоқсанда ынта төмендеді", IF(N45&lt;N44, "3-тоқсанда ынта төмендеді", IF(N46&lt;N45, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="41"/>
-      <c r="B48" s="41"/>
+      <c r="A48" s="52"/>
+      <c r="B48" s="52"/>
       <c r="C48" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H48" s="23">
         <v>5</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J48" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K48" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L48" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M48" s="25" t="str">
         <f t="shared" si="10"/>
@@ -5781,43 +5751,43 @@
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="O48" s="46" t="str">
+      <c r="O48" s="40" t="str">
         <f t="shared" si="12"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="42"/>
-      <c r="B49" s="42"/>
+      <c r="A49" s="51"/>
+      <c r="B49" s="51"/>
       <c r="C49" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H49" s="23">
         <v>5</v>
       </c>
       <c r="I49" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J49" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K49" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L49" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M49" s="25" t="str">
         <f t="shared" si="10"/>
@@ -5827,33 +5797,33 @@
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="O49" s="46" t="str">
+      <c r="O49" s="40" t="str">
         <f t="shared" si="12"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="40">
+      <c r="A50" s="50">
         <v>6</v>
       </c>
-      <c r="B50" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="C50" s="51" t="str">
+      <c r="B50" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" s="46" t="str">
         <f>IF(O44:O50="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N47&gt;3, N49&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="52"/>
-      <c r="H50" s="52"/>
-      <c r="I50" s="52"/>
-      <c r="J50" s="52"/>
-      <c r="K50" s="52"/>
-      <c r="L50" s="52"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="47"/>
+      <c r="K50" s="47"/>
+      <c r="L50" s="47"/>
       <c r="N50" s="29">
         <f>AVERAGE(D47:L49)</f>
         <v>5</v>
@@ -5865,13 +5835,13 @@
       </c>
     </row>
     <row r="51" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="41"/>
-      <c r="B51" s="41"/>
+      <c r="A51" s="52"/>
+      <c r="B51" s="52"/>
       <c r="C51" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E51" s="23">
         <v>5</v>
@@ -5907,10 +5877,10 @@
       </c>
     </row>
     <row r="52" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="41"/>
-      <c r="B52" s="41"/>
+      <c r="A52" s="52"/>
+      <c r="B52" s="52"/>
       <c r="C52" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D52" s="23">
         <v>4</v>
@@ -5947,19 +5917,19 @@
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="O52" s="46" t="str">
+      <c r="O52" s="40" t="str">
         <f>IF(OR(N52&lt;N51,AND(N52&lt;=3,N52&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="41"/>
-      <c r="B53" s="41"/>
+      <c r="A53" s="52"/>
+      <c r="B53" s="52"/>
       <c r="C53" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E53" s="23">
         <v>5</v>
@@ -5993,16 +5963,16 @@
         <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="O53" s="46" t="str">
+      <c r="O53" s="40" t="str">
         <f t="shared" ref="O53:O57" si="15">IF(OR(N53&lt;N52,AND(N53&lt;=3,N53&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="41"/>
-      <c r="B54" s="41"/>
+      <c r="A54" s="52"/>
+      <c r="B54" s="52"/>
       <c r="C54" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D54" s="23">
         <v>5</v>
@@ -6039,16 +6009,16 @@
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="O54" s="46" t="str">
+      <c r="O54" s="40" t="str">
         <f t="shared" si="15"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="41"/>
-      <c r="B55" s="41"/>
+      <c r="A55" s="52"/>
+      <c r="B55" s="52"/>
       <c r="C55" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D55" s="23">
         <v>5</v>
@@ -6085,47 +6055,47 @@
         <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="O55" s="46" t="str">
+      <c r="O55" s="40" t="str">
         <f t="shared" si="15"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q55" s="48" t="str">
+      <c r="Q55" s="42" t="str">
         <f>IF(N52&lt;N51, "2-тоқсанда ынта төмендеді", IF(N53&lt;N52, "3-тоқсанда ынта төмендеді", IF(N54&lt;N53, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>2-тоқсанда ынта төмендеді</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="41"/>
-      <c r="B56" s="41"/>
+      <c r="A56" s="52"/>
+      <c r="B56" s="52"/>
       <c r="C56" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F56" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G56" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H56" s="23">
         <v>5</v>
       </c>
       <c r="I56" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J56" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K56" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L56" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M56" s="25" t="str">
         <f t="shared" si="13"/>
@@ -6135,43 +6105,43 @@
         <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="O56" s="46" t="str">
+      <c r="O56" s="40" t="str">
         <f t="shared" si="15"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="42"/>
-      <c r="B57" s="42"/>
+      <c r="A57" s="51"/>
+      <c r="B57" s="51"/>
       <c r="C57" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F57" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H57" s="23">
         <v>5</v>
       </c>
       <c r="I57" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J57" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K57" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L57" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M57" s="25" t="str">
         <f t="shared" si="13"/>
@@ -6181,33 +6151,33 @@
         <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="O57" s="46" t="str">
+      <c r="O57" s="40" t="str">
         <f t="shared" si="15"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="40">
+      <c r="A58" s="50">
         <v>7</v>
       </c>
-      <c r="B58" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="C58" s="51" t="str">
+      <c r="B58" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="46" t="str">
         <f>IF(O52:O58="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N55&gt;3, N57&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D58" s="52"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="52"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="52"/>
-      <c r="K58" s="52"/>
-      <c r="L58" s="52"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="47"/>
+      <c r="H58" s="47"/>
+      <c r="I58" s="47"/>
+      <c r="J58" s="47"/>
+      <c r="K58" s="47"/>
+      <c r="L58" s="47"/>
       <c r="N58" s="29">
         <f>AVERAGE(D55:L57)</f>
         <v>5</v>
@@ -6219,13 +6189,13 @@
       </c>
     </row>
     <row r="59" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="41"/>
-      <c r="B59" s="41"/>
+      <c r="A59" s="52"/>
+      <c r="B59" s="52"/>
       <c r="C59" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E59" s="23">
         <v>5</v>
@@ -6261,10 +6231,10 @@
       </c>
     </row>
     <row r="60" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="41"/>
-      <c r="B60" s="41"/>
+      <c r="A60" s="52"/>
+      <c r="B60" s="52"/>
       <c r="C60" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D60" s="23">
         <v>4</v>
@@ -6301,19 +6271,19 @@
         <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="O60" s="46" t="str">
+      <c r="O60" s="40" t="str">
         <f>IF(OR(N60&lt;N59,AND(N60&lt;=3,N60&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="41"/>
-      <c r="B61" s="41"/>
+      <c r="A61" s="52"/>
+      <c r="B61" s="52"/>
       <c r="C61" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E61" s="23">
         <v>4</v>
@@ -6347,16 +6317,16 @@
         <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="O61" s="46" t="str">
+      <c r="O61" s="40" t="str">
         <f t="shared" ref="O61:O65" si="18">IF(OR(N61&lt;N60,AND(N61&lt;=3,N61&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="41"/>
-      <c r="B62" s="41"/>
+      <c r="A62" s="52"/>
+      <c r="B62" s="52"/>
       <c r="C62" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D62" s="23">
         <v>4</v>
@@ -6393,16 +6363,16 @@
         <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="O62" s="46" t="str">
+      <c r="O62" s="40" t="str">
         <f t="shared" si="18"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="41"/>
-      <c r="B63" s="41"/>
+      <c r="A63" s="52"/>
+      <c r="B63" s="52"/>
       <c r="C63" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D63" s="23">
         <v>4</v>
@@ -6439,47 +6409,47 @@
         <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="O63" s="46" t="str">
+      <c r="O63" s="40" t="str">
         <f t="shared" si="18"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q63" s="48" t="str">
+      <c r="Q63" s="42" t="str">
         <f>IF(N60&lt;N59, "2-тоқсанда ынта төмендеді", IF(N61&lt;N60, "3-тоқсанда ынта төмендеді", IF(N62&lt;N61, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="41"/>
-      <c r="B64" s="41"/>
+      <c r="A64" s="52"/>
+      <c r="B64" s="52"/>
       <c r="C64" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F64" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G64" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H64" s="23">
         <v>4</v>
       </c>
       <c r="I64" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J64" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K64" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L64" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M64" s="25" t="str">
         <f t="shared" si="16"/>
@@ -6489,43 +6459,43 @@
         <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="O64" s="46" t="str">
+      <c r="O64" s="40" t="str">
         <f t="shared" si="18"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="42"/>
-      <c r="B65" s="42"/>
+      <c r="A65" s="51"/>
+      <c r="B65" s="51"/>
       <c r="C65" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F65" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G65" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H65" s="23">
         <v>4</v>
       </c>
       <c r="I65" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J65" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K65" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L65" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M65" s="25" t="str">
         <f t="shared" si="16"/>
@@ -6535,33 +6505,33 @@
         <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="O65" s="46" t="str">
+      <c r="O65" s="40" t="str">
         <f t="shared" si="18"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="40">
+      <c r="A66" s="50">
         <v>8</v>
       </c>
-      <c r="B66" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="C66" s="51" t="str">
+      <c r="B66" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" s="46" t="str">
         <f>IF(O60:O66="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N63&gt;3, N65&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D66" s="52"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="52"/>
-      <c r="G66" s="52"/>
-      <c r="H66" s="52"/>
-      <c r="I66" s="52"/>
-      <c r="J66" s="52"/>
-      <c r="K66" s="52"/>
-      <c r="L66" s="52"/>
+      <c r="D66" s="47"/>
+      <c r="E66" s="47"/>
+      <c r="F66" s="47"/>
+      <c r="G66" s="47"/>
+      <c r="H66" s="47"/>
+      <c r="I66" s="47"/>
+      <c r="J66" s="47"/>
+      <c r="K66" s="47"/>
+      <c r="L66" s="47"/>
       <c r="N66" s="29">
         <f>AVERAGE(D63:L65)</f>
         <v>4</v>
@@ -6573,13 +6543,13 @@
       </c>
     </row>
     <row r="67" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="41"/>
-      <c r="B67" s="41"/>
+      <c r="A67" s="52"/>
+      <c r="B67" s="52"/>
       <c r="C67" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E67" s="23">
         <v>5</v>
@@ -6615,10 +6585,10 @@
       </c>
     </row>
     <row r="68" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="41"/>
-      <c r="B68" s="41"/>
+      <c r="A68" s="52"/>
+      <c r="B68" s="52"/>
       <c r="C68" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D68" s="23">
         <v>5</v>
@@ -6655,19 +6625,19 @@
         <f t="shared" si="20"/>
         <v>4</v>
       </c>
-      <c r="O68" s="46" t="str">
+      <c r="O68" s="40" t="str">
         <f>IF(OR(N68&lt;N67,AND(N68&lt;=3,N68&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="41"/>
-      <c r="B69" s="41"/>
+      <c r="A69" s="52"/>
+      <c r="B69" s="52"/>
       <c r="C69" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E69" s="23">
         <v>5</v>
@@ -6701,16 +6671,16 @@
         <f t="shared" si="20"/>
         <v>4</v>
       </c>
-      <c r="O69" s="46" t="str">
+      <c r="O69" s="40" t="str">
         <f t="shared" ref="O69:O73" si="21">IF(OR(N69&lt;N68,AND(N69&lt;=3,N69&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="70" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="41"/>
-      <c r="B70" s="41"/>
+      <c r="A70" s="52"/>
+      <c r="B70" s="52"/>
       <c r="C70" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D70" s="23">
         <v>5</v>
@@ -6747,16 +6717,16 @@
         <f t="shared" si="20"/>
         <v>4</v>
       </c>
-      <c r="O70" s="46" t="str">
+      <c r="O70" s="40" t="str">
         <f t="shared" si="21"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="71" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="41"/>
-      <c r="B71" s="41"/>
+      <c r="A71" s="52"/>
+      <c r="B71" s="52"/>
       <c r="C71" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D71" s="23">
         <v>5</v>
@@ -6793,47 +6763,47 @@
         <f t="shared" si="20"/>
         <v>5</v>
       </c>
-      <c r="O71" s="46" t="str">
+      <c r="O71" s="40" t="str">
         <f t="shared" si="21"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q71" s="48" t="str">
+      <c r="Q71" s="42" t="str">
         <f>IF(N68&lt;N67, "2-тоқсанда ынта төмендеді", IF(N69&lt;N68, "3-тоқсанда ынта төмендеді", IF(N70&lt;N69, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="72" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="41"/>
-      <c r="B72" s="41"/>
+      <c r="A72" s="52"/>
+      <c r="B72" s="52"/>
       <c r="C72" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E72" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F72" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G72" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H72" s="23">
         <v>5</v>
       </c>
       <c r="I72" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J72" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K72" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L72" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M72" s="25" t="str">
         <f t="shared" si="19"/>
@@ -6843,43 +6813,43 @@
         <f t="shared" si="20"/>
         <v>5</v>
       </c>
-      <c r="O72" s="46" t="str">
+      <c r="O72" s="40" t="str">
         <f t="shared" si="21"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="73" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="42"/>
-      <c r="B73" s="42"/>
+      <c r="A73" s="51"/>
+      <c r="B73" s="51"/>
       <c r="C73" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E73" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F73" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G73" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H73" s="23">
         <v>5</v>
       </c>
       <c r="I73" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J73" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K73" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L73" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M73" s="25" t="str">
         <f t="shared" si="19"/>
@@ -6889,33 +6859,33 @@
         <f t="shared" si="20"/>
         <v>5</v>
       </c>
-      <c r="O73" s="46" t="str">
+      <c r="O73" s="40" t="str">
         <f t="shared" si="21"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="74" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="40">
+      <c r="A74" s="50">
         <v>9</v>
       </c>
-      <c r="B74" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="C74" s="51" t="str">
+      <c r="B74" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C74" s="46" t="str">
         <f>IF(O68:O74="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N71&gt;3, N73&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
-      <c r="G74" s="52"/>
-      <c r="H74" s="52"/>
-      <c r="I74" s="52"/>
-      <c r="J74" s="52"/>
-      <c r="K74" s="52"/>
-      <c r="L74" s="52"/>
+      <c r="D74" s="47"/>
+      <c r="E74" s="47"/>
+      <c r="F74" s="47"/>
+      <c r="G74" s="47"/>
+      <c r="H74" s="47"/>
+      <c r="I74" s="47"/>
+      <c r="J74" s="47"/>
+      <c r="K74" s="47"/>
+      <c r="L74" s="47"/>
       <c r="N74" s="29">
         <f>AVERAGE(D71:L73)</f>
         <v>5</v>
@@ -6927,13 +6897,13 @@
       </c>
     </row>
     <row r="75" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="41"/>
-      <c r="B75" s="41"/>
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
       <c r="C75" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E75" s="23">
         <v>4</v>
@@ -6969,10 +6939,10 @@
       </c>
     </row>
     <row r="76" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="41"/>
-      <c r="B76" s="41"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
       <c r="C76" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D76" s="23">
         <v>4</v>
@@ -7009,19 +6979,19 @@
         <f t="shared" si="23"/>
         <v>4</v>
       </c>
-      <c r="O76" s="46" t="str">
+      <c r="O76" s="40" t="str">
         <f>IF(OR(N76&lt;N75,AND(N76&lt;=3,N76&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="77" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="41"/>
-      <c r="B77" s="41"/>
+      <c r="A77" s="52"/>
+      <c r="B77" s="52"/>
       <c r="C77" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E77" s="23">
         <v>5</v>
@@ -7055,16 +7025,16 @@
         <f t="shared" si="23"/>
         <v>4</v>
       </c>
-      <c r="O77" s="46" t="str">
+      <c r="O77" s="40" t="str">
         <f t="shared" ref="O77:O81" si="24">IF(OR(N77&lt;N76,AND(N77&lt;=3,N77&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="78" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="41"/>
-      <c r="B78" s="41"/>
+      <c r="A78" s="52"/>
+      <c r="B78" s="52"/>
       <c r="C78" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D78" s="23">
         <v>4</v>
@@ -7101,16 +7071,16 @@
         <f t="shared" si="23"/>
         <v>4</v>
       </c>
-      <c r="O78" s="46" t="str">
+      <c r="O78" s="40" t="str">
         <f t="shared" si="24"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="41"/>
-      <c r="B79" s="41"/>
+      <c r="A79" s="52"/>
+      <c r="B79" s="52"/>
       <c r="C79" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D79" s="23">
         <v>4</v>
@@ -7147,47 +7117,47 @@
         <f t="shared" si="23"/>
         <v>4</v>
       </c>
-      <c r="O79" s="46" t="str">
+      <c r="O79" s="40" t="str">
         <f t="shared" si="24"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q79" s="48" t="str">
+      <c r="Q79" s="42" t="str">
         <f>IF(N76&lt;N75, "2-тоқсанда ынта төмендеді", IF(N77&lt;N76, "3-тоқсанда ынта төмендеді", IF(N78&lt;N77, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="41"/>
-      <c r="B80" s="41"/>
+      <c r="A80" s="52"/>
+      <c r="B80" s="52"/>
       <c r="C80" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G80" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H80" s="23">
         <v>4</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K80" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L80" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M80" s="25" t="str">
         <f t="shared" si="22"/>
@@ -7197,43 +7167,43 @@
         <f t="shared" si="23"/>
         <v>4</v>
       </c>
-      <c r="O80" s="46" t="str">
+      <c r="O80" s="40" t="str">
         <f t="shared" si="24"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="81" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="42"/>
-      <c r="B81" s="42"/>
+      <c r="A81" s="51"/>
+      <c r="B81" s="51"/>
       <c r="C81" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G81" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H81" s="23">
         <v>4</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K81" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L81" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M81" s="25" t="str">
         <f t="shared" si="22"/>
@@ -7243,33 +7213,33 @@
         <f t="shared" si="23"/>
         <v>4</v>
       </c>
-      <c r="O81" s="46" t="str">
+      <c r="O81" s="40" t="str">
         <f t="shared" si="24"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="82" spans="1:17" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="40">
+      <c r="A82" s="50">
         <v>10</v>
       </c>
-      <c r="B82" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="C82" s="51" t="str">
+      <c r="B82" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="C82" s="46" t="str">
         <f>IF(O76:O82="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N79&gt;3, N81&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D82" s="52"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="52"/>
-      <c r="G82" s="52"/>
-      <c r="H82" s="52"/>
-      <c r="I82" s="52"/>
-      <c r="J82" s="52"/>
-      <c r="K82" s="52"/>
-      <c r="L82" s="52"/>
+      <c r="D82" s="47"/>
+      <c r="E82" s="47"/>
+      <c r="F82" s="47"/>
+      <c r="G82" s="47"/>
+      <c r="H82" s="47"/>
+      <c r="I82" s="47"/>
+      <c r="J82" s="47"/>
+      <c r="K82" s="47"/>
+      <c r="L82" s="47"/>
       <c r="N82" s="29">
         <f>AVERAGE(D79:L81)</f>
         <v>4.2727272727272725</v>
@@ -7281,13 +7251,13 @@
       </c>
     </row>
     <row r="83" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="41"/>
-      <c r="B83" s="41"/>
+      <c r="A83" s="52"/>
+      <c r="B83" s="52"/>
       <c r="C83" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E83" s="23">
         <v>5</v>
@@ -7323,10 +7293,10 @@
       </c>
     </row>
     <row r="84" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="41"/>
-      <c r="B84" s="41"/>
+      <c r="A84" s="52"/>
+      <c r="B84" s="52"/>
       <c r="C84" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D84" s="23">
         <v>4</v>
@@ -7363,19 +7333,19 @@
         <f t="shared" si="26"/>
         <v>4</v>
       </c>
-      <c r="O84" s="46" t="str">
+      <c r="O84" s="40" t="str">
         <f>IF(OR(N84&lt;N83,AND(N84&lt;=3,N84&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="85" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="41"/>
-      <c r="B85" s="41"/>
+      <c r="A85" s="52"/>
+      <c r="B85" s="52"/>
       <c r="C85" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D85" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E85" s="23">
         <v>5</v>
@@ -7409,16 +7379,16 @@
         <f t="shared" si="26"/>
         <v>4</v>
       </c>
-      <c r="O85" s="46" t="str">
+      <c r="O85" s="40" t="str">
         <f t="shared" ref="O85:O89" si="27">IF(OR(N85&lt;N84,AND(N85&lt;=3,N85&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="86" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="41"/>
-      <c r="B86" s="41"/>
+      <c r="A86" s="52"/>
+      <c r="B86" s="52"/>
       <c r="C86" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D86" s="23">
         <v>4</v>
@@ -7455,16 +7425,16 @@
         <f t="shared" si="26"/>
         <v>4</v>
       </c>
-      <c r="O86" s="46" t="str">
+      <c r="O86" s="40" t="str">
         <f t="shared" si="27"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="87" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="41"/>
-      <c r="B87" s="41"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="52"/>
       <c r="C87" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D87" s="23">
         <v>4</v>
@@ -7501,47 +7471,47 @@
         <f t="shared" si="26"/>
         <v>4</v>
       </c>
-      <c r="O87" s="46" t="str">
+      <c r="O87" s="40" t="str">
         <f t="shared" si="27"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q87" s="48" t="str">
+      <c r="Q87" s="42" t="str">
         <f>IF(N84&lt;N83, "2-тоқсанда ынта төмендеді", IF(N85&lt;N84, "3-тоқсанда ынта төмендеді", IF(N86&lt;N85, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="88" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="41"/>
-      <c r="B88" s="41"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
       <c r="C88" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E88" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F88" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G88" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H88" s="23">
         <v>4</v>
       </c>
       <c r="I88" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J88" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K88" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L88" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M88" s="25" t="str">
         <f t="shared" si="25"/>
@@ -7551,43 +7521,43 @@
         <f t="shared" si="26"/>
         <v>4</v>
       </c>
-      <c r="O88" s="46" t="str">
+      <c r="O88" s="40" t="str">
         <f t="shared" si="27"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="89" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="42"/>
-      <c r="B89" s="42"/>
+      <c r="A89" s="51"/>
+      <c r="B89" s="51"/>
       <c r="C89" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F89" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G89" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H89" s="23">
         <v>4</v>
       </c>
       <c r="I89" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J89" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K89" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L89" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M89" s="25" t="str">
         <f t="shared" si="25"/>
@@ -7597,33 +7567,33 @@
         <f t="shared" si="26"/>
         <v>4</v>
       </c>
-      <c r="O89" s="46" t="str">
+      <c r="O89" s="40" t="str">
         <f t="shared" si="27"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="90" spans="1:17" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="40">
+      <c r="A90" s="50">
         <v>11</v>
       </c>
-      <c r="B90" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="C90" s="51" t="str">
+      <c r="B90" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C90" s="46" t="str">
         <f>IF(O84:O90="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N87&gt;3, N89&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D90" s="52"/>
-      <c r="E90" s="52"/>
-      <c r="F90" s="52"/>
-      <c r="G90" s="52"/>
-      <c r="H90" s="52"/>
-      <c r="I90" s="52"/>
-      <c r="J90" s="52"/>
-      <c r="K90" s="52"/>
-      <c r="L90" s="52"/>
+      <c r="D90" s="47"/>
+      <c r="E90" s="47"/>
+      <c r="F90" s="47"/>
+      <c r="G90" s="47"/>
+      <c r="H90" s="47"/>
+      <c r="I90" s="47"/>
+      <c r="J90" s="47"/>
+      <c r="K90" s="47"/>
+      <c r="L90" s="47"/>
       <c r="N90" s="29">
         <f>AVERAGE(D87:L89)</f>
         <v>4.2727272727272725</v>
@@ -7635,13 +7605,13 @@
       </c>
     </row>
     <row r="91" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="41"/>
-      <c r="B91" s="41"/>
+      <c r="A91" s="52"/>
+      <c r="B91" s="52"/>
       <c r="C91" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E91" s="23">
         <v>4</v>
@@ -7677,10 +7647,10 @@
       </c>
     </row>
     <row r="92" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="41"/>
-      <c r="B92" s="41"/>
+      <c r="A92" s="52"/>
+      <c r="B92" s="52"/>
       <c r="C92" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D92" s="23">
         <v>4</v>
@@ -7717,19 +7687,19 @@
         <f t="shared" si="29"/>
         <v>4</v>
       </c>
-      <c r="O92" s="46" t="str">
+      <c r="O92" s="40" t="str">
         <f>IF(OR(N92&lt;N91,AND(N92&lt;=3,N92&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="93" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="41"/>
-      <c r="B93" s="41"/>
+      <c r="A93" s="52"/>
+      <c r="B93" s="52"/>
       <c r="C93" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E93" s="23">
         <v>4</v>
@@ -7763,16 +7733,16 @@
         <f t="shared" si="29"/>
         <v>4</v>
       </c>
-      <c r="O93" s="46" t="str">
+      <c r="O93" s="40" t="str">
         <f t="shared" ref="O93:O97" si="30">IF(OR(N93&lt;N92,AND(N93&lt;=3,N93&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="94" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="41"/>
-      <c r="B94" s="41"/>
+      <c r="A94" s="52"/>
+      <c r="B94" s="52"/>
       <c r="C94" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D94" s="23">
         <v>4</v>
@@ -7809,16 +7779,16 @@
         <f t="shared" si="29"/>
         <v>3</v>
       </c>
-      <c r="O94" s="46" t="str">
+      <c r="O94" s="40" t="str">
         <f t="shared" si="30"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="95" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="41"/>
-      <c r="B95" s="41"/>
+      <c r="A95" s="52"/>
+      <c r="B95" s="52"/>
       <c r="C95" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D95" s="23">
         <v>4</v>
@@ -7855,47 +7825,47 @@
         <f t="shared" si="29"/>
         <v>4</v>
       </c>
-      <c r="O95" s="46" t="str">
+      <c r="O95" s="40" t="str">
         <f t="shared" si="30"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q95" s="48" t="str">
+      <c r="Q95" s="42" t="str">
         <f>IF(N92&lt;N91, "2-тоқсанда ынта төмендеді", IF(N93&lt;N92, "3-тоқсанда ынта төмендеді", IF(N94&lt;N93, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>4-тоқсанда ынта төмендеді</v>
       </c>
     </row>
     <row r="96" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="41"/>
-      <c r="B96" s="41"/>
+      <c r="A96" s="52"/>
+      <c r="B96" s="52"/>
       <c r="C96" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D96" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E96" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F96" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G96" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H96" s="23">
         <v>4</v>
       </c>
       <c r="I96" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J96" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K96" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L96" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M96" s="25" t="str">
         <f t="shared" si="28"/>
@@ -7905,43 +7875,43 @@
         <f t="shared" si="29"/>
         <v>4</v>
       </c>
-      <c r="O96" s="46" t="str">
+      <c r="O96" s="40" t="str">
         <f t="shared" si="30"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="97" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="42"/>
-      <c r="B97" s="42"/>
+      <c r="A97" s="51"/>
+      <c r="B97" s="51"/>
       <c r="C97" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E97" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F97" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G97" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H97" s="23">
         <v>4</v>
       </c>
       <c r="I97" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J97" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K97" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L97" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M97" s="25" t="str">
         <f t="shared" si="28"/>
@@ -7951,33 +7921,33 @@
         <f t="shared" si="29"/>
         <v>4</v>
       </c>
-      <c r="O97" s="46" t="str">
+      <c r="O97" s="40" t="str">
         <f t="shared" si="30"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="98" spans="1:17" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="40">
+      <c r="A98" s="50">
         <v>12</v>
       </c>
-      <c r="B98" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="C98" s="51" t="str">
+      <c r="B98" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="C98" s="46" t="str">
         <f>IF(O92:O98="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N95&gt;3, N97&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D98" s="52"/>
-      <c r="E98" s="52"/>
-      <c r="F98" s="52"/>
-      <c r="G98" s="52"/>
-      <c r="H98" s="52"/>
-      <c r="I98" s="52"/>
-      <c r="J98" s="52"/>
-      <c r="K98" s="52"/>
-      <c r="L98" s="52"/>
+      <c r="D98" s="47"/>
+      <c r="E98" s="47"/>
+      <c r="F98" s="47"/>
+      <c r="G98" s="47"/>
+      <c r="H98" s="47"/>
+      <c r="I98" s="47"/>
+      <c r="J98" s="47"/>
+      <c r="K98" s="47"/>
+      <c r="L98" s="47"/>
       <c r="N98" s="29">
         <f>AVERAGE(D95:L97)</f>
         <v>4</v>
@@ -7989,13 +7959,13 @@
       </c>
     </row>
     <row r="99" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="41"/>
-      <c r="B99" s="41"/>
+      <c r="A99" s="52"/>
+      <c r="B99" s="52"/>
       <c r="C99" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D99" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E99" s="23">
         <v>4</v>
@@ -8031,10 +8001,10 @@
       </c>
     </row>
     <row r="100" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="41"/>
-      <c r="B100" s="41"/>
+      <c r="A100" s="52"/>
+      <c r="B100" s="52"/>
       <c r="C100" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D100" s="23">
         <v>4</v>
@@ -8071,19 +8041,19 @@
         <f t="shared" si="32"/>
         <v>4</v>
       </c>
-      <c r="O100" s="46" t="str">
+      <c r="O100" s="40" t="str">
         <f>IF(OR(N100&lt;N99,AND(N100&lt;=3,N100&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="41"/>
-      <c r="B101" s="41"/>
+      <c r="A101" s="52"/>
+      <c r="B101" s="52"/>
       <c r="C101" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D101" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E101" s="23">
         <v>5</v>
@@ -8117,16 +8087,16 @@
         <f t="shared" si="32"/>
         <v>4</v>
       </c>
-      <c r="O101" s="46" t="str">
+      <c r="O101" s="40" t="str">
         <f t="shared" ref="O101:O105" si="33">IF(OR(N101&lt;N100,AND(N101&lt;=3,N101&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="41"/>
-      <c r="B102" s="41"/>
+      <c r="A102" s="52"/>
+      <c r="B102" s="52"/>
       <c r="C102" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D102" s="23">
         <v>4</v>
@@ -8163,16 +8133,16 @@
         <f t="shared" si="32"/>
         <v>4</v>
       </c>
-      <c r="O102" s="46" t="str">
+      <c r="O102" s="40" t="str">
         <f t="shared" si="33"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="103" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="41"/>
-      <c r="B103" s="41"/>
+      <c r="A103" s="52"/>
+      <c r="B103" s="52"/>
       <c r="C103" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D103" s="23">
         <v>4</v>
@@ -8209,47 +8179,47 @@
         <f t="shared" si="32"/>
         <v>4</v>
       </c>
-      <c r="O103" s="46" t="str">
+      <c r="O103" s="40" t="str">
         <f t="shared" si="33"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q103" s="48" t="str">
+      <c r="Q103" s="42" t="str">
         <f>IF(N100&lt;N99, "2-тоқсанда ынта төмендеді", IF(N101&lt;N100, "3-тоқсанда ынта төмендеді", IF(N102&lt;N101, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="104" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="41"/>
-      <c r="B104" s="41"/>
+      <c r="A104" s="52"/>
+      <c r="B104" s="52"/>
       <c r="C104" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E104" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F104" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G104" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H104" s="23">
         <v>4</v>
       </c>
       <c r="I104" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J104" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K104" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L104" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M104" s="25" t="str">
         <f t="shared" si="31"/>
@@ -8259,43 +8229,43 @@
         <f t="shared" si="32"/>
         <v>4</v>
       </c>
-      <c r="O104" s="46" t="str">
+      <c r="O104" s="40" t="str">
         <f t="shared" si="33"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="105" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="42"/>
-      <c r="B105" s="42"/>
+      <c r="A105" s="51"/>
+      <c r="B105" s="51"/>
       <c r="C105" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D105" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E105" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F105" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G105" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H105" s="23">
         <v>4</v>
       </c>
       <c r="I105" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J105" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K105" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L105" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M105" s="25" t="str">
         <f t="shared" si="31"/>
@@ -8305,33 +8275,33 @@
         <f t="shared" si="32"/>
         <v>4</v>
       </c>
-      <c r="O105" s="46" t="str">
+      <c r="O105" s="40" t="str">
         <f t="shared" si="33"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="106" spans="1:17" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="40">
+      <c r="A106" s="50">
         <v>13</v>
       </c>
-      <c r="B106" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="C106" s="51" t="str">
+      <c r="B106" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="C106" s="46" t="str">
         <f>IF(O100:O106="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N103&gt;3, N105&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D106" s="52"/>
-      <c r="E106" s="52"/>
-      <c r="F106" s="52"/>
-      <c r="G106" s="52"/>
-      <c r="H106" s="52"/>
-      <c r="I106" s="52"/>
-      <c r="J106" s="52"/>
-      <c r="K106" s="52"/>
-      <c r="L106" s="52"/>
+      <c r="D106" s="47"/>
+      <c r="E106" s="47"/>
+      <c r="F106" s="47"/>
+      <c r="G106" s="47"/>
+      <c r="H106" s="47"/>
+      <c r="I106" s="47"/>
+      <c r="J106" s="47"/>
+      <c r="K106" s="47"/>
+      <c r="L106" s="47"/>
       <c r="N106" s="29">
         <f>AVERAGE(D103:L105)</f>
         <v>4.2727272727272725</v>
@@ -8343,13 +8313,13 @@
       </c>
     </row>
     <row r="107" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="41"/>
-      <c r="B107" s="41"/>
+      <c r="A107" s="52"/>
+      <c r="B107" s="52"/>
       <c r="C107" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E107" s="23">
         <v>5</v>
@@ -8385,10 +8355,10 @@
       </c>
     </row>
     <row r="108" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="41"/>
-      <c r="B108" s="41"/>
+      <c r="A108" s="52"/>
+      <c r="B108" s="52"/>
       <c r="C108" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D108" s="23">
         <v>5</v>
@@ -8425,19 +8395,19 @@
         <f t="shared" si="35"/>
         <v>5</v>
       </c>
-      <c r="O108" s="46" t="str">
+      <c r="O108" s="40" t="str">
         <f>IF(OR(N108&lt;N107,AND(N108&lt;=3,N108&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="109" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="41"/>
-      <c r="B109" s="41"/>
+      <c r="A109" s="52"/>
+      <c r="B109" s="52"/>
       <c r="C109" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D109" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E109" s="23">
         <v>5</v>
@@ -8471,16 +8441,16 @@
         <f t="shared" si="35"/>
         <v>5</v>
       </c>
-      <c r="O109" s="46" t="str">
+      <c r="O109" s="40" t="str">
         <f t="shared" ref="O109:O113" si="36">IF(OR(N109&lt;N108,AND(N109&lt;=3,N109&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="110" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="41"/>
-      <c r="B110" s="41"/>
+      <c r="A110" s="52"/>
+      <c r="B110" s="52"/>
       <c r="C110" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D110" s="23">
         <v>5</v>
@@ -8517,16 +8487,16 @@
         <f t="shared" si="35"/>
         <v>5</v>
       </c>
-      <c r="O110" s="46" t="str">
+      <c r="O110" s="40" t="str">
         <f t="shared" si="36"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="111" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="41"/>
-      <c r="B111" s="41"/>
+      <c r="A111" s="52"/>
+      <c r="B111" s="52"/>
       <c r="C111" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D111" s="23">
         <v>5</v>
@@ -8563,47 +8533,47 @@
         <f t="shared" si="35"/>
         <v>5</v>
       </c>
-      <c r="O111" s="46" t="str">
+      <c r="O111" s="40" t="str">
         <f t="shared" si="36"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q111" s="48" t="str">
+      <c r="Q111" s="42" t="str">
         <f>IF(N108&lt;N107, "2-тоқсанда ынта төмендеді", IF(N109&lt;N108, "3-тоқсанда ынта төмендеді", IF(N110&lt;N109, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="112" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="41"/>
-      <c r="B112" s="41"/>
+      <c r="A112" s="52"/>
+      <c r="B112" s="52"/>
       <c r="C112" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D112" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E112" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F112" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G112" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H112" s="23">
         <v>5</v>
       </c>
       <c r="I112" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J112" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K112" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L112" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M112" s="25" t="str">
         <f t="shared" si="34"/>
@@ -8613,43 +8583,43 @@
         <f t="shared" si="35"/>
         <v>5</v>
       </c>
-      <c r="O112" s="46" t="str">
+      <c r="O112" s="40" t="str">
         <f t="shared" si="36"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="113" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="42"/>
-      <c r="B113" s="42"/>
+      <c r="A113" s="51"/>
+      <c r="B113" s="51"/>
       <c r="C113" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D113" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E113" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F113" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G113" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H113" s="23">
         <v>5</v>
       </c>
       <c r="I113" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J113" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K113" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L113" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M113" s="25" t="str">
         <f t="shared" si="34"/>
@@ -8659,33 +8629,33 @@
         <f t="shared" si="35"/>
         <v>5</v>
       </c>
-      <c r="O113" s="46" t="str">
+      <c r="O113" s="40" t="str">
         <f t="shared" si="36"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="114" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="40">
+      <c r="A114" s="50">
         <v>14</v>
       </c>
-      <c r="B114" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="C114" s="51" t="str">
+      <c r="B114" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="C114" s="46" t="str">
         <f>IF(O108:O114="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N111&gt;3, N113&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D114" s="52"/>
-      <c r="E114" s="52"/>
-      <c r="F114" s="52"/>
-      <c r="G114" s="52"/>
-      <c r="H114" s="52"/>
-      <c r="I114" s="52"/>
-      <c r="J114" s="52"/>
-      <c r="K114" s="52"/>
-      <c r="L114" s="52"/>
+      <c r="D114" s="47"/>
+      <c r="E114" s="47"/>
+      <c r="F114" s="47"/>
+      <c r="G114" s="47"/>
+      <c r="H114" s="47"/>
+      <c r="I114" s="47"/>
+      <c r="J114" s="47"/>
+      <c r="K114" s="47"/>
+      <c r="L114" s="47"/>
       <c r="N114" s="29">
         <f>AVERAGE(D111:L113)</f>
         <v>5</v>
@@ -8697,13 +8667,13 @@
       </c>
     </row>
     <row r="115" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="41"/>
-      <c r="B115" s="41"/>
+      <c r="A115" s="52"/>
+      <c r="B115" s="52"/>
       <c r="C115" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D115" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E115" s="23">
         <v>4</v>
@@ -8739,10 +8709,10 @@
       </c>
     </row>
     <row r="116" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="41"/>
-      <c r="B116" s="41"/>
+      <c r="A116" s="52"/>
+      <c r="B116" s="52"/>
       <c r="C116" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D116" s="23">
         <v>4</v>
@@ -8779,19 +8749,19 @@
         <f t="shared" si="38"/>
         <v>4</v>
       </c>
-      <c r="O116" s="46" t="str">
+      <c r="O116" s="40" t="str">
         <f>IF(OR(N116&lt;N115,AND(N116&lt;=3,N116&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="117" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="41"/>
-      <c r="B117" s="41"/>
+      <c r="A117" s="52"/>
+      <c r="B117" s="52"/>
       <c r="C117" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D117" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E117" s="23">
         <v>5</v>
@@ -8825,16 +8795,16 @@
         <f t="shared" si="38"/>
         <v>4</v>
       </c>
-      <c r="O117" s="46" t="str">
+      <c r="O117" s="40" t="str">
         <f t="shared" ref="O117:O121" si="39">IF(OR(N117&lt;N116,AND(N117&lt;=3,N117&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="118" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="41"/>
-      <c r="B118" s="41"/>
+      <c r="A118" s="52"/>
+      <c r="B118" s="52"/>
       <c r="C118" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D118" s="23">
         <v>4</v>
@@ -8871,16 +8841,16 @@
         <f t="shared" si="38"/>
         <v>4</v>
       </c>
-      <c r="O118" s="46" t="str">
+      <c r="O118" s="40" t="str">
         <f t="shared" si="39"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="119" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="41"/>
-      <c r="B119" s="41"/>
+      <c r="A119" s="52"/>
+      <c r="B119" s="52"/>
       <c r="C119" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D119" s="23">
         <v>4</v>
@@ -8917,47 +8887,47 @@
         <f t="shared" si="38"/>
         <v>4</v>
       </c>
-      <c r="O119" s="46" t="str">
+      <c r="O119" s="40" t="str">
         <f t="shared" si="39"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q119" s="48" t="str">
+      <c r="Q119" s="42" t="str">
         <f>IF(N116&lt;N115, "2-тоқсанда ынта төмендеді", IF(N117&lt;N116, "3-тоқсанда ынта төмендеді", IF(N118&lt;N117, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="120" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="41"/>
-      <c r="B120" s="41"/>
+      <c r="A120" s="52"/>
+      <c r="B120" s="52"/>
       <c r="C120" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D120" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E120" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F120" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G120" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H120" s="23">
         <v>4</v>
       </c>
       <c r="I120" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J120" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K120" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L120" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M120" s="25" t="str">
         <f t="shared" si="37"/>
@@ -8967,43 +8937,43 @@
         <f t="shared" si="38"/>
         <v>4</v>
       </c>
-      <c r="O120" s="46" t="str">
+      <c r="O120" s="40" t="str">
         <f t="shared" si="39"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="121" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="42"/>
-      <c r="B121" s="42"/>
+      <c r="A121" s="51"/>
+      <c r="B121" s="51"/>
       <c r="C121" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D121" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E121" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F121" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G121" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H121" s="23">
         <v>4</v>
       </c>
       <c r="I121" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J121" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K121" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L121" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M121" s="25" t="str">
         <f t="shared" si="37"/>
@@ -9013,33 +8983,33 @@
         <f t="shared" si="38"/>
         <v>4</v>
       </c>
-      <c r="O121" s="46" t="str">
+      <c r="O121" s="40" t="str">
         <f t="shared" si="39"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="122" spans="1:17" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="40">
+      <c r="A122" s="50">
         <v>15</v>
       </c>
-      <c r="B122" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="C122" s="51" t="str">
+      <c r="B122" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="C122" s="46" t="str">
         <f>IF(O116:O122="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N119&gt;3, N121&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D122" s="52"/>
-      <c r="E122" s="52"/>
-      <c r="F122" s="52"/>
-      <c r="G122" s="52"/>
-      <c r="H122" s="52"/>
-      <c r="I122" s="52"/>
-      <c r="J122" s="52"/>
-      <c r="K122" s="52"/>
-      <c r="L122" s="52"/>
+      <c r="D122" s="47"/>
+      <c r="E122" s="47"/>
+      <c r="F122" s="47"/>
+      <c r="G122" s="47"/>
+      <c r="H122" s="47"/>
+      <c r="I122" s="47"/>
+      <c r="J122" s="47"/>
+      <c r="K122" s="47"/>
+      <c r="L122" s="47"/>
       <c r="N122" s="29">
         <f>AVERAGE(D119:L121)</f>
         <v>4.1818181818181817</v>
@@ -9051,13 +9021,13 @@
       </c>
     </row>
     <row r="123" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="41"/>
-      <c r="B123" s="41"/>
+      <c r="A123" s="52"/>
+      <c r="B123" s="52"/>
       <c r="C123" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D123" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E123" s="23">
         <v>4</v>
@@ -9093,10 +9063,10 @@
       </c>
     </row>
     <row r="124" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="41"/>
-      <c r="B124" s="41"/>
+      <c r="A124" s="52"/>
+      <c r="B124" s="52"/>
       <c r="C124" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D124" s="23">
         <v>4</v>
@@ -9133,19 +9103,19 @@
         <f t="shared" si="41"/>
         <v>4</v>
       </c>
-      <c r="O124" s="46" t="str">
+      <c r="O124" s="40" t="str">
         <f>IF(OR(N124&lt;N123,AND(N124&lt;=3,N124&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="125" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="41"/>
-      <c r="B125" s="41"/>
+      <c r="A125" s="52"/>
+      <c r="B125" s="52"/>
       <c r="C125" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D125" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E125" s="23">
         <v>5</v>
@@ -9179,16 +9149,16 @@
         <f t="shared" si="41"/>
         <v>4</v>
       </c>
-      <c r="O125" s="46" t="str">
+      <c r="O125" s="40" t="str">
         <f t="shared" ref="O125:O129" si="42">IF(OR(N125&lt;N124,AND(N125&lt;=3,N125&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="126" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="41"/>
-      <c r="B126" s="41"/>
+      <c r="A126" s="52"/>
+      <c r="B126" s="52"/>
       <c r="C126" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D126" s="23">
         <v>5</v>
@@ -9225,16 +9195,16 @@
         <f t="shared" si="41"/>
         <v>5</v>
       </c>
-      <c r="O126" s="46" t="str">
+      <c r="O126" s="40" t="str">
         <f t="shared" si="42"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="127" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="41"/>
-      <c r="B127" s="41"/>
+      <c r="A127" s="52"/>
+      <c r="B127" s="52"/>
       <c r="C127" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D127" s="23">
         <v>5</v>
@@ -9271,47 +9241,47 @@
         <f t="shared" si="41"/>
         <v>5</v>
       </c>
-      <c r="O127" s="46" t="str">
+      <c r="O127" s="40" t="str">
         <f t="shared" si="42"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q127" s="48" t="str">
+      <c r="Q127" s="42" t="str">
         <f>IF(N124&lt;N123, "2-тоқсанда ынта төмендеді", IF(N125&lt;N124, "3-тоқсанда ынта төмендеді", IF(N126&lt;N125, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="128" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="41"/>
-      <c r="B128" s="41"/>
+      <c r="A128" s="52"/>
+      <c r="B128" s="52"/>
       <c r="C128" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D128" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E128" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F128" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G128" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H128" s="23">
         <v>5</v>
       </c>
       <c r="I128" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J128" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K128" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L128" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M128" s="25" t="str">
         <f t="shared" si="40"/>
@@ -9321,43 +9291,43 @@
         <f t="shared" si="41"/>
         <v>5</v>
       </c>
-      <c r="O128" s="46" t="str">
+      <c r="O128" s="40" t="str">
         <f t="shared" si="42"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="129" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="42"/>
-      <c r="B129" s="42"/>
+      <c r="A129" s="51"/>
+      <c r="B129" s="51"/>
       <c r="C129" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D129" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E129" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F129" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G129" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H129" s="23">
         <v>5</v>
       </c>
       <c r="I129" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J129" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K129" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L129" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M129" s="25" t="str">
         <f t="shared" si="40"/>
@@ -9367,33 +9337,33 @@
         <f t="shared" si="41"/>
         <v>5</v>
       </c>
-      <c r="O129" s="46" t="str">
+      <c r="O129" s="40" t="str">
         <f t="shared" si="42"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="130" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="40">
+      <c r="A130" s="50">
         <v>16</v>
       </c>
-      <c r="B130" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="C130" s="51" t="str">
+      <c r="B130" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="C130" s="46" t="str">
         <f>IF(O124:O130="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N127&gt;3, N129&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D130" s="52"/>
-      <c r="E130" s="52"/>
-      <c r="F130" s="52"/>
-      <c r="G130" s="52"/>
-      <c r="H130" s="52"/>
-      <c r="I130" s="52"/>
-      <c r="J130" s="52"/>
-      <c r="K130" s="52"/>
-      <c r="L130" s="52"/>
+      <c r="D130" s="47"/>
+      <c r="E130" s="47"/>
+      <c r="F130" s="47"/>
+      <c r="G130" s="47"/>
+      <c r="H130" s="47"/>
+      <c r="I130" s="47"/>
+      <c r="J130" s="47"/>
+      <c r="K130" s="47"/>
+      <c r="L130" s="47"/>
       <c r="N130" s="29">
         <f>AVERAGE(D127:L129)</f>
         <v>5</v>
@@ -9405,13 +9375,13 @@
       </c>
     </row>
     <row r="131" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="41"/>
-      <c r="B131" s="41"/>
+      <c r="A131" s="52"/>
+      <c r="B131" s="52"/>
       <c r="C131" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D131" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E131" s="23">
         <v>5</v>
@@ -9447,10 +9417,10 @@
       </c>
     </row>
     <row r="132" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="41"/>
-      <c r="B132" s="41"/>
+      <c r="A132" s="52"/>
+      <c r="B132" s="52"/>
       <c r="C132" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D132" s="23">
         <v>5</v>
@@ -9487,19 +9457,19 @@
         <f t="shared" si="44"/>
         <v>5</v>
       </c>
-      <c r="O132" s="46" t="str">
+      <c r="O132" s="40" t="str">
         <f>IF(OR(N132&lt;N131,AND(N132&lt;=3,N132&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="133" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="41"/>
-      <c r="B133" s="41"/>
+      <c r="A133" s="52"/>
+      <c r="B133" s="52"/>
       <c r="C133" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D133" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E133" s="23">
         <v>5</v>
@@ -9533,16 +9503,16 @@
         <f t="shared" si="44"/>
         <v>4</v>
       </c>
-      <c r="O133" s="46" t="str">
+      <c r="O133" s="40" t="str">
         <f t="shared" ref="O133:O137" si="45">IF(OR(N133&lt;N132,AND(N133&lt;=3,N133&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="134" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="41"/>
-      <c r="B134" s="41"/>
+      <c r="A134" s="52"/>
+      <c r="B134" s="52"/>
       <c r="C134" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D134" s="23">
         <v>5</v>
@@ -9579,16 +9549,16 @@
         <f t="shared" si="44"/>
         <v>4</v>
       </c>
-      <c r="O134" s="46" t="str">
+      <c r="O134" s="40" t="str">
         <f t="shared" si="45"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="135" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="41"/>
-      <c r="B135" s="41"/>
+      <c r="A135" s="52"/>
+      <c r="B135" s="52"/>
       <c r="C135" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D135" s="23">
         <v>5</v>
@@ -9625,47 +9595,47 @@
         <f t="shared" si="44"/>
         <v>5</v>
       </c>
-      <c r="O135" s="46" t="str">
+      <c r="O135" s="40" t="str">
         <f t="shared" si="45"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q135" s="48" t="str">
+      <c r="Q135" s="42" t="str">
         <f>IF(N132&lt;N131, "2-тоқсанда ынта төмендеді", IF(N133&lt;N132, "3-тоқсанда ынта төмендеді", IF(N134&lt;N133, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>3-тоқсанда ынта төмендеді</v>
       </c>
     </row>
     <row r="136" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="41"/>
-      <c r="B136" s="41"/>
+      <c r="A136" s="52"/>
+      <c r="B136" s="52"/>
       <c r="C136" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D136" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E136" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F136" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G136" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H136" s="23">
         <v>5</v>
       </c>
       <c r="I136" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J136" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K136" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L136" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M136" s="25" t="str">
         <f t="shared" si="43"/>
@@ -9675,43 +9645,43 @@
         <f t="shared" si="44"/>
         <v>5</v>
       </c>
-      <c r="O136" s="46" t="str">
+      <c r="O136" s="40" t="str">
         <f t="shared" si="45"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="137" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="42"/>
-      <c r="B137" s="42"/>
+      <c r="A137" s="51"/>
+      <c r="B137" s="51"/>
       <c r="C137" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D137" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E137" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F137" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G137" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H137" s="23">
         <v>5</v>
       </c>
       <c r="I137" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J137" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K137" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L137" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M137" s="25" t="str">
         <f t="shared" si="43"/>
@@ -9721,33 +9691,33 @@
         <f t="shared" si="44"/>
         <v>5</v>
       </c>
-      <c r="O137" s="46" t="str">
+      <c r="O137" s="40" t="str">
         <f t="shared" si="45"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="138" spans="1:17" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="40">
+      <c r="A138" s="50">
         <v>17</v>
       </c>
-      <c r="B138" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="C138" s="51" t="str">
+      <c r="B138" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="C138" s="46" t="str">
         <f>IF(O132:O138="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N135&gt;3, N137&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D138" s="52"/>
-      <c r="E138" s="52"/>
-      <c r="F138" s="52"/>
-      <c r="G138" s="52"/>
-      <c r="H138" s="52"/>
-      <c r="I138" s="52"/>
-      <c r="J138" s="52"/>
-      <c r="K138" s="52"/>
-      <c r="L138" s="52"/>
+      <c r="D138" s="47"/>
+      <c r="E138" s="47"/>
+      <c r="F138" s="47"/>
+      <c r="G138" s="47"/>
+      <c r="H138" s="47"/>
+      <c r="I138" s="47"/>
+      <c r="J138" s="47"/>
+      <c r="K138" s="47"/>
+      <c r="L138" s="47"/>
       <c r="N138" s="29">
         <f>AVERAGE(D135:L137)</f>
         <v>5</v>
@@ -9759,13 +9729,13 @@
       </c>
     </row>
     <row r="139" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="41"/>
-      <c r="B139" s="41"/>
+      <c r="A139" s="52"/>
+      <c r="B139" s="52"/>
       <c r="C139" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D139" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E139" s="23">
         <v>5</v>
@@ -9801,10 +9771,10 @@
       </c>
     </row>
     <row r="140" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="41"/>
-      <c r="B140" s="41"/>
+      <c r="A140" s="52"/>
+      <c r="B140" s="52"/>
       <c r="C140" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D140" s="23">
         <v>5</v>
@@ -9841,19 +9811,19 @@
         <f t="shared" si="47"/>
         <v>4</v>
       </c>
-      <c r="O140" s="46" t="str">
+      <c r="O140" s="40" t="str">
         <f>IF(OR(N140&lt;N139,AND(N140&lt;=3,N140&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="141" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="41"/>
-      <c r="B141" s="41"/>
+      <c r="A141" s="52"/>
+      <c r="B141" s="52"/>
       <c r="C141" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D141" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E141" s="23">
         <v>5</v>
@@ -9887,16 +9857,16 @@
         <f t="shared" si="47"/>
         <v>5</v>
       </c>
-      <c r="O141" s="46" t="str">
+      <c r="O141" s="40" t="str">
         <f t="shared" ref="O141:O145" si="48">IF(OR(N141&lt;N140,AND(N141&lt;=3,N141&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="142" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="41"/>
-      <c r="B142" s="41"/>
+      <c r="A142" s="52"/>
+      <c r="B142" s="52"/>
       <c r="C142" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D142" s="23">
         <v>5</v>
@@ -9933,16 +9903,16 @@
         <f t="shared" si="47"/>
         <v>4</v>
       </c>
-      <c r="O142" s="46" t="str">
+      <c r="O142" s="40" t="str">
         <f t="shared" si="48"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="143" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="41"/>
-      <c r="B143" s="41"/>
+      <c r="A143" s="52"/>
+      <c r="B143" s="52"/>
       <c r="C143" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D143" s="23">
         <v>5</v>
@@ -9979,47 +9949,47 @@
         <f t="shared" si="47"/>
         <v>5</v>
       </c>
-      <c r="O143" s="46" t="str">
+      <c r="O143" s="40" t="str">
         <f t="shared" si="48"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q143" s="48" t="str">
+      <c r="Q143" s="42" t="str">
         <f>IF(N140&lt;N139, "2-тоқсанда ынта төмендеді", IF(N141&lt;N140, "3-тоқсанда ынта төмендеді", IF(N142&lt;N141, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>4-тоқсанда ынта төмендеді</v>
       </c>
     </row>
     <row r="144" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="41"/>
-      <c r="B144" s="41"/>
+      <c r="A144" s="52"/>
+      <c r="B144" s="52"/>
       <c r="C144" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D144" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F144" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G144" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H144" s="23">
         <v>5</v>
       </c>
       <c r="I144" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J144" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K144" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L144" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M144" s="25" t="str">
         <f t="shared" si="46"/>
@@ -10029,43 +9999,43 @@
         <f t="shared" si="47"/>
         <v>5</v>
       </c>
-      <c r="O144" s="46" t="str">
+      <c r="O144" s="40" t="str">
         <f t="shared" si="48"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="145" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="42"/>
-      <c r="B145" s="42"/>
+      <c r="A145" s="51"/>
+      <c r="B145" s="51"/>
       <c r="C145" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D145" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F145" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G145" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H145" s="23">
         <v>5</v>
       </c>
       <c r="I145" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J145" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K145" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L145" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M145" s="25" t="str">
         <f t="shared" si="46"/>
@@ -10075,33 +10045,33 @@
         <f t="shared" si="47"/>
         <v>5</v>
       </c>
-      <c r="O145" s="46" t="str">
+      <c r="O145" s="40" t="str">
         <f t="shared" si="48"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="146" spans="1:17" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="40">
+      <c r="A146" s="50">
         <v>18</v>
       </c>
-      <c r="B146" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="C146" s="51" t="str">
+      <c r="B146" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="C146" s="46" t="str">
         <f>IF(O140:O146="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N143&gt;3, N145&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D146" s="52"/>
-      <c r="E146" s="52"/>
-      <c r="F146" s="52"/>
-      <c r="G146" s="52"/>
-      <c r="H146" s="52"/>
-      <c r="I146" s="52"/>
-      <c r="J146" s="52"/>
-      <c r="K146" s="52"/>
-      <c r="L146" s="52"/>
+      <c r="D146" s="47"/>
+      <c r="E146" s="47"/>
+      <c r="F146" s="47"/>
+      <c r="G146" s="47"/>
+      <c r="H146" s="47"/>
+      <c r="I146" s="47"/>
+      <c r="J146" s="47"/>
+      <c r="K146" s="47"/>
+      <c r="L146" s="47"/>
       <c r="N146" s="29">
         <f>AVERAGE(D143:L145)</f>
         <v>5</v>
@@ -10113,120 +10083,120 @@
       </c>
     </row>
     <row r="147" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="41"/>
-      <c r="B147" s="41"/>
+      <c r="A147" s="52"/>
+      <c r="B147" s="52"/>
       <c r="C147" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D147" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E147" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="F147" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="G147" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="H147" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="I147" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="J147" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="K147" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="L147" s="23" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A148" s="52"/>
+      <c r="B148" s="52"/>
+      <c r="C148" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="E147" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="F147" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="G147" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="H147" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="I147" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="J147" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="K147" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="L147" s="23" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="41"/>
-      <c r="B148" s="41"/>
-      <c r="C148" s="22" t="s">
-        <v>117</v>
-      </c>
       <c r="D148" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E148" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F148" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G148" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H148" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I148" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J148" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K148" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L148" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="O148" s="46" t="str">
+        <v>115</v>
+      </c>
+      <c r="O148" s="40" t="str">
         <f>IF(OR(N148&lt;N147,AND(N148&lt;=3,N148&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="149" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="41"/>
-      <c r="B149" s="41"/>
+      <c r="A149" s="52"/>
+      <c r="B149" s="52"/>
       <c r="C149" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D149" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E149" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F149" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G149" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H149" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I149" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J149" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K149" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L149" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="O149" s="46" t="str">
+        <v>115</v>
+      </c>
+      <c r="O149" s="40" t="str">
         <f t="shared" ref="O149:O153" si="49">IF(OR(N149&lt;N148,AND(N149&lt;=3,N149&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="150" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="41"/>
-      <c r="B150" s="41"/>
+      <c r="A150" s="52"/>
+      <c r="B150" s="52"/>
       <c r="C150" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D150" s="23">
         <v>5</v>
@@ -10263,16 +10233,16 @@
         <f>IF(MIN(D150:L150)=5, "5", IF(MIN(D150:L150)&gt;=4, "4", IF(MIN(D150:L150)=3, "3")))</f>
         <v>5</v>
       </c>
-      <c r="O150" s="46" t="str">
+      <c r="O150" s="40" t="str">
         <f t="shared" si="49"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="151" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="41"/>
-      <c r="B151" s="41"/>
+      <c r="A151" s="52"/>
+      <c r="B151" s="52"/>
       <c r="C151" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D151" s="23">
         <v>5</v>
@@ -10309,47 +10279,47 @@
         <f>IF(MIN(D151:L151)=5, "5", IF(MIN(D151:L151)&gt;=4, "4", IF(MIN(D151:L151)=3, "3")))</f>
         <v>5</v>
       </c>
-      <c r="O151" s="46" t="str">
+      <c r="O151" s="40" t="str">
         <f t="shared" si="49"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q151" s="48" t="str">
+      <c r="Q151" s="42" t="str">
         <f>IF(N148&lt;N147, "2-тоқсанда ынта төмендеді", IF(N149&lt;N148, "3-тоқсанда ынта төмендеді", IF(N150&lt;N149, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="152" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="41"/>
-      <c r="B152" s="41"/>
+      <c r="A152" s="52"/>
+      <c r="B152" s="52"/>
       <c r="C152" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D152" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E152" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F152" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G152" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H152" s="23">
         <v>5</v>
       </c>
       <c r="I152" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J152" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K152" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L152" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M152" s="25" t="str">
         <f>IF(MIN(D152:L152)=5, "Отличник", IF(MIN(D152:L152)&gt;=4, "Хорошист", IF(MIN(D152:L152)=3, "Троечник", "Двоечник")))</f>
@@ -10359,43 +10329,43 @@
         <f>IF(MIN(D152:L152)=5, "5", IF(MIN(D152:L152)&gt;=4, "4", IF(MIN(D152:L152)=3, "3")))</f>
         <v>5</v>
       </c>
-      <c r="O152" s="46" t="str">
+      <c r="O152" s="40" t="str">
         <f t="shared" si="49"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="153" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="42"/>
-      <c r="B153" s="42"/>
+      <c r="A153" s="51"/>
+      <c r="B153" s="51"/>
       <c r="C153" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D153" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E153" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F153" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G153" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H153" s="23">
         <v>5</v>
       </c>
       <c r="I153" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J153" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K153" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L153" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M153" s="25" t="str">
         <f>IF(MIN(D153:L153)=5, "Отличник", IF(MIN(D153:L153)&gt;=4, "Хорошист", IF(MIN(D153:L153)=3, "Троечник", "Двоечник")))</f>
@@ -10405,33 +10375,33 @@
         <f>IF(MIN(D153:L153)=5, "5", IF(MIN(D153:L153)&gt;=4, "4", IF(MIN(D153:L153)=3, "3")))</f>
         <v>5</v>
       </c>
-      <c r="O153" s="46" t="str">
+      <c r="O153" s="40" t="str">
         <f t="shared" si="49"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="154" spans="1:17" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="40">
+      <c r="A154" s="50">
         <v>19</v>
       </c>
-      <c r="B154" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="C154" s="51" t="str">
+      <c r="B154" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="C154" s="46" t="str">
         <f>IF(O148:O154="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N151&gt;3, N153&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D154" s="52"/>
-      <c r="E154" s="52"/>
-      <c r="F154" s="52"/>
-      <c r="G154" s="52"/>
-      <c r="H154" s="52"/>
-      <c r="I154" s="52"/>
-      <c r="J154" s="52"/>
-      <c r="K154" s="52"/>
-      <c r="L154" s="52"/>
+      <c r="D154" s="47"/>
+      <c r="E154" s="47"/>
+      <c r="F154" s="47"/>
+      <c r="G154" s="47"/>
+      <c r="H154" s="47"/>
+      <c r="I154" s="47"/>
+      <c r="J154" s="47"/>
+      <c r="K154" s="47"/>
+      <c r="L154" s="47"/>
       <c r="N154" s="29">
         <f>AVERAGE(D151:L153)</f>
         <v>5</v>
@@ -10443,13 +10413,13 @@
       </c>
     </row>
     <row r="155" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="41"/>
-      <c r="B155" s="41"/>
+      <c r="A155" s="52"/>
+      <c r="B155" s="52"/>
       <c r="C155" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D155" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E155" s="23">
         <v>5</v>
@@ -10485,10 +10455,10 @@
       </c>
     </row>
     <row r="156" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="41"/>
-      <c r="B156" s="41"/>
+      <c r="A156" s="52"/>
+      <c r="B156" s="52"/>
       <c r="C156" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D156" s="23">
         <v>5</v>
@@ -10525,19 +10495,19 @@
         <f t="shared" si="51"/>
         <v>5</v>
       </c>
-      <c r="O156" s="46" t="str">
+      <c r="O156" s="40" t="str">
         <f>IF(OR(N156&lt;N155,AND(N156&lt;=3,N156&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="157" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="41"/>
-      <c r="B157" s="41"/>
+      <c r="A157" s="52"/>
+      <c r="B157" s="52"/>
       <c r="C157" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D157" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E157" s="23">
         <v>5</v>
@@ -10571,16 +10541,16 @@
         <f t="shared" si="51"/>
         <v>5</v>
       </c>
-      <c r="O157" s="46" t="str">
+      <c r="O157" s="40" t="str">
         <f t="shared" ref="O157:O161" si="52">IF(OR(N157&lt;N156,AND(N157&lt;=3,N157&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="158" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="41"/>
-      <c r="B158" s="41"/>
+      <c r="A158" s="52"/>
+      <c r="B158" s="52"/>
       <c r="C158" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D158" s="23">
         <v>5</v>
@@ -10617,16 +10587,16 @@
         <f t="shared" si="51"/>
         <v>4</v>
       </c>
-      <c r="O158" s="46" t="str">
+      <c r="O158" s="40" t="str">
         <f t="shared" si="52"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="159" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="41"/>
-      <c r="B159" s="41"/>
+      <c r="A159" s="52"/>
+      <c r="B159" s="52"/>
       <c r="C159" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D159" s="23">
         <v>5</v>
@@ -10663,47 +10633,47 @@
         <f t="shared" si="51"/>
         <v>5</v>
       </c>
-      <c r="O159" s="46" t="str">
+      <c r="O159" s="40" t="str">
         <f t="shared" si="52"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q159" s="48" t="str">
+      <c r="Q159" s="42" t="str">
         <f>IF(N156&lt;N155, "2-тоқсанда ынта төмендеді", IF(N157&lt;N156, "3-тоқсанда ынта төмендеді", IF(N158&lt;N157, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>4-тоқсанда ынта төмендеді</v>
       </c>
     </row>
     <row r="160" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="41"/>
-      <c r="B160" s="41"/>
+      <c r="A160" s="52"/>
+      <c r="B160" s="52"/>
       <c r="C160" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D160" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F160" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G160" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H160" s="23">
         <v>5</v>
       </c>
       <c r="I160" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J160" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K160" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L160" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M160" s="25" t="str">
         <f t="shared" si="50"/>
@@ -10713,43 +10683,43 @@
         <f t="shared" si="51"/>
         <v>5</v>
       </c>
-      <c r="O160" s="46" t="str">
+      <c r="O160" s="40" t="str">
         <f t="shared" si="52"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="161" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="42"/>
-      <c r="B161" s="42"/>
+      <c r="A161" s="51"/>
+      <c r="B161" s="51"/>
       <c r="C161" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D161" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F161" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G161" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H161" s="23">
         <v>5</v>
       </c>
       <c r="I161" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J161" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K161" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L161" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M161" s="25" t="str">
         <f t="shared" si="50"/>
@@ -10759,33 +10729,33 @@
         <f t="shared" si="51"/>
         <v>5</v>
       </c>
-      <c r="O161" s="46" t="str">
+      <c r="O161" s="40" t="str">
         <f t="shared" si="52"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="162" spans="1:17" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="40">
+      <c r="A162" s="50">
         <v>20</v>
       </c>
-      <c r="B162" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="C162" s="51" t="str">
+      <c r="B162" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C162" s="46" t="str">
         <f>IF(O156:O162="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N159&gt;3, N161&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D162" s="52"/>
-      <c r="E162" s="52"/>
-      <c r="F162" s="52"/>
-      <c r="G162" s="52"/>
-      <c r="H162" s="52"/>
-      <c r="I162" s="52"/>
-      <c r="J162" s="52"/>
-      <c r="K162" s="52"/>
-      <c r="L162" s="52"/>
+      <c r="D162" s="47"/>
+      <c r="E162" s="47"/>
+      <c r="F162" s="47"/>
+      <c r="G162" s="47"/>
+      <c r="H162" s="47"/>
+      <c r="I162" s="47"/>
+      <c r="J162" s="47"/>
+      <c r="K162" s="47"/>
+      <c r="L162" s="47"/>
       <c r="N162" s="29">
         <f>AVERAGE(D159:L161)</f>
         <v>5</v>
@@ -10797,13 +10767,13 @@
       </c>
     </row>
     <row r="163" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="41"/>
-      <c r="B163" s="41"/>
+      <c r="A163" s="52"/>
+      <c r="B163" s="52"/>
       <c r="C163" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D163" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E163" s="23">
         <v>4</v>
@@ -10839,10 +10809,10 @@
       </c>
     </row>
     <row r="164" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="41"/>
-      <c r="B164" s="41"/>
+      <c r="A164" s="52"/>
+      <c r="B164" s="52"/>
       <c r="C164" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D164" s="23">
         <v>4</v>
@@ -10879,19 +10849,19 @@
         <f t="shared" si="54"/>
         <v>4</v>
       </c>
-      <c r="O164" s="46" t="str">
+      <c r="O164" s="40" t="str">
         <f>IF(OR(N164&lt;N163,AND(N164&lt;=3,N164&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="165" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="41"/>
-      <c r="B165" s="41"/>
+      <c r="A165" s="52"/>
+      <c r="B165" s="52"/>
       <c r="C165" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D165" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E165" s="23">
         <v>4</v>
@@ -10925,16 +10895,16 @@
         <f t="shared" si="54"/>
         <v>4</v>
       </c>
-      <c r="O165" s="46" t="str">
+      <c r="O165" s="40" t="str">
         <f t="shared" ref="O165:O169" si="55">IF(OR(N165&lt;N164,AND(N165&lt;=3,N165&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="166" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="41"/>
-      <c r="B166" s="41"/>
+      <c r="A166" s="52"/>
+      <c r="B166" s="52"/>
       <c r="C166" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D166" s="23">
         <v>4</v>
@@ -10971,16 +10941,16 @@
         <f t="shared" si="54"/>
         <v>4</v>
       </c>
-      <c r="O166" s="46" t="str">
+      <c r="O166" s="40" t="str">
         <f t="shared" si="55"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="167" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="41"/>
-      <c r="B167" s="41"/>
+      <c r="A167" s="52"/>
+      <c r="B167" s="52"/>
       <c r="C167" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D167" s="23">
         <v>4</v>
@@ -11017,43 +10987,43 @@
         <f t="shared" si="54"/>
         <v>4</v>
       </c>
-      <c r="O167" s="46" t="str">
+      <c r="O167" s="40" t="str">
         <f t="shared" si="55"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="168" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="41"/>
-      <c r="B168" s="41"/>
+      <c r="A168" s="52"/>
+      <c r="B168" s="52"/>
       <c r="C168" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D168" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E168" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F168" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G168" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H168" s="23">
         <v>5</v>
       </c>
       <c r="I168" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J168" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K168" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L168" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M168" s="25" t="str">
         <f t="shared" si="53"/>
@@ -11063,47 +11033,47 @@
         <f t="shared" si="54"/>
         <v>5</v>
       </c>
-      <c r="O168" s="46" t="str">
+      <c r="O168" s="40" t="str">
         <f t="shared" si="55"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q168" s="48" t="str">
+      <c r="Q168" s="42" t="str">
         <f>IF(N165&lt;N164, "2-тоқсанда ынта төмендеді", IF(N166&lt;N165, "3-тоқсанда ынта төмендеді", IF(N167&lt;N166, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="169" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="42"/>
-      <c r="B169" s="42"/>
+      <c r="A169" s="51"/>
+      <c r="B169" s="51"/>
       <c r="C169" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D169" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E169" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F169" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G169" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H169" s="23">
         <v>5</v>
       </c>
       <c r="I169" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J169" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K169" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L169" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M169" s="25" t="str">
         <f t="shared" si="53"/>
@@ -11113,33 +11083,33 @@
         <f t="shared" si="54"/>
         <v>5</v>
       </c>
-      <c r="O169" s="46" t="str">
+      <c r="O169" s="40" t="str">
         <f t="shared" si="55"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="170" spans="1:17" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="40">
+      <c r="A170" s="50">
         <v>21</v>
       </c>
-      <c r="B170" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="C170" s="51" t="str">
+      <c r="B170" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C170" s="46" t="str">
         <f>IF(O164:O170="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N167&gt;3, N169&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D170" s="52"/>
-      <c r="E170" s="52"/>
-      <c r="F170" s="52"/>
-      <c r="G170" s="52"/>
-      <c r="H170" s="52"/>
-      <c r="I170" s="52"/>
-      <c r="J170" s="52"/>
-      <c r="K170" s="52"/>
-      <c r="L170" s="52"/>
+      <c r="D170" s="47"/>
+      <c r="E170" s="47"/>
+      <c r="F170" s="47"/>
+      <c r="G170" s="47"/>
+      <c r="H170" s="47"/>
+      <c r="I170" s="47"/>
+      <c r="J170" s="47"/>
+      <c r="K170" s="47"/>
+      <c r="L170" s="47"/>
       <c r="N170" s="29">
         <f>AVERAGE(D167:L169)</f>
         <v>4.4545454545454541</v>
@@ -11151,13 +11121,13 @@
       </c>
     </row>
     <row r="171" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="41"/>
-      <c r="B171" s="41"/>
+      <c r="A171" s="52"/>
+      <c r="B171" s="52"/>
       <c r="C171" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D171" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E171" s="23">
         <v>4</v>
@@ -11193,10 +11163,10 @@
       </c>
     </row>
     <row r="172" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="41"/>
-      <c r="B172" s="41"/>
+      <c r="A172" s="52"/>
+      <c r="B172" s="52"/>
       <c r="C172" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D172" s="23">
         <v>4</v>
@@ -11233,119 +11203,119 @@
         <f>IF(MIN(D172:L172)=5, "5", IF(MIN(D172:L172)&gt;=4, "4", IF(MIN(D172:L172)=3, "3")))</f>
         <v>4</v>
       </c>
-      <c r="O172" s="46" t="str">
+      <c r="O172" s="40" t="str">
         <f>IF(OR(N172&lt;N171,AND(N172&lt;=3,N172&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="173" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="41"/>
-      <c r="B173" s="41"/>
+      <c r="A173" s="52"/>
+      <c r="B173" s="52"/>
       <c r="C173" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D173" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E173" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F173" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G173" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H173" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I173" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J173" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K173" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L173" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="O173" s="46" t="str">
+        <v>115</v>
+      </c>
+      <c r="O173" s="40" t="str">
         <f t="shared" ref="O173:O177" si="56">IF(OR(N173&lt;N172,AND(N173&lt;=3,N173&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="174" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="41"/>
-      <c r="B174" s="41"/>
+      <c r="A174" s="52"/>
+      <c r="B174" s="52"/>
       <c r="C174" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D174" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E174" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F174" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G174" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H174" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I174" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J174" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K174" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L174" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="O174" s="46" t="str">
+        <v>115</v>
+      </c>
+      <c r="O174" s="40" t="str">
         <f t="shared" si="56"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="175" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="41"/>
-      <c r="B175" s="41"/>
+      <c r="A175" s="52"/>
+      <c r="B175" s="52"/>
       <c r="C175" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D175" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E175" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F175" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G175" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H175" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I175" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J175" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K175" s="23">
         <v>5</v>
       </c>
       <c r="L175" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M175" s="25" t="str">
         <f>IF(MIN(D175:L175)=5, "Отличник", IF(MIN(D175:L175)&gt;=4, "Хорошист", IF(MIN(D175:L175)=3, "Троечник", "Двоечник")))</f>
@@ -11355,113 +11325,113 @@
         <f>IF(MIN(D175:L175)=5, "5", IF(MIN(D175:L175)&gt;=4, "4", IF(MIN(D175:L175)=3, "3")))</f>
         <v>5</v>
       </c>
-      <c r="O175" s="46" t="str">
+      <c r="O175" s="40" t="str">
         <f t="shared" si="56"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q175" s="48" t="str">
+      <c r="Q175" s="42" t="str">
         <f>IF(N172&lt;N171, "2-тоқсанда ынта төмендеді", IF(N173&lt;N172, "3-тоқсанда ынта төмендеді", IF(N174&lt;N173, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>3-тоқсанда ынта төмендеді</v>
       </c>
     </row>
     <row r="176" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="41"/>
-      <c r="B176" s="41"/>
+      <c r="A176" s="52"/>
+      <c r="B176" s="52"/>
       <c r="C176" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D176" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E176" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F176" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G176" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H176" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I176" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J176" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K176" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L176" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="O176" s="46" t="str">
+        <v>115</v>
+      </c>
+      <c r="O176" s="40" t="str">
         <f t="shared" si="56"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="177" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="42"/>
-      <c r="B177" s="42"/>
+      <c r="A177" s="51"/>
+      <c r="B177" s="51"/>
       <c r="C177" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D177" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E177" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F177" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G177" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H177" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I177" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J177" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K177" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L177" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="O177" s="46" t="str">
+        <v>115</v>
+      </c>
+      <c r="O177" s="40" t="str">
         <f t="shared" si="56"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="178" spans="1:17" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="40">
+      <c r="A178" s="50">
         <v>22</v>
       </c>
-      <c r="B178" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="C178" s="51" t="str">
+      <c r="B178" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="C178" s="46" t="str">
         <f>IF(O172:O178="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N175&gt;3, N177&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D178" s="52"/>
-      <c r="E178" s="52"/>
-      <c r="F178" s="52"/>
-      <c r="G178" s="52"/>
-      <c r="H178" s="52"/>
-      <c r="I178" s="52"/>
-      <c r="J178" s="52"/>
-      <c r="K178" s="52"/>
-      <c r="L178" s="52"/>
+      <c r="D178" s="47"/>
+      <c r="E178" s="47"/>
+      <c r="F178" s="47"/>
+      <c r="G178" s="47"/>
+      <c r="H178" s="47"/>
+      <c r="I178" s="47"/>
+      <c r="J178" s="47"/>
+      <c r="K178" s="47"/>
+      <c r="L178" s="47"/>
       <c r="N178" s="29">
         <f>AVERAGE(D172:L177)</f>
         <v>4.7</v>
@@ -11473,13 +11443,13 @@
       </c>
     </row>
     <row r="179" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="41"/>
-      <c r="B179" s="41"/>
+      <c r="A179" s="52"/>
+      <c r="B179" s="52"/>
       <c r="C179" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D179" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E179" s="23">
         <v>5</v>
@@ -11515,10 +11485,10 @@
       </c>
     </row>
     <row r="180" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="41"/>
-      <c r="B180" s="41"/>
+      <c r="A180" s="52"/>
+      <c r="B180" s="52"/>
       <c r="C180" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D180" s="23">
         <v>4</v>
@@ -11555,19 +11525,19 @@
         <f t="shared" si="58"/>
         <v>4</v>
       </c>
-      <c r="O180" s="46" t="str">
+      <c r="O180" s="40" t="str">
         <f>IF(OR(N180&lt;N179,AND(N180&lt;=3,N180&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="181" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="41"/>
-      <c r="B181" s="41"/>
+      <c r="A181" s="52"/>
+      <c r="B181" s="52"/>
       <c r="C181" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D181" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E181" s="23">
         <v>5</v>
@@ -11601,16 +11571,16 @@
         <f t="shared" si="58"/>
         <v>5</v>
       </c>
-      <c r="O181" s="46" t="str">
+      <c r="O181" s="40" t="str">
         <f t="shared" ref="O181:O185" si="59">IF(OR(N181&lt;N180,AND(N181&lt;=3,N181&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="182" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="41"/>
-      <c r="B182" s="41"/>
+      <c r="A182" s="52"/>
+      <c r="B182" s="52"/>
       <c r="C182" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D182" s="23">
         <v>5</v>
@@ -11647,16 +11617,16 @@
         <f t="shared" si="58"/>
         <v>5</v>
       </c>
-      <c r="O182" s="46" t="str">
+      <c r="O182" s="40" t="str">
         <f t="shared" si="59"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="183" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="41"/>
-      <c r="B183" s="41"/>
+      <c r="A183" s="52"/>
+      <c r="B183" s="52"/>
       <c r="C183" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D183" s="23">
         <v>5</v>
@@ -11693,47 +11663,47 @@
         <f t="shared" si="58"/>
         <v>5</v>
       </c>
-      <c r="O183" s="46" t="str">
+      <c r="O183" s="40" t="str">
         <f t="shared" si="59"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q183" s="48" t="str">
+      <c r="Q183" s="42" t="str">
         <f>IF(N180&lt;N179, "2-тоқсанда ынта төмендеді", IF(N181&lt;N180, "3-тоқсанда ынта төмендеді", IF(N182&lt;N181, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="184" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="41"/>
-      <c r="B184" s="41"/>
+      <c r="A184" s="52"/>
+      <c r="B184" s="52"/>
       <c r="C184" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D184" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E184" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F184" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G184" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H184" s="23">
         <v>5</v>
       </c>
       <c r="I184" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J184" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K184" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L184" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M184" s="25" t="str">
         <f t="shared" si="57"/>
@@ -11743,43 +11713,43 @@
         <f t="shared" si="58"/>
         <v>5</v>
       </c>
-      <c r="O184" s="46" t="str">
+      <c r="O184" s="40" t="str">
         <f t="shared" si="59"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="185" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="42"/>
-      <c r="B185" s="42"/>
+      <c r="A185" s="51"/>
+      <c r="B185" s="51"/>
       <c r="C185" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D185" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E185" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F185" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G185" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H185" s="23">
         <v>5</v>
       </c>
       <c r="I185" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J185" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K185" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L185" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M185" s="25" t="str">
         <f t="shared" si="57"/>
@@ -11789,33 +11759,33 @@
         <f t="shared" si="58"/>
         <v>5</v>
       </c>
-      <c r="O185" s="46" t="str">
+      <c r="O185" s="40" t="str">
         <f t="shared" si="59"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="186" spans="1:17" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="40">
+      <c r="A186" s="50">
         <v>23</v>
       </c>
-      <c r="B186" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="C186" s="51" t="str">
+      <c r="B186" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="C186" s="46" t="str">
         <f>IF(O180:O186="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N183&gt;3, N185&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D186" s="52"/>
-      <c r="E186" s="52"/>
-      <c r="F186" s="52"/>
-      <c r="G186" s="52"/>
-      <c r="H186" s="52"/>
-      <c r="I186" s="52"/>
-      <c r="J186" s="52"/>
-      <c r="K186" s="52"/>
-      <c r="L186" s="52"/>
+      <c r="D186" s="47"/>
+      <c r="E186" s="47"/>
+      <c r="F186" s="47"/>
+      <c r="G186" s="47"/>
+      <c r="H186" s="47"/>
+      <c r="I186" s="47"/>
+      <c r="J186" s="47"/>
+      <c r="K186" s="47"/>
+      <c r="L186" s="47"/>
       <c r="N186" s="29">
         <f>AVERAGE(D183:L185)</f>
         <v>5</v>
@@ -11827,13 +11797,13 @@
       </c>
     </row>
     <row r="187" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="41"/>
-      <c r="B187" s="41"/>
+      <c r="A187" s="52"/>
+      <c r="B187" s="52"/>
       <c r="C187" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D187" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E187" s="23">
         <v>4</v>
@@ -11869,10 +11839,10 @@
       </c>
     </row>
     <row r="188" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="41"/>
-      <c r="B188" s="41"/>
+      <c r="A188" s="52"/>
+      <c r="B188" s="52"/>
       <c r="C188" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D188" s="23">
         <v>4</v>
@@ -11909,19 +11879,19 @@
         <f t="shared" si="61"/>
         <v>4</v>
       </c>
-      <c r="O188" s="46" t="str">
+      <c r="O188" s="40" t="str">
         <f>IF(OR(N188&lt;N187,AND(N188&lt;=3,N188&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="189" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="41"/>
-      <c r="B189" s="41"/>
+      <c r="A189" s="52"/>
+      <c r="B189" s="52"/>
       <c r="C189" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D189" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E189" s="23">
         <v>4</v>
@@ -11955,16 +11925,16 @@
         <f t="shared" si="61"/>
         <v>4</v>
       </c>
-      <c r="O189" s="46" t="str">
+      <c r="O189" s="40" t="str">
         <f t="shared" ref="O189:O193" si="62">IF(OR(N189&lt;N188,AND(N189&lt;=3,N189&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="190" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="41"/>
-      <c r="B190" s="41"/>
+      <c r="A190" s="52"/>
+      <c r="B190" s="52"/>
       <c r="C190" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D190" s="23">
         <v>4</v>
@@ -12001,16 +11971,16 @@
         <f t="shared" si="61"/>
         <v>4</v>
       </c>
-      <c r="O190" s="46" t="str">
+      <c r="O190" s="40" t="str">
         <f t="shared" si="62"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="191" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="41"/>
-      <c r="B191" s="41"/>
+      <c r="A191" s="52"/>
+      <c r="B191" s="52"/>
       <c r="C191" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D191" s="23">
         <v>4</v>
@@ -12047,47 +12017,47 @@
         <f t="shared" si="61"/>
         <v>4</v>
       </c>
-      <c r="O191" s="46" t="str">
+      <c r="O191" s="40" t="str">
         <f t="shared" si="62"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q191" s="48" t="str">
+      <c r="Q191" s="42" t="str">
         <f>IF(N188&lt;N187, "2-тоқсанда ынта төмендеді", IF(N189&lt;N188, "3-тоқсанда ынта төмендеді", IF(N190&lt;N189, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="192" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="41"/>
-      <c r="B192" s="41"/>
+      <c r="A192" s="52"/>
+      <c r="B192" s="52"/>
       <c r="C192" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D192" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E192" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F192" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G192" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H192" s="23">
         <v>4</v>
       </c>
       <c r="I192" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J192" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K192" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L192" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M192" s="25" t="str">
         <f t="shared" si="60"/>
@@ -12097,43 +12067,43 @@
         <f t="shared" si="61"/>
         <v>4</v>
       </c>
-      <c r="O192" s="46" t="str">
+      <c r="O192" s="40" t="str">
         <f t="shared" si="62"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="193" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="42"/>
-      <c r="B193" s="42"/>
+      <c r="A193" s="51"/>
+      <c r="B193" s="51"/>
       <c r="C193" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D193" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E193" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F193" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G193" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H193" s="23">
         <v>4</v>
       </c>
       <c r="I193" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J193" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K193" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L193" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M193" s="25" t="str">
         <f t="shared" si="60"/>
@@ -12143,33 +12113,33 @@
         <f t="shared" si="61"/>
         <v>4</v>
       </c>
-      <c r="O193" s="46" t="str">
+      <c r="O193" s="40" t="str">
         <f t="shared" si="62"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="194" spans="1:17" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="40">
+      <c r="A194" s="50">
         <v>24</v>
       </c>
-      <c r="B194" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="C194" s="51" t="str">
+      <c r="B194" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="C194" s="46" t="str">
         <f>IF(O188:O194="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N191&gt;3, N193&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D194" s="52"/>
-      <c r="E194" s="52"/>
-      <c r="F194" s="52"/>
-      <c r="G194" s="52"/>
-      <c r="H194" s="52"/>
-      <c r="I194" s="52"/>
-      <c r="J194" s="52"/>
-      <c r="K194" s="52"/>
-      <c r="L194" s="52"/>
+      <c r="D194" s="47"/>
+      <c r="E194" s="47"/>
+      <c r="F194" s="47"/>
+      <c r="G194" s="47"/>
+      <c r="H194" s="47"/>
+      <c r="I194" s="47"/>
+      <c r="J194" s="47"/>
+      <c r="K194" s="47"/>
+      <c r="L194" s="47"/>
       <c r="N194" s="29">
         <f>AVERAGE(D191:L193)</f>
         <v>4.0909090909090908</v>
@@ -12181,13 +12151,13 @@
       </c>
     </row>
     <row r="195" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="41"/>
-      <c r="B195" s="41"/>
+      <c r="A195" s="52"/>
+      <c r="B195" s="52"/>
       <c r="C195" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D195" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E195" s="23">
         <v>5</v>
@@ -12223,10 +12193,10 @@
       </c>
     </row>
     <row r="196" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="41"/>
-      <c r="B196" s="41"/>
+      <c r="A196" s="52"/>
+      <c r="B196" s="52"/>
       <c r="C196" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D196" s="23">
         <v>5</v>
@@ -12263,19 +12233,19 @@
         <f t="shared" si="64"/>
         <v>5</v>
       </c>
-      <c r="O196" s="46" t="str">
+      <c r="O196" s="40" t="str">
         <f>IF(OR(N196&lt;N195,AND(N196&lt;=3,N196&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="197" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="41"/>
-      <c r="B197" s="41"/>
+      <c r="A197" s="52"/>
+      <c r="B197" s="52"/>
       <c r="C197" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D197" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E197" s="23">
         <v>5</v>
@@ -12309,16 +12279,16 @@
         <f t="shared" si="64"/>
         <v>5</v>
       </c>
-      <c r="O197" s="46" t="str">
+      <c r="O197" s="40" t="str">
         <f t="shared" ref="O197:O201" si="65">IF(OR(N197&lt;N196,AND(N197&lt;=3,N197&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="198" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="41"/>
-      <c r="B198" s="41"/>
+      <c r="A198" s="52"/>
+      <c r="B198" s="52"/>
       <c r="C198" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D198" s="23">
         <v>5</v>
@@ -12355,16 +12325,16 @@
         <f t="shared" si="64"/>
         <v>4</v>
       </c>
-      <c r="O198" s="46" t="str">
+      <c r="O198" s="40" t="str">
         <f t="shared" si="65"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="199" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="41"/>
-      <c r="B199" s="41"/>
+      <c r="A199" s="52"/>
+      <c r="B199" s="52"/>
       <c r="C199" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D199" s="23">
         <v>5</v>
@@ -12401,47 +12371,47 @@
         <f t="shared" si="64"/>
         <v>5</v>
       </c>
-      <c r="O199" s="46" t="str">
+      <c r="O199" s="40" t="str">
         <f t="shared" si="65"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q199" s="48" t="str">
+      <c r="Q199" s="42" t="str">
         <f>IF(N196&lt;N195, "2-тоқсанда ынта төмендеді", IF(N197&lt;N196, "3-тоқсанда ынта төмендеді", IF(N198&lt;N197, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>4-тоқсанда ынта төмендеді</v>
       </c>
     </row>
     <row r="200" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="41"/>
-      <c r="B200" s="41"/>
+      <c r="A200" s="52"/>
+      <c r="B200" s="52"/>
       <c r="C200" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D200" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E200" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F200" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G200" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H200" s="23">
         <v>5</v>
       </c>
       <c r="I200" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J200" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K200" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L200" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M200" s="25" t="str">
         <f t="shared" si="63"/>
@@ -12451,43 +12421,43 @@
         <f t="shared" si="64"/>
         <v>5</v>
       </c>
-      <c r="O200" s="46" t="str">
+      <c r="O200" s="40" t="str">
         <f t="shared" si="65"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="201" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="42"/>
-      <c r="B201" s="42"/>
+      <c r="A201" s="51"/>
+      <c r="B201" s="51"/>
       <c r="C201" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D201" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E201" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F201" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G201" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H201" s="23">
         <v>5</v>
       </c>
       <c r="I201" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J201" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K201" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L201" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M201" s="25" t="str">
         <f t="shared" si="63"/>
@@ -12497,33 +12467,33 @@
         <f t="shared" si="64"/>
         <v>5</v>
       </c>
-      <c r="O201" s="46" t="str">
+      <c r="O201" s="40" t="str">
         <f t="shared" si="65"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="202" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="40">
+      <c r="A202" s="50">
         <v>25</v>
       </c>
-      <c r="B202" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="C202" s="51" t="str">
+      <c r="B202" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="C202" s="46" t="str">
         <f>IF(O196:O202="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N199&gt;3, N201&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D202" s="52"/>
-      <c r="E202" s="52"/>
-      <c r="F202" s="52"/>
-      <c r="G202" s="52"/>
-      <c r="H202" s="52"/>
-      <c r="I202" s="52"/>
-      <c r="J202" s="52"/>
-      <c r="K202" s="52"/>
-      <c r="L202" s="52"/>
+      <c r="D202" s="47"/>
+      <c r="E202" s="47"/>
+      <c r="F202" s="47"/>
+      <c r="G202" s="47"/>
+      <c r="H202" s="47"/>
+      <c r="I202" s="47"/>
+      <c r="J202" s="47"/>
+      <c r="K202" s="47"/>
+      <c r="L202" s="47"/>
       <c r="N202" s="29">
         <f>AVERAGE(D199:L201)</f>
         <v>5</v>
@@ -12535,13 +12505,13 @@
       </c>
     </row>
     <row r="203" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="41"/>
-      <c r="B203" s="41"/>
+      <c r="A203" s="52"/>
+      <c r="B203" s="52"/>
       <c r="C203" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D203" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E203" s="23">
         <v>4</v>
@@ -12577,10 +12547,10 @@
       </c>
     </row>
     <row r="204" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="41"/>
-      <c r="B204" s="41"/>
+      <c r="A204" s="52"/>
+      <c r="B204" s="52"/>
       <c r="C204" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D204" s="23">
         <v>4</v>
@@ -12617,19 +12587,19 @@
         <f t="shared" si="67"/>
         <v>4</v>
       </c>
-      <c r="O204" s="46" t="str">
+      <c r="O204" s="40" t="str">
         <f>IF(OR(N204&lt;N203,AND(N204&lt;=3,N204&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="205" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="41"/>
-      <c r="B205" s="41"/>
+      <c r="A205" s="52"/>
+      <c r="B205" s="52"/>
       <c r="C205" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D205" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E205" s="23">
         <v>5</v>
@@ -12663,16 +12633,16 @@
         <f t="shared" si="67"/>
         <v>4</v>
       </c>
-      <c r="O205" s="46" t="str">
+      <c r="O205" s="40" t="str">
         <f t="shared" ref="O205:O209" si="68">IF(OR(N205&lt;N204,AND(N205&lt;=3,N205&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="206" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="41"/>
-      <c r="B206" s="41"/>
+      <c r="A206" s="52"/>
+      <c r="B206" s="52"/>
       <c r="C206" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D206" s="23">
         <v>4</v>
@@ -12709,16 +12679,16 @@
         <f t="shared" si="67"/>
         <v>4</v>
       </c>
-      <c r="O206" s="46" t="str">
+      <c r="O206" s="40" t="str">
         <f t="shared" si="68"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="207" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="41"/>
-      <c r="B207" s="41"/>
+      <c r="A207" s="52"/>
+      <c r="B207" s="52"/>
       <c r="C207" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D207" s="23">
         <v>5</v>
@@ -12755,47 +12725,47 @@
         <f t="shared" si="67"/>
         <v>4</v>
       </c>
-      <c r="O207" s="46" t="str">
+      <c r="O207" s="40" t="str">
         <f t="shared" si="68"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q207" s="48" t="str">
+      <c r="Q207" s="42" t="str">
         <f>IF(N204&lt;N203, "2-тоқсанда ынта төмендеді", IF(N205&lt;N204, "3-тоқсанда ынта төмендеді", IF(N206&lt;N205, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>Төмендеу жоқ</v>
       </c>
     </row>
     <row r="208" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="41"/>
-      <c r="B208" s="41"/>
+      <c r="A208" s="52"/>
+      <c r="B208" s="52"/>
       <c r="C208" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D208" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E208" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F208" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G208" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H208" s="23">
         <v>4</v>
       </c>
       <c r="I208" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J208" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K208" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L208" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M208" s="25" t="str">
         <f t="shared" si="66"/>
@@ -12805,43 +12775,43 @@
         <f t="shared" si="67"/>
         <v>4</v>
       </c>
-      <c r="O208" s="46" t="str">
+      <c r="O208" s="40" t="str">
         <f t="shared" si="68"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="209" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="42"/>
-      <c r="B209" s="41"/>
+      <c r="A209" s="51"/>
+      <c r="B209" s="52"/>
       <c r="C209" s="35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D209" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E209" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F209" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G209" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H209" s="20">
         <v>4</v>
       </c>
       <c r="I209" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J209" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K209" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L209" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M209" s="25" t="str">
         <f t="shared" si="66"/>
@@ -12851,7 +12821,7 @@
         <f t="shared" si="67"/>
         <v>4</v>
       </c>
-      <c r="O209" s="46" t="str">
+      <c r="O209" s="40" t="str">
         <f t="shared" si="68"/>
         <v>Ынта тұрақты</v>
       </c>
@@ -12875,24 +12845,24 @@
       <c r="A211" s="31">
         <v>26</v>
       </c>
-      <c r="B211" s="41" t="s">
-        <v>147</v>
-      </c>
-      <c r="C211" s="51" t="str">
+      <c r="B211" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="C211" s="46" t="str">
         <f>IF(O205:O211="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N208&gt;3, N210&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D211" s="52"/>
-      <c r="E211" s="52"/>
-      <c r="F211" s="52"/>
-      <c r="G211" s="52"/>
-      <c r="H211" s="52"/>
-      <c r="I211" s="52"/>
-      <c r="J211" s="52"/>
-      <c r="K211" s="52"/>
-      <c r="L211" s="52"/>
+      <c r="D211" s="47"/>
+      <c r="E211" s="47"/>
+      <c r="F211" s="47"/>
+      <c r="G211" s="47"/>
+      <c r="H211" s="47"/>
+      <c r="I211" s="47"/>
+      <c r="J211" s="47"/>
+      <c r="K211" s="47"/>
+      <c r="L211" s="47"/>
       <c r="N211" s="29">
         <f>AVERAGE(D207:L209)</f>
         <v>4.1818181818181817</v>
@@ -12905,9 +12875,9 @@
     </row>
     <row r="212" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="32"/>
-      <c r="B212" s="41"/>
+      <c r="B212" s="52"/>
       <c r="C212" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D212" s="23">
         <v>5</v>
@@ -12947,9 +12917,9 @@
     </row>
     <row r="213" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="32"/>
-      <c r="B213" s="41"/>
+      <c r="B213" s="52"/>
       <c r="C213" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D213" s="23">
         <v>5</v>
@@ -12986,17 +12956,17 @@
         <f>IF(MIN(D213:L213)=5, "5", IF(MIN(D213:L213)&gt;=4, "4", IF(MIN(D213:L213)=3, "3")))</f>
         <v>3</v>
       </c>
-      <c r="O213" s="46" t="str">
+      <c r="O213" s="40" t="str">
         <f>IF(OR(N213&lt;N212,AND(N213&lt;=3,N213&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта төмендеді</v>
       </c>
-      <c r="Q213" s="49"/>
+      <c r="Q213" s="43"/>
     </row>
     <row r="214" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="32"/>
-      <c r="B214" s="41"/>
+      <c r="B214" s="52"/>
       <c r="C214" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D214" s="23">
         <v>5</v>
@@ -13033,17 +13003,17 @@
         <f>IF(MIN(D214:L214)=5, "5", IF(MIN(D214:L214)&gt;=4, "4", IF(MIN(D214:L214)=3, "3")))</f>
         <v>3</v>
       </c>
-      <c r="O214" s="46" t="str">
+      <c r="O214" s="40" t="str">
         <f t="shared" ref="O214:O218" si="69">IF(OR(N214&lt;N213,AND(N214&lt;=3,N214&lt;=3)),"Ынта төмендеді","Ынта тұрақты")</f>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q214" s="49"/>
+      <c r="Q214" s="43"/>
     </row>
     <row r="215" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="32"/>
-      <c r="B215" s="41"/>
+      <c r="B215" s="52"/>
       <c r="C215" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D215" s="23">
         <v>5</v>
@@ -13080,16 +13050,16 @@
         <f>IF(MIN(D215:L215)=5, "5", IF(MIN(D215:L215)&gt;=4, "4", IF(MIN(D215:L215)=3, "3")))</f>
         <v>3</v>
       </c>
-      <c r="O215" s="46" t="str">
+      <c r="O215" s="40" t="str">
         <f t="shared" si="69"/>
         <v>Ынта тұрақты</v>
       </c>
     </row>
     <row r="216" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="32"/>
-      <c r="B216" s="41"/>
+      <c r="B216" s="52"/>
       <c r="C216" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D216" s="23">
         <v>5</v>
@@ -13126,107 +13096,107 @@
         <f>IF(MIN(D216:L216)=5, "5", IF(MIN(D216:L216)&gt;=4, "4", IF(MIN(D216:L216)=3, "3")))</f>
         <v>3</v>
       </c>
-      <c r="O216" s="46" t="str">
+      <c r="O216" s="40" t="str">
         <f t="shared" si="69"/>
         <v>Ынта тұрақты</v>
       </c>
-      <c r="Q216" s="48" t="str">
+      <c r="Q216" s="42" t="str">
         <f>IF(N213&lt;N212, "2-тоқсанда ынта төмендеді", IF(N214&lt;N213, "3-тоқсанда ынта төмендеді", IF(N215&lt;N214, "4-тоқсанда ынта төмендеді", "Төмендеу жоқ")))</f>
         <v>2-тоқсанда ынта төмендеді</v>
       </c>
     </row>
     <row r="217" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="32"/>
-      <c r="B217" s="41"/>
+      <c r="B217" s="52"/>
       <c r="C217" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D217" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E217" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F217" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G217" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H217" s="23">
         <v>5</v>
       </c>
       <c r="I217" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J217" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K217" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L217" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="O217" s="46" t="str">
+        <v>115</v>
+      </c>
+      <c r="O217" s="40" t="str">
         <f t="shared" si="69"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="218" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="33"/>
-      <c r="B218" s="42"/>
+      <c r="B218" s="51"/>
       <c r="C218" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D218" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E218" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F218" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G218" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H218" s="23">
         <v>5</v>
       </c>
       <c r="I218" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J218" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K218" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L218" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="O218" s="46" t="str">
+        <v>115</v>
+      </c>
+      <c r="O218" s="40" t="str">
         <f t="shared" si="69"/>
         <v>Ынта төмендеді</v>
       </c>
     </row>
     <row r="219" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C219" s="51" t="str">
+      <c r="C219" s="46" t="str">
         <f>IF(O213:O219="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N216&gt;3, N218&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D219" s="52"/>
-      <c r="E219" s="52"/>
-      <c r="F219" s="52"/>
-      <c r="G219" s="52"/>
-      <c r="H219" s="52"/>
-      <c r="I219" s="52"/>
-      <c r="J219" s="52"/>
-      <c r="K219" s="52"/>
-      <c r="L219" s="52"/>
+      <c r="D219" s="47"/>
+      <c r="E219" s="47"/>
+      <c r="F219" s="47"/>
+      <c r="G219" s="47"/>
+      <c r="H219" s="47"/>
+      <c r="I219" s="47"/>
+      <c r="J219" s="47"/>
+      <c r="K219" s="47"/>
+      <c r="L219" s="47"/>
       <c r="N219" s="29">
         <f>SUM(N216)</f>
         <v>0</v>
@@ -13239,7 +13209,7 @@
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.35">
       <c r="N220" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P220" s="25">
         <v>2</v>
@@ -13247,7 +13217,7 @@
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.35">
       <c r="N221" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P221" s="4">
         <f>COUNTIF(P18:P220, "&gt;3")</f>
@@ -13256,10 +13226,10 @@
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A222" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N222" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P222" s="26">
         <f>SUM(P221/A211*100)</f>
@@ -13268,7 +13238,7 @@
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.35">
       <c r="N223" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P223" s="26">
         <v>100</v>
@@ -13276,7 +13246,7 @@
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A224" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.35">
@@ -13284,33 +13254,57 @@
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="C211:L211"/>
-    <mergeCell ref="C219:L219"/>
-    <mergeCell ref="C170:L170"/>
-    <mergeCell ref="C178:L178"/>
-    <mergeCell ref="C186:L186"/>
-    <mergeCell ref="C194:L194"/>
-    <mergeCell ref="C202:L202"/>
-    <mergeCell ref="C130:L130"/>
-    <mergeCell ref="C138:L138"/>
-    <mergeCell ref="C146:L146"/>
-    <mergeCell ref="C154:L154"/>
-    <mergeCell ref="C162:L162"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C106:L106"/>
-    <mergeCell ref="C114:L114"/>
-    <mergeCell ref="C122:L122"/>
-    <mergeCell ref="C50:L50"/>
-    <mergeCell ref="C58:L58"/>
-    <mergeCell ref="C66:L66"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C82:L82"/>
-    <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C10:L10"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="C34:L34"/>
-    <mergeCell ref="C42:L42"/>
+    <mergeCell ref="A202:A209"/>
+    <mergeCell ref="B202:B209"/>
+    <mergeCell ref="B211:B218"/>
+    <mergeCell ref="A178:A185"/>
+    <mergeCell ref="B178:B185"/>
+    <mergeCell ref="A186:A193"/>
+    <mergeCell ref="B186:B193"/>
+    <mergeCell ref="A194:A201"/>
+    <mergeCell ref="B194:B201"/>
+    <mergeCell ref="A154:A161"/>
+    <mergeCell ref="B154:B161"/>
+    <mergeCell ref="A162:A169"/>
+    <mergeCell ref="B162:B169"/>
+    <mergeCell ref="A170:A177"/>
+    <mergeCell ref="B170:B177"/>
+    <mergeCell ref="A130:A137"/>
+    <mergeCell ref="B130:B137"/>
+    <mergeCell ref="A138:A145"/>
+    <mergeCell ref="B138:B145"/>
+    <mergeCell ref="A146:A153"/>
+    <mergeCell ref="B146:B153"/>
+    <mergeCell ref="A106:A113"/>
+    <mergeCell ref="B106:B113"/>
+    <mergeCell ref="A114:A121"/>
+    <mergeCell ref="B114:B121"/>
+    <mergeCell ref="A122:A129"/>
+    <mergeCell ref="B122:B129"/>
+    <mergeCell ref="A82:A89"/>
+    <mergeCell ref="B82:B89"/>
+    <mergeCell ref="A90:A97"/>
+    <mergeCell ref="B90:B97"/>
+    <mergeCell ref="A98:A105"/>
+    <mergeCell ref="B98:B105"/>
+    <mergeCell ref="A58:A65"/>
+    <mergeCell ref="B58:B65"/>
+    <mergeCell ref="A66:A73"/>
+    <mergeCell ref="B66:B73"/>
+    <mergeCell ref="A74:A81"/>
+    <mergeCell ref="B74:B81"/>
+    <mergeCell ref="A34:A41"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="A42:A49"/>
+    <mergeCell ref="B42:B49"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="B50:B57"/>
+    <mergeCell ref="A10:A17"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="A18:A25"/>
+    <mergeCell ref="B18:B25"/>
+    <mergeCell ref="A26:A33"/>
+    <mergeCell ref="B26:B33"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="H8:H9"/>
     <mergeCell ref="J8:J9"/>
@@ -13320,57 +13314,33 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A10:A17"/>
-    <mergeCell ref="B10:B17"/>
-    <mergeCell ref="A18:A25"/>
-    <mergeCell ref="B18:B25"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="A34:A41"/>
-    <mergeCell ref="B34:B41"/>
-    <mergeCell ref="A42:A49"/>
-    <mergeCell ref="B42:B49"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="B50:B57"/>
-    <mergeCell ref="A58:A65"/>
-    <mergeCell ref="B58:B65"/>
-    <mergeCell ref="A66:A73"/>
-    <mergeCell ref="B66:B73"/>
-    <mergeCell ref="A74:A81"/>
-    <mergeCell ref="B74:B81"/>
-    <mergeCell ref="A82:A89"/>
-    <mergeCell ref="B82:B89"/>
-    <mergeCell ref="A90:A97"/>
-    <mergeCell ref="B90:B97"/>
-    <mergeCell ref="A98:A105"/>
-    <mergeCell ref="B98:B105"/>
-    <mergeCell ref="A106:A113"/>
-    <mergeCell ref="B106:B113"/>
-    <mergeCell ref="A114:A121"/>
-    <mergeCell ref="B114:B121"/>
-    <mergeCell ref="A122:A129"/>
-    <mergeCell ref="B122:B129"/>
-    <mergeCell ref="A130:A137"/>
-    <mergeCell ref="B130:B137"/>
-    <mergeCell ref="A138:A145"/>
-    <mergeCell ref="B138:B145"/>
-    <mergeCell ref="A146:A153"/>
-    <mergeCell ref="B146:B153"/>
-    <mergeCell ref="A154:A161"/>
-    <mergeCell ref="B154:B161"/>
-    <mergeCell ref="A162:A169"/>
-    <mergeCell ref="B162:B169"/>
-    <mergeCell ref="A170:A177"/>
-    <mergeCell ref="B170:B177"/>
-    <mergeCell ref="A202:A209"/>
-    <mergeCell ref="B202:B209"/>
-    <mergeCell ref="B211:B218"/>
-    <mergeCell ref="A178:A185"/>
-    <mergeCell ref="B178:B185"/>
-    <mergeCell ref="A186:A193"/>
-    <mergeCell ref="B186:B193"/>
-    <mergeCell ref="A194:A201"/>
-    <mergeCell ref="B194:B201"/>
+    <mergeCell ref="C18:L18"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C42:L42"/>
+    <mergeCell ref="C50:L50"/>
+    <mergeCell ref="C58:L58"/>
+    <mergeCell ref="C66:L66"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C106:L106"/>
+    <mergeCell ref="C114:L114"/>
+    <mergeCell ref="C122:L122"/>
+    <mergeCell ref="C130:L130"/>
+    <mergeCell ref="C138:L138"/>
+    <mergeCell ref="C146:L146"/>
+    <mergeCell ref="C154:L154"/>
+    <mergeCell ref="C162:L162"/>
+    <mergeCell ref="C211:L211"/>
+    <mergeCell ref="C219:L219"/>
+    <mergeCell ref="C170:L170"/>
+    <mergeCell ref="C178:L178"/>
+    <mergeCell ref="C186:L186"/>
+    <mergeCell ref="C194:L194"/>
+    <mergeCell ref="C202:L202"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/reiting.xlsx
+++ b/reiting.xlsx
@@ -963,7 +963,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1099,28 +1099,6 @@
       <alignment horizontal="left" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1139,6 +1117,32 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1555,43 +1559,43 @@
       <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45" t="s">
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45" t="s">
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45" t="s">
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="45"/>
-      <c r="V3" s="45"/>
-      <c r="W3" s="45"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45" t="s">
+      <c r="U3" s="54"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="54"/>
+      <c r="X3" s="54"/>
+      <c r="Y3" s="54"/>
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
+      <c r="AB3" s="54"/>
+      <c r="AC3" s="54"/>
+      <c r="AD3" s="54"/>
+      <c r="AE3" s="54"/>
     </row>
     <row r="4" spans="1:32" s="2" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
@@ -2631,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD38"/>
+  <dimension ref="A1:AD40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -2735,163 +2739,101 @@
       </c>
       <c r="AD1" s="3"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
-        <v>1</v>
-      </c>
-      <c r="B2" s="53" t="s">
-        <v>153</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="60">
-        <v>0.9</v>
-      </c>
-      <c r="E2" s="11">
-        <v>1</v>
-      </c>
-      <c r="F2" s="11">
-        <v>2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>3</v>
-      </c>
-      <c r="H2" s="11">
-        <v>5</v>
-      </c>
-      <c r="I2" s="11">
-        <v>5</v>
-      </c>
-      <c r="J2" s="12">
-        <f>SUM(E2+F2+G2+H2+I2)</f>
-        <v>16</v>
-      </c>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="13">
-        <f>SUM(K2+L2+M2+N2+O2+P2+Q2)</f>
-        <v>0</v>
-      </c>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="14">
-        <f>SUM(S2+T2+U2+V2+W2+X2)</f>
-        <v>0</v>
-      </c>
-      <c r="Z2" s="12">
-        <f t="shared" ref="Z2:Z14" si="0">SUM(J2)</f>
-        <v>16</v>
-      </c>
-      <c r="AA2" s="13">
-        <f t="shared" ref="AA2:AA14" si="1">SUM(R2)</f>
-        <v>0</v>
-      </c>
-      <c r="AB2" s="14">
-        <f t="shared" ref="AB2:AB14" si="2">SUM(Y2)</f>
-        <v>0</v>
-      </c>
-      <c r="AC2" s="16">
-        <f>SUM(J2+R2+Y2)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
-        <v>2</v>
-      </c>
-      <c r="B3" s="53" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="60">
-        <v>0.9</v>
-      </c>
-      <c r="E3" s="11">
-        <v>4.5</v>
-      </c>
-      <c r="F3" s="11">
-        <v>8</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J14" si="3">SUM(E3+F3+G3+H3+I3)</f>
-        <v>12.5</v>
-      </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="13">
-        <f t="shared" ref="R3:R14" si="4">SUM(K3+L3+M3+N3+O3+P3+Q3)</f>
-        <v>0</v>
-      </c>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="14">
-        <f t="shared" ref="Y3:Y14" si="5">SUM(S3+T3+U3+V3+W3+X3)</f>
-        <v>0</v>
-      </c>
-      <c r="Z3" s="12">
-        <f t="shared" si="0"/>
-        <v>12.5</v>
-      </c>
-      <c r="AA3" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB3" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC3" s="16">
-        <f t="shared" ref="AC3:AC14" si="6">SUM(J3+R3+Y3)</f>
-        <v>12.5</v>
-      </c>
+    <row r="2" spans="1:30" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="3"/>
+    </row>
+    <row r="3" spans="1:30" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="3"/>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
+        <v>1</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="52">
+        <v>0.9</v>
+      </c>
+      <c r="E4" s="11">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11">
+        <v>2</v>
+      </c>
+      <c r="G4" s="11">
         <v>3</v>
       </c>
-      <c r="B4" s="53" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="60">
-        <v>0.1</v>
-      </c>
-      <c r="E4" s="11">
-        <v>4.7</v>
-      </c>
-      <c r="F4" s="11">
-        <v>9</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
+      <c r="H4" s="11">
+        <v>5</v>
+      </c>
+      <c r="I4" s="11">
+        <v>5</v>
+      </c>
       <c r="J4" s="12">
-        <f t="shared" si="3"/>
-        <v>13.7</v>
+        <f>SUM(E4+F4+G4+H4+I4)</f>
+        <v>16</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
@@ -2901,7 +2843,7 @@
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
       <c r="R4" s="13">
-        <f t="shared" si="4"/>
+        <f>SUM(K4+L4+M4+N4+O4+P4+Q4)</f>
         <v>0</v>
       </c>
       <c r="S4" s="11"/>
@@ -2911,51 +2853,51 @@
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
       <c r="Y4" s="14">
-        <f t="shared" si="5"/>
+        <f>SUM(S4+T4+U4+V4+W4+X4)</f>
         <v>0</v>
       </c>
       <c r="Z4" s="12">
-        <f t="shared" si="0"/>
-        <v>13.7</v>
+        <f t="shared" ref="Z4:Z16" si="0">SUM(J4)</f>
+        <v>16</v>
       </c>
       <c r="AA4" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="AA4:AA16" si="1">SUM(R4)</f>
         <v>0</v>
       </c>
       <c r="AB4" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AB4:AB16" si="2">SUM(Y4)</f>
         <v>0</v>
       </c>
       <c r="AC4" s="16">
-        <f t="shared" si="6"/>
-        <v>13.7</v>
+        <f>SUM(J4+R4+Y4)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>4</v>
-      </c>
-      <c r="B5" s="53" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="60">
-        <v>0.3</v>
+        <v>2</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="52">
+        <v>0.9</v>
       </c>
       <c r="E5" s="11">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="F5" s="11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="12">
-        <f t="shared" si="3"/>
-        <v>9.8000000000000007</v>
+        <f t="shared" ref="J5:J16" si="3">SUM(E5+F5+G5+H5+I5)</f>
+        <v>12.5</v>
       </c>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
@@ -2965,7 +2907,7 @@
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
       <c r="R5" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="R5:R16" si="4">SUM(K5+L5+M5+N5+O5+P5+Q5)</f>
         <v>0</v>
       </c>
       <c r="S5" s="11"/>
@@ -2975,12 +2917,12 @@
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="Y5:Y16" si="5">SUM(S5+T5+U5+V5+W5+X5)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="12">
         <f t="shared" si="0"/>
-        <v>9.8000000000000007</v>
+        <v>12.5</v>
       </c>
       <c r="AA5" s="13">
         <f t="shared" si="1"/>
@@ -2991,35 +2933,33 @@
         <v>0</v>
       </c>
       <c r="AC5" s="16">
-        <f t="shared" si="6"/>
-        <v>9.8000000000000007</v>
+        <f t="shared" ref="AC5:AC16" si="6">SUM(J5+R5+Y5)</f>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>5</v>
-      </c>
-      <c r="B6" s="55" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="60">
-        <v>0.9</v>
+        <v>3</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="46"/>
+      <c r="D6" s="52">
+        <v>0.1</v>
       </c>
       <c r="E6" s="11">
         <v>4.7</v>
       </c>
       <c r="F6" s="11">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="12">
         <f t="shared" si="3"/>
-        <v>7.7</v>
+        <v>13.7</v>
       </c>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -3044,7 +2984,7 @@
       </c>
       <c r="Z6" s="12">
         <f t="shared" si="0"/>
-        <v>7.7</v>
+        <v>13.7</v>
       </c>
       <c r="AA6" s="13">
         <f t="shared" si="1"/>
@@ -3056,34 +2996,34 @@
       </c>
       <c r="AC6" s="16">
         <f t="shared" si="6"/>
-        <v>7.7</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>6</v>
-      </c>
-      <c r="B7" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="60">
-        <v>0.7</v>
+        <v>4</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="52">
+        <v>0.3</v>
       </c>
       <c r="E7" s="11">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F7" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="12">
         <f t="shared" si="3"/>
-        <v>8.6999999999999993</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -3108,7 +3048,7 @@
       </c>
       <c r="Z7" s="12">
         <f t="shared" si="0"/>
-        <v>8.6999999999999993</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="AA7" s="13">
         <f t="shared" si="1"/>
@@ -3120,34 +3060,34 @@
       </c>
       <c r="AC7" s="16">
         <f t="shared" si="6"/>
-        <v>8.6999999999999993</v>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>7</v>
-      </c>
-      <c r="B8" s="55" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="60">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="52">
+        <v>0.9</v>
       </c>
       <c r="E8" s="11">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="F8" s="11">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="12">
         <f t="shared" si="3"/>
-        <v>11.6</v>
+        <v>7.7</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -3172,7 +3112,7 @@
       </c>
       <c r="Z8" s="12">
         <f t="shared" si="0"/>
-        <v>11.6</v>
+        <v>7.7</v>
       </c>
       <c r="AA8" s="13">
         <f t="shared" si="1"/>
@@ -3184,34 +3124,34 @@
       </c>
       <c r="AC8" s="16">
         <f t="shared" si="6"/>
-        <v>11.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>8</v>
-      </c>
-      <c r="B9" s="53" t="s">
-        <v>160</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="60">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="52">
+        <v>0.7</v>
       </c>
       <c r="E9" s="11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F9" s="11">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="12">
         <f t="shared" si="3"/>
-        <v>14.5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -3236,7 +3176,7 @@
       </c>
       <c r="Z9" s="12">
         <f t="shared" si="0"/>
-        <v>14.5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AA9" s="13">
         <f t="shared" si="1"/>
@@ -3248,34 +3188,34 @@
       </c>
       <c r="AC9" s="16">
         <f t="shared" si="6"/>
-        <v>14.5</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>9</v>
-      </c>
-      <c r="B10" s="53" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" s="54" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="60">
-        <v>1.2</v>
+        <v>7</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="52">
+        <v>1</v>
       </c>
       <c r="E10" s="11">
-        <v>4.0999999999999996</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F10" s="11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="12">
         <f t="shared" si="3"/>
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
@@ -3300,7 +3240,7 @@
       </c>
       <c r="Z10" s="12">
         <f t="shared" si="0"/>
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="AA10" s="13">
         <f t="shared" si="1"/>
@@ -3312,34 +3252,34 @@
       </c>
       <c r="AC10" s="16">
         <f t="shared" si="6"/>
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
+        <v>8</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="52">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="F11" s="11">
         <v>10</v>
-      </c>
-      <c r="B11" s="56" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" s="54" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="60">
-        <v>0.8</v>
-      </c>
-      <c r="E11" s="11">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F11" s="11">
-        <v>11</v>
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="J11" s="12">
         <f t="shared" si="3"/>
-        <v>15.9</v>
+        <v>14.5</v>
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
@@ -3364,7 +3304,7 @@
       </c>
       <c r="Z11" s="12">
         <f t="shared" si="0"/>
-        <v>15.9</v>
+        <v>14.5</v>
       </c>
       <c r="AA11" s="13">
         <f t="shared" si="1"/>
@@ -3376,34 +3316,34 @@
       </c>
       <c r="AC11" s="16">
         <f t="shared" si="6"/>
-        <v>15.9</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>11</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>163</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="60">
-        <v>0.9</v>
+        <v>9</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="52">
+        <v>1.2</v>
       </c>
       <c r="E12" s="11">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F12" s="11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="12">
         <f t="shared" si="3"/>
-        <v>7.3</v>
+        <v>12.1</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -3428,7 +3368,7 @@
       </c>
       <c r="Z12" s="12">
         <f t="shared" si="0"/>
-        <v>7.3</v>
+        <v>12.1</v>
       </c>
       <c r="AA12" s="13">
         <f t="shared" si="1"/>
@@ -3440,34 +3380,34 @@
       </c>
       <c r="AC12" s="16">
         <f t="shared" si="6"/>
-        <v>7.3</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>12</v>
-      </c>
-      <c r="B13" s="55" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="54" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="60">
-        <v>0.9</v>
+        <v>10</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="52">
+        <v>0.8</v>
       </c>
       <c r="E13" s="11">
-        <v>4.4000000000000004</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F13" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="12">
         <f t="shared" si="3"/>
-        <v>14.4</v>
+        <v>15.9</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -3492,7 +3432,7 @@
       </c>
       <c r="Z13" s="12">
         <f t="shared" si="0"/>
-        <v>14.4</v>
+        <v>15.9</v>
       </c>
       <c r="AA13" s="13">
         <f t="shared" si="1"/>
@@ -3504,34 +3444,34 @@
       </c>
       <c r="AC13" s="16">
         <f t="shared" si="6"/>
-        <v>14.4</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>13</v>
-      </c>
-      <c r="B14" s="55" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="60">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="52">
+        <v>0.9</v>
       </c>
       <c r="E14" s="11">
         <v>4.3</v>
       </c>
       <c r="F14" s="11">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="12">
         <f t="shared" si="3"/>
-        <v>12.3</v>
+        <v>7.3</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
@@ -3556,7 +3496,7 @@
       </c>
       <c r="Z14" s="12">
         <f t="shared" si="0"/>
-        <v>12.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA14" s="13">
         <f t="shared" si="1"/>
@@ -3568,34 +3508,34 @@
       </c>
       <c r="AC14" s="16">
         <f t="shared" si="6"/>
-        <v>12.3</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>14</v>
-      </c>
-      <c r="B15" s="55" t="s">
-        <v>166</v>
-      </c>
-      <c r="C15" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="61">
-        <v>0.3</v>
+        <v>12</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="52">
+        <v>0.9</v>
       </c>
       <c r="E15" s="11">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F15" s="11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="12">
-        <f t="shared" ref="J15:J38" si="7">SUM(E15+F15+G15+H15+I15)</f>
-        <v>12.3</v>
+        <f t="shared" si="3"/>
+        <v>14.4</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -3605,7 +3545,7 @@
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:R38" si="8">SUM(K15+L15+M15+N15+O15+P15+Q15)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S15" s="11"/>
@@ -3615,38 +3555,38 @@
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
       <c r="Y15" s="14">
-        <f t="shared" ref="Y15:Y38" si="9">SUM(S15+T15+U15+V15+W15+X15)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z15" s="12">
-        <f t="shared" ref="Z15:Z38" si="10">SUM(J15)</f>
-        <v>12.3</v>
+        <f t="shared" si="0"/>
+        <v>14.4</v>
       </c>
       <c r="AA15" s="13">
-        <f t="shared" ref="AA15:AA38" si="11">SUM(R15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB15" s="14">
-        <f t="shared" ref="AB15:AB38" si="12">SUM(Y15)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC15" s="16">
-        <f t="shared" ref="AC15:AC38" si="13">SUM(J15+R15+Y15)</f>
-        <v>12.3</v>
+        <f t="shared" si="6"/>
+        <v>14.4</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>15</v>
-      </c>
-      <c r="B16" s="58" t="s">
-        <v>167</v>
-      </c>
-      <c r="C16" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="61">
-        <v>0.7</v>
+        <v>13</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="52">
+        <v>1</v>
       </c>
       <c r="E16" s="11">
         <v>4.3</v>
@@ -3658,7 +3598,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>12.3</v>
       </c>
       <c r="K16" s="11"/>
@@ -3669,7 +3609,7 @@
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
       <c r="R16" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S16" s="11"/>
@@ -3679,38 +3619,38 @@
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
       <c r="Y16" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z16" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="0"/>
         <v>12.3</v>
       </c>
       <c r="AA16" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB16" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC16" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>12.3</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>16</v>
-      </c>
-      <c r="B17" s="55" t="s">
-        <v>168</v>
-      </c>
-      <c r="C17" s="54" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="61">
-        <v>0.8</v>
+        <v>14</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="53">
+        <v>0.3</v>
       </c>
       <c r="E17" s="11">
         <v>4.3</v>
@@ -3722,7 +3662,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J17:J40" si="7">SUM(E17+F17+G17+H17+I17)</f>
         <v>12.3</v>
       </c>
       <c r="K17" s="11"/>
@@ -3733,7 +3673,7 @@
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
       <c r="R17" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="R17:R40" si="8">SUM(K17+L17+M17+N17+O17+P17+Q17)</f>
         <v>0</v>
       </c>
       <c r="S17" s="11"/>
@@ -3743,38 +3683,38 @@
       <c r="W17" s="11"/>
       <c r="X17" s="11"/>
       <c r="Y17" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="Y17:Y40" si="9">SUM(S17+T17+U17+V17+W17+X17)</f>
         <v>0</v>
       </c>
       <c r="Z17" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="Z17:Z40" si="10">SUM(J17)</f>
         <v>12.3</v>
       </c>
       <c r="AA17" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="AA17:AA40" si="11">SUM(R17)</f>
         <v>0</v>
       </c>
       <c r="AB17" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="AB17:AB40" si="12">SUM(Y17)</f>
         <v>0</v>
       </c>
       <c r="AC17" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="AC17:AC40" si="13">SUM(J17+R17+Y17)</f>
         <v>12.3</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>17</v>
-      </c>
-      <c r="B18" s="53" t="s">
-        <v>169</v>
-      </c>
-      <c r="C18" s="59" t="s">
-        <v>170</v>
-      </c>
-      <c r="D18" s="61">
-        <v>0.1</v>
+        <v>15</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="53">
+        <v>0.7</v>
       </c>
       <c r="E18" s="11">
         <v>4.3</v>
@@ -3829,16 +3769,16 @@
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>18</v>
-      </c>
-      <c r="B19" s="53" t="s">
-        <v>171</v>
-      </c>
-      <c r="C19" s="59" t="s">
-        <v>172</v>
-      </c>
-      <c r="D19" s="61">
-        <v>0.1</v>
+        <v>16</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="53">
+        <v>0.8</v>
       </c>
       <c r="E19" s="11">
         <v>4.3</v>
@@ -3893,16 +3833,16 @@
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>19</v>
-      </c>
-      <c r="B20" s="55" t="s">
-        <v>173</v>
-      </c>
-      <c r="C20" s="54" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="61">
-        <v>0.8</v>
+        <v>17</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="53">
+        <v>0.1</v>
       </c>
       <c r="E20" s="11">
         <v>4.3</v>
@@ -3957,16 +3897,16 @@
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>20</v>
-      </c>
-      <c r="B21" s="57" t="s">
-        <v>174</v>
-      </c>
-      <c r="C21" s="59" t="s">
-        <v>175</v>
-      </c>
-      <c r="D21" s="61">
-        <v>0.3</v>
+        <v>18</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" s="53">
+        <v>0.1</v>
       </c>
       <c r="E21" s="11">
         <v>4.3</v>
@@ -4021,16 +3961,16 @@
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>21</v>
-      </c>
-      <c r="B22" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="C22" s="59" t="s">
-        <v>175</v>
-      </c>
-      <c r="D22" s="61">
-        <v>0.3</v>
+        <v>19</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="53">
+        <v>0.8</v>
       </c>
       <c r="E22" s="11">
         <v>4.3</v>
@@ -4085,16 +4025,16 @@
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>22</v>
-      </c>
-      <c r="B23" s="53" t="s">
-        <v>177</v>
-      </c>
-      <c r="C23" s="54" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="61">
-        <v>0.9</v>
+        <v>20</v>
+      </c>
+      <c r="B23" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="D23" s="53">
+        <v>0.3</v>
       </c>
       <c r="E23" s="11">
         <v>4.3</v>
@@ -4149,16 +4089,16 @@
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>23</v>
-      </c>
-      <c r="B24" s="55" t="s">
-        <v>178</v>
-      </c>
-      <c r="C24" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="61">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" s="53">
+        <v>0.3</v>
       </c>
       <c r="E24" s="11">
         <v>4.3</v>
@@ -4213,15 +4153,15 @@
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>24</v>
-      </c>
-      <c r="B25" s="55" t="s">
-        <v>179</v>
-      </c>
-      <c r="C25" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="61">
+        <v>22</v>
+      </c>
+      <c r="B25" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="53">
         <v>0.9</v>
       </c>
       <c r="E25" s="11">
@@ -4277,16 +4217,16 @@
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>25</v>
-      </c>
-      <c r="B26" s="53" t="s">
-        <v>180</v>
-      </c>
-      <c r="C26" s="54" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="61">
-        <v>1.2</v>
+        <v>23</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="53">
+        <v>1</v>
       </c>
       <c r="E26" s="11">
         <v>4.3</v>
@@ -4341,16 +4281,16 @@
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>26</v>
-      </c>
-      <c r="B27" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="C27" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="61">
-        <v>0.7</v>
+        <v>24</v>
+      </c>
+      <c r="B27" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="53">
+        <v>0.9</v>
       </c>
       <c r="E27" s="11">
         <v>4.3</v>
@@ -4405,15 +4345,15 @@
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>27</v>
-      </c>
-      <c r="B28" s="53" t="s">
-        <v>182</v>
-      </c>
-      <c r="C28" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="D28" s="61">
+        <v>25</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="53">
         <v>1.2</v>
       </c>
       <c r="E28" s="11">
@@ -4469,16 +4409,16 @@
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>28</v>
-      </c>
-      <c r="B29" s="53" t="s">
-        <v>184</v>
-      </c>
-      <c r="C29" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="61">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="53">
+        <v>0.7</v>
       </c>
       <c r="E29" s="11">
         <v>4.3</v>
@@ -4533,16 +4473,16 @@
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>29</v>
-      </c>
-      <c r="B30" s="53" t="s">
-        <v>185</v>
-      </c>
-      <c r="C30" s="54" t="s">
-        <v>186</v>
-      </c>
-      <c r="D30" s="61">
-        <v>0.1</v>
+        <v>27</v>
+      </c>
+      <c r="B30" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="D30" s="53">
+        <v>1.2</v>
       </c>
       <c r="E30" s="11">
         <v>4.3</v>
@@ -4597,15 +4537,15 @@
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>30</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>187</v>
-      </c>
-      <c r="C31" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="61">
+        <v>28</v>
+      </c>
+      <c r="B31" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="C31" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="53">
         <v>1</v>
       </c>
       <c r="E31" s="11">
@@ -4661,15 +4601,15 @@
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>31</v>
-      </c>
-      <c r="B32" s="53" t="s">
-        <v>188</v>
-      </c>
-      <c r="C32" s="59" t="s">
-        <v>170</v>
-      </c>
-      <c r="D32" s="61">
+        <v>29</v>
+      </c>
+      <c r="B32" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="D32" s="53">
         <v>0.1</v>
       </c>
       <c r="E32" s="11">
@@ -4725,16 +4665,16 @@
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>32</v>
-      </c>
-      <c r="B33" s="53" t="s">
-        <v>189</v>
-      </c>
-      <c r="C33" s="54" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="61">
-        <v>0.9</v>
+        <v>30</v>
+      </c>
+      <c r="B33" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="53">
+        <v>1</v>
       </c>
       <c r="E33" s="11">
         <v>4.3</v>
@@ -4789,16 +4729,16 @@
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>33</v>
-      </c>
-      <c r="B34" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="C34" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="61">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="B34" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" s="53">
+        <v>0.1</v>
       </c>
       <c r="E34" s="11">
         <v>4.3</v>
@@ -4853,16 +4793,16 @@
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>34</v>
-      </c>
-      <c r="B35" s="53" t="s">
-        <v>191</v>
-      </c>
-      <c r="C35" s="59" t="s">
-        <v>192</v>
-      </c>
-      <c r="D35" s="61">
-        <v>0.1</v>
+        <v>32</v>
+      </c>
+      <c r="B35" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="C35" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="53">
+        <v>0.9</v>
       </c>
       <c r="E35" s="11">
         <v>4.3</v>
@@ -4917,16 +4857,16 @@
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>35</v>
-      </c>
-      <c r="B36" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="C36" s="59" t="s">
-        <v>194</v>
-      </c>
-      <c r="D36" s="61">
-        <v>0.1</v>
+        <v>33</v>
+      </c>
+      <c r="B36" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="C36" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="53">
+        <v>1</v>
       </c>
       <c r="E36" s="11">
         <v>4.3</v>
@@ -4981,16 +4921,16 @@
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>36</v>
-      </c>
-      <c r="B37" s="53" t="s">
-        <v>195</v>
-      </c>
-      <c r="C37" s="59" t="s">
-        <v>196</v>
-      </c>
-      <c r="D37" s="61">
-        <v>0.7</v>
+        <v>34</v>
+      </c>
+      <c r="B37" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="D37" s="53">
+        <v>0.1</v>
       </c>
       <c r="E37" s="11">
         <v>4.3</v>
@@ -5045,16 +4985,16 @@
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>37</v>
-      </c>
-      <c r="B38" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="C38" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="D38" s="61">
-        <v>1.2</v>
+        <v>35</v>
+      </c>
+      <c r="B38" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="D38" s="53">
+        <v>0.1</v>
       </c>
       <c r="E38" s="11">
         <v>4.3</v>
@@ -5103,6 +5043,134 @@
         <v>0</v>
       </c>
       <c r="AC38" s="16">
+        <f t="shared" si="13"/>
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A39" s="11">
+        <v>36</v>
+      </c>
+      <c r="B39" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="D39" s="53">
+        <v>0.7</v>
+      </c>
+      <c r="E39" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="F39" s="11">
+        <v>8</v>
+      </c>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="12">
+        <f t="shared" si="7"/>
+        <v>12.3</v>
+      </c>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="13">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="11"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="11"/>
+      <c r="V39" s="11"/>
+      <c r="W39" s="11"/>
+      <c r="X39" s="11"/>
+      <c r="Y39" s="14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="12">
+        <f t="shared" si="10"/>
+        <v>12.3</v>
+      </c>
+      <c r="AA39" s="13">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB39" s="14">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AC39" s="16">
+        <f t="shared" si="13"/>
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A40" s="11">
+        <v>37</v>
+      </c>
+      <c r="B40" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="D40" s="53">
+        <v>1.2</v>
+      </c>
+      <c r="E40" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="F40" s="11">
+        <v>8</v>
+      </c>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="12">
+        <f t="shared" si="7"/>
+        <v>12.3</v>
+      </c>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="13">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="11"/>
+      <c r="T40" s="11"/>
+      <c r="U40" s="11"/>
+      <c r="V40" s="11"/>
+      <c r="W40" s="11"/>
+      <c r="X40" s="11"/>
+      <c r="Y40" s="14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="12">
+        <f t="shared" si="10"/>
+        <v>12.3</v>
+      </c>
+      <c r="AA40" s="13">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB40" s="14">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AC40" s="16">
         <f t="shared" si="13"/>
         <v>12.3</v>
       </c>
@@ -5737,84 +5805,84 @@
     </row>
     <row r="7" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="8" spans="1:18" ht="56.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="59" t="s">
         <v>103</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="49" t="s">
+      <c r="E8" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="F8" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="49" t="s">
+      <c r="G8" s="57" t="s">
         <v>106</v>
       </c>
-      <c r="H8" s="49" t="s">
+      <c r="H8" s="57" t="s">
         <v>107</v>
       </c>
       <c r="I8" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="J8" s="49" t="s">
+      <c r="J8" s="57" t="s">
         <v>5</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="L8" s="49" t="s">
+      <c r="L8" s="57" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
+      <c r="A9" s="60"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
       <c r="D9" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
       <c r="I9" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="J9" s="50"/>
+      <c r="J9" s="58"/>
       <c r="K9" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="L9" s="50"/>
+      <c r="L9" s="58"/>
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="46">
+      <c r="A10" s="59">
         <v>1</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="52"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
     </row>
     <row r="11" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="47"/>
-      <c r="B11" s="47"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="22" t="s">
         <v>114</v>
       </c>
@@ -5856,8 +5924,8 @@
       <c r="P11" s="4"/>
     </row>
     <row r="12" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="47"/>
-      <c r="B12" s="47"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="61"/>
       <c r="C12" s="22" t="s">
         <v>116</v>
       </c>
@@ -5903,8 +5971,8 @@
       <c r="P12" s="4"/>
     </row>
     <row r="13" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="61"/>
       <c r="C13" s="22" t="s">
         <v>117</v>
       </c>
@@ -5949,8 +6017,8 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="47"/>
-      <c r="B14" s="47"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
       <c r="C14" s="22" t="s">
         <v>118</v>
       </c>
@@ -5995,8 +6063,8 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="47"/>
-      <c r="B15" s="47"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="61"/>
       <c r="C15" s="22" t="s">
         <v>119</v>
       </c>
@@ -6046,8 +6114,8 @@
       <c r="R15" s="39"/>
     </row>
     <row r="16" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="47"/>
-      <c r="B16" s="47"/>
+      <c r="A16" s="61"/>
+      <c r="B16" s="61"/>
       <c r="C16" s="22" t="s">
         <v>120</v>
       </c>
@@ -6093,8 +6161,8 @@
       <c r="R16" s="39"/>
     </row>
     <row r="17" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="48"/>
-      <c r="B17" s="48"/>
+      <c r="A17" s="60"/>
+      <c r="B17" s="60"/>
       <c r="C17" s="22" t="s">
         <v>121</v>
       </c>
@@ -6145,27 +6213,27 @@
       </c>
     </row>
     <row r="18" spans="1:17" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="46">
+      <c r="A18" s="59">
         <v>2</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="51" t="str">
+      <c r="C18" s="55" t="str">
         <f>IF(O12:O18="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N15&gt;3, N17&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="56"/>
       <c r="N18" s="29">
         <v>3</v>
       </c>
@@ -6182,8 +6250,8 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
       <c r="C19" s="22" t="s">
         <v>114</v>
       </c>
@@ -6224,8 +6292,8 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="47"/>
-      <c r="B20" s="47"/>
+      <c r="A20" s="61"/>
+      <c r="B20" s="61"/>
       <c r="C20" s="22" t="s">
         <v>116</v>
       </c>
@@ -6270,8 +6338,8 @@
       </c>
     </row>
     <row r="21" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="61"/>
+      <c r="B21" s="61"/>
       <c r="C21" s="22" t="s">
         <v>117</v>
       </c>
@@ -6316,8 +6384,8 @@
       </c>
     </row>
     <row r="22" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
       <c r="C22" s="22" t="s">
         <v>118</v>
       </c>
@@ -6362,8 +6430,8 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
+      <c r="A23" s="61"/>
+      <c r="B23" s="61"/>
       <c r="C23" s="22" t="s">
         <v>119</v>
       </c>
@@ -6412,8 +6480,8 @@
       </c>
     </row>
     <row r="24" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="47"/>
-      <c r="B24" s="47"/>
+      <c r="A24" s="61"/>
+      <c r="B24" s="61"/>
       <c r="C24" s="22" t="s">
         <v>120</v>
       </c>
@@ -6458,8 +6526,8 @@
       </c>
     </row>
     <row r="25" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="48"/>
-      <c r="B25" s="48"/>
+      <c r="A25" s="60"/>
+      <c r="B25" s="60"/>
       <c r="C25" s="22" t="s">
         <v>121</v>
       </c>
@@ -6504,27 +6572,27 @@
       </c>
     </row>
     <row r="26" spans="1:17" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="46">
+      <c r="A26" s="59">
         <v>3</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="51" t="str">
+      <c r="C26" s="55" t="str">
         <f>IF(O20:O26="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N23&gt;3, N25&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="52"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="56"/>
       <c r="N26" s="29">
         <f>AVERAGE(D23:L25)</f>
         <v>5</v>
@@ -6536,8 +6604,8 @@
       </c>
     </row>
     <row r="27" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="47"/>
-      <c r="B27" s="47"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
       <c r="C27" s="22" t="s">
         <v>114</v>
       </c>
@@ -6578,8 +6646,8 @@
       </c>
     </row>
     <row r="28" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="47"/>
-      <c r="B28" s="47"/>
+      <c r="A28" s="61"/>
+      <c r="B28" s="61"/>
       <c r="C28" s="22" t="s">
         <v>116</v>
       </c>
@@ -6624,8 +6692,8 @@
       </c>
     </row>
     <row r="29" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="47"/>
-      <c r="B29" s="47"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="61"/>
       <c r="C29" s="22" t="s">
         <v>117</v>
       </c>
@@ -6670,8 +6738,8 @@
       </c>
     </row>
     <row r="30" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="61"/>
+      <c r="B30" s="61"/>
       <c r="C30" s="22" t="s">
         <v>118</v>
       </c>
@@ -6716,8 +6784,8 @@
       </c>
     </row>
     <row r="31" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="47"/>
-      <c r="B31" s="47"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
       <c r="C31" s="22" t="s">
         <v>119</v>
       </c>
@@ -6766,8 +6834,8 @@
       </c>
     </row>
     <row r="32" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="47"/>
-      <c r="B32" s="47"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="61"/>
       <c r="C32" s="22" t="s">
         <v>120</v>
       </c>
@@ -6812,8 +6880,8 @@
       </c>
     </row>
     <row r="33" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="48"/>
-      <c r="B33" s="48"/>
+      <c r="A33" s="60"/>
+      <c r="B33" s="60"/>
       <c r="C33" s="22" t="s">
         <v>121</v>
       </c>
@@ -6858,27 +6926,27 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="46">
-        <v>4</v>
-      </c>
-      <c r="B34" s="46" t="s">
+      <c r="A34" s="59">
+        <v>4</v>
+      </c>
+      <c r="B34" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="51" t="str">
+      <c r="C34" s="55" t="str">
         <f>IF(O28:O34="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N31&gt;3, N33&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="52"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="56"/>
       <c r="N34" s="27">
         <f>AVERAGE(D31:L33)</f>
         <v>5</v>
@@ -6890,8 +6958,8 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="47"/>
-      <c r="B35" s="47"/>
+      <c r="A35" s="61"/>
+      <c r="B35" s="61"/>
       <c r="C35" s="22" t="s">
         <v>114</v>
       </c>
@@ -6926,8 +6994,8 @@
       <c r="O35" s="28"/>
     </row>
     <row r="36" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="47"/>
-      <c r="B36" s="47"/>
+      <c r="A36" s="61"/>
+      <c r="B36" s="61"/>
       <c r="C36" s="22" t="s">
         <v>116</v>
       </c>
@@ -6965,8 +7033,8 @@
       </c>
     </row>
     <row r="37" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="47"/>
-      <c r="B37" s="47"/>
+      <c r="A37" s="61"/>
+      <c r="B37" s="61"/>
       <c r="C37" s="22" t="s">
         <v>117</v>
       </c>
@@ -7011,8 +7079,8 @@
       </c>
     </row>
     <row r="38" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="47"/>
-      <c r="B38" s="47"/>
+      <c r="A38" s="61"/>
+      <c r="B38" s="61"/>
       <c r="C38" s="22" t="s">
         <v>118</v>
       </c>
@@ -7050,8 +7118,8 @@
       </c>
     </row>
     <row r="39" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="47"/>
-      <c r="B39" s="47"/>
+      <c r="A39" s="61"/>
+      <c r="B39" s="61"/>
       <c r="C39" s="22" t="s">
         <v>119</v>
       </c>
@@ -7100,8 +7168,8 @@
       </c>
     </row>
     <row r="40" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="47"/>
-      <c r="B40" s="47"/>
+      <c r="A40" s="61"/>
+      <c r="B40" s="61"/>
       <c r="C40" s="22" t="s">
         <v>120</v>
       </c>
@@ -7139,8 +7207,8 @@
       </c>
     </row>
     <row r="41" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="48"/>
-      <c r="B41" s="48"/>
+      <c r="A41" s="60"/>
+      <c r="B41" s="60"/>
       <c r="C41" s="22" t="s">
         <v>121</v>
       </c>
@@ -7178,27 +7246,27 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="46">
-        <v>5</v>
-      </c>
-      <c r="B42" s="46" t="s">
+      <c r="A42" s="59">
+        <v>5</v>
+      </c>
+      <c r="B42" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="51" t="str">
+      <c r="C42" s="55" t="str">
         <f>IF(O36:O42="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N39&gt;3, N41&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="52"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="56"/>
+      <c r="L42" s="56"/>
       <c r="N42" s="29">
         <f>AVERAGE(D39:L41)</f>
         <v>3.8888888888888888</v>
@@ -7210,8 +7278,8 @@
       </c>
     </row>
     <row r="43" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="47"/>
-      <c r="B43" s="47"/>
+      <c r="A43" s="61"/>
+      <c r="B43" s="61"/>
       <c r="C43" s="22" t="s">
         <v>114</v>
       </c>
@@ -7252,8 +7320,8 @@
       </c>
     </row>
     <row r="44" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="47"/>
-      <c r="B44" s="47"/>
+      <c r="A44" s="61"/>
+      <c r="B44" s="61"/>
       <c r="C44" s="22" t="s">
         <v>116</v>
       </c>
@@ -7298,8 +7366,8 @@
       </c>
     </row>
     <row r="45" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="47"/>
-      <c r="B45" s="47"/>
+      <c r="A45" s="61"/>
+      <c r="B45" s="61"/>
       <c r="C45" s="22" t="s">
         <v>117</v>
       </c>
@@ -7344,8 +7412,8 @@
       </c>
     </row>
     <row r="46" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="47"/>
-      <c r="B46" s="47"/>
+      <c r="A46" s="61"/>
+      <c r="B46" s="61"/>
       <c r="C46" s="22" t="s">
         <v>118</v>
       </c>
@@ -7390,8 +7458,8 @@
       </c>
     </row>
     <row r="47" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="47"/>
-      <c r="B47" s="47"/>
+      <c r="A47" s="61"/>
+      <c r="B47" s="61"/>
       <c r="C47" s="22" t="s">
         <v>119</v>
       </c>
@@ -7440,8 +7508,8 @@
       </c>
     </row>
     <row r="48" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="47"/>
-      <c r="B48" s="47"/>
+      <c r="A48" s="61"/>
+      <c r="B48" s="61"/>
       <c r="C48" s="22" t="s">
         <v>120</v>
       </c>
@@ -7486,8 +7554,8 @@
       </c>
     </row>
     <row r="49" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="48"/>
-      <c r="B49" s="48"/>
+      <c r="A49" s="60"/>
+      <c r="B49" s="60"/>
       <c r="C49" s="22" t="s">
         <v>121</v>
       </c>
@@ -7532,27 +7600,27 @@
       </c>
     </row>
     <row r="50" spans="1:17" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="46">
+      <c r="A50" s="59">
         <v>6</v>
       </c>
-      <c r="B50" s="46" t="s">
+      <c r="B50" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="C50" s="51" t="str">
+      <c r="C50" s="55" t="str">
         <f>IF(O44:O50="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N47&gt;3, N49&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="52"/>
-      <c r="H50" s="52"/>
-      <c r="I50" s="52"/>
-      <c r="J50" s="52"/>
-      <c r="K50" s="52"/>
-      <c r="L50" s="52"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="56"/>
+      <c r="J50" s="56"/>
+      <c r="K50" s="56"/>
+      <c r="L50" s="56"/>
       <c r="N50" s="29">
         <f>AVERAGE(D47:L49)</f>
         <v>5</v>
@@ -7564,8 +7632,8 @@
       </c>
     </row>
     <row r="51" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="47"/>
-      <c r="B51" s="47"/>
+      <c r="A51" s="61"/>
+      <c r="B51" s="61"/>
       <c r="C51" s="22" t="s">
         <v>114</v>
       </c>
@@ -7606,8 +7674,8 @@
       </c>
     </row>
     <row r="52" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="47"/>
-      <c r="B52" s="47"/>
+      <c r="A52" s="61"/>
+      <c r="B52" s="61"/>
       <c r="C52" s="22" t="s">
         <v>116</v>
       </c>
@@ -7652,8 +7720,8 @@
       </c>
     </row>
     <row r="53" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="47"/>
-      <c r="B53" s="47"/>
+      <c r="A53" s="61"/>
+      <c r="B53" s="61"/>
       <c r="C53" s="22" t="s">
         <v>117</v>
       </c>
@@ -7698,8 +7766,8 @@
       </c>
     </row>
     <row r="54" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="47"/>
-      <c r="B54" s="47"/>
+      <c r="A54" s="61"/>
+      <c r="B54" s="61"/>
       <c r="C54" s="22" t="s">
         <v>118</v>
       </c>
@@ -7744,8 +7812,8 @@
       </c>
     </row>
     <row r="55" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="47"/>
-      <c r="B55" s="47"/>
+      <c r="A55" s="61"/>
+      <c r="B55" s="61"/>
       <c r="C55" s="22" t="s">
         <v>119</v>
       </c>
@@ -7794,8 +7862,8 @@
       </c>
     </row>
     <row r="56" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="47"/>
-      <c r="B56" s="47"/>
+      <c r="A56" s="61"/>
+      <c r="B56" s="61"/>
       <c r="C56" s="22" t="s">
         <v>120</v>
       </c>
@@ -7840,8 +7908,8 @@
       </c>
     </row>
     <row r="57" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="48"/>
-      <c r="B57" s="48"/>
+      <c r="A57" s="60"/>
+      <c r="B57" s="60"/>
       <c r="C57" s="22" t="s">
         <v>121</v>
       </c>
@@ -7886,27 +7954,27 @@
       </c>
     </row>
     <row r="58" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="46">
+      <c r="A58" s="59">
         <v>7</v>
       </c>
-      <c r="B58" s="46" t="s">
+      <c r="B58" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="C58" s="51" t="str">
+      <c r="C58" s="55" t="str">
         <f>IF(O52:O58="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N55&gt;3, N57&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D58" s="52"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="52"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="52"/>
-      <c r="K58" s="52"/>
-      <c r="L58" s="52"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="56"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56"/>
+      <c r="J58" s="56"/>
+      <c r="K58" s="56"/>
+      <c r="L58" s="56"/>
       <c r="N58" s="29">
         <f>AVERAGE(D55:L57)</f>
         <v>5</v>
@@ -7918,8 +7986,8 @@
       </c>
     </row>
     <row r="59" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="47"/>
-      <c r="B59" s="47"/>
+      <c r="A59" s="61"/>
+      <c r="B59" s="61"/>
       <c r="C59" s="22" t="s">
         <v>114</v>
       </c>
@@ -7960,8 +8028,8 @@
       </c>
     </row>
     <row r="60" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="47"/>
-      <c r="B60" s="47"/>
+      <c r="A60" s="61"/>
+      <c r="B60" s="61"/>
       <c r="C60" s="22" t="s">
         <v>116</v>
       </c>
@@ -8006,8 +8074,8 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="47"/>
-      <c r="B61" s="47"/>
+      <c r="A61" s="61"/>
+      <c r="B61" s="61"/>
       <c r="C61" s="22" t="s">
         <v>117</v>
       </c>
@@ -8052,8 +8120,8 @@
       </c>
     </row>
     <row r="62" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="47"/>
-      <c r="B62" s="47"/>
+      <c r="A62" s="61"/>
+      <c r="B62" s="61"/>
       <c r="C62" s="22" t="s">
         <v>118</v>
       </c>
@@ -8098,8 +8166,8 @@
       </c>
     </row>
     <row r="63" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="47"/>
-      <c r="B63" s="47"/>
+      <c r="A63" s="61"/>
+      <c r="B63" s="61"/>
       <c r="C63" s="22" t="s">
         <v>119</v>
       </c>
@@ -8148,8 +8216,8 @@
       </c>
     </row>
     <row r="64" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="47"/>
-      <c r="B64" s="47"/>
+      <c r="A64" s="61"/>
+      <c r="B64" s="61"/>
       <c r="C64" s="22" t="s">
         <v>120</v>
       </c>
@@ -8194,8 +8262,8 @@
       </c>
     </row>
     <row r="65" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="48"/>
-      <c r="B65" s="48"/>
+      <c r="A65" s="60"/>
+      <c r="B65" s="60"/>
       <c r="C65" s="22" t="s">
         <v>121</v>
       </c>
@@ -8240,27 +8308,27 @@
       </c>
     </row>
     <row r="66" spans="1:17" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="46">
+      <c r="A66" s="59">
         <v>8</v>
       </c>
-      <c r="B66" s="46" t="s">
+      <c r="B66" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="C66" s="51" t="str">
+      <c r="C66" s="55" t="str">
         <f>IF(O60:O66="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N63&gt;3, N65&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D66" s="52"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="52"/>
-      <c r="G66" s="52"/>
-      <c r="H66" s="52"/>
-      <c r="I66" s="52"/>
-      <c r="J66" s="52"/>
-      <c r="K66" s="52"/>
-      <c r="L66" s="52"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="56"/>
+      <c r="F66" s="56"/>
+      <c r="G66" s="56"/>
+      <c r="H66" s="56"/>
+      <c r="I66" s="56"/>
+      <c r="J66" s="56"/>
+      <c r="K66" s="56"/>
+      <c r="L66" s="56"/>
       <c r="N66" s="29">
         <f>AVERAGE(D63:L65)</f>
         <v>4</v>
@@ -8272,8 +8340,8 @@
       </c>
     </row>
     <row r="67" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="47"/>
-      <c r="B67" s="47"/>
+      <c r="A67" s="61"/>
+      <c r="B67" s="61"/>
       <c r="C67" s="22" t="s">
         <v>114</v>
       </c>
@@ -8314,8 +8382,8 @@
       </c>
     </row>
     <row r="68" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="47"/>
-      <c r="B68" s="47"/>
+      <c r="A68" s="61"/>
+      <c r="B68" s="61"/>
       <c r="C68" s="22" t="s">
         <v>116</v>
       </c>
@@ -8360,8 +8428,8 @@
       </c>
     </row>
     <row r="69" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="47"/>
-      <c r="B69" s="47"/>
+      <c r="A69" s="61"/>
+      <c r="B69" s="61"/>
       <c r="C69" s="22" t="s">
         <v>117</v>
       </c>
@@ -8406,8 +8474,8 @@
       </c>
     </row>
     <row r="70" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
+      <c r="A70" s="61"/>
+      <c r="B70" s="61"/>
       <c r="C70" s="22" t="s">
         <v>118</v>
       </c>
@@ -8452,8 +8520,8 @@
       </c>
     </row>
     <row r="71" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
+      <c r="A71" s="61"/>
+      <c r="B71" s="61"/>
       <c r="C71" s="22" t="s">
         <v>119</v>
       </c>
@@ -8502,8 +8570,8 @@
       </c>
     </row>
     <row r="72" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="47"/>
-      <c r="B72" s="47"/>
+      <c r="A72" s="61"/>
+      <c r="B72" s="61"/>
       <c r="C72" s="22" t="s">
         <v>120</v>
       </c>
@@ -8548,8 +8616,8 @@
       </c>
     </row>
     <row r="73" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="48"/>
-      <c r="B73" s="48"/>
+      <c r="A73" s="60"/>
+      <c r="B73" s="60"/>
       <c r="C73" s="22" t="s">
         <v>121</v>
       </c>
@@ -8594,27 +8662,27 @@
       </c>
     </row>
     <row r="74" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="46">
+      <c r="A74" s="59">
         <v>9</v>
       </c>
-      <c r="B74" s="46" t="s">
+      <c r="B74" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="C74" s="51" t="str">
+      <c r="C74" s="55" t="str">
         <f>IF(O68:O74="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N71&gt;3, N73&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
-      <c r="G74" s="52"/>
-      <c r="H74" s="52"/>
-      <c r="I74" s="52"/>
-      <c r="J74" s="52"/>
-      <c r="K74" s="52"/>
-      <c r="L74" s="52"/>
+      <c r="D74" s="56"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="56"/>
+      <c r="G74" s="56"/>
+      <c r="H74" s="56"/>
+      <c r="I74" s="56"/>
+      <c r="J74" s="56"/>
+      <c r="K74" s="56"/>
+      <c r="L74" s="56"/>
       <c r="N74" s="29">
         <f>AVERAGE(D71:L73)</f>
         <v>5</v>
@@ -8626,8 +8694,8 @@
       </c>
     </row>
     <row r="75" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="47"/>
-      <c r="B75" s="47"/>
+      <c r="A75" s="61"/>
+      <c r="B75" s="61"/>
       <c r="C75" s="22" t="s">
         <v>114</v>
       </c>
@@ -8668,8 +8736,8 @@
       </c>
     </row>
     <row r="76" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="47"/>
-      <c r="B76" s="47"/>
+      <c r="A76" s="61"/>
+      <c r="B76" s="61"/>
       <c r="C76" s="22" t="s">
         <v>116</v>
       </c>
@@ -8714,8 +8782,8 @@
       </c>
     </row>
     <row r="77" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="47"/>
-      <c r="B77" s="47"/>
+      <c r="A77" s="61"/>
+      <c r="B77" s="61"/>
       <c r="C77" s="22" t="s">
         <v>117</v>
       </c>
@@ -8760,8 +8828,8 @@
       </c>
     </row>
     <row r="78" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="47"/>
-      <c r="B78" s="47"/>
+      <c r="A78" s="61"/>
+      <c r="B78" s="61"/>
       <c r="C78" s="22" t="s">
         <v>118</v>
       </c>
@@ -8806,8 +8874,8 @@
       </c>
     </row>
     <row r="79" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="47"/>
-      <c r="B79" s="47"/>
+      <c r="A79" s="61"/>
+      <c r="B79" s="61"/>
       <c r="C79" s="22" t="s">
         <v>119</v>
       </c>
@@ -8856,8 +8924,8 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="47"/>
-      <c r="B80" s="47"/>
+      <c r="A80" s="61"/>
+      <c r="B80" s="61"/>
       <c r="C80" s="22" t="s">
         <v>120</v>
       </c>
@@ -8902,8 +8970,8 @@
       </c>
     </row>
     <row r="81" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="48"/>
-      <c r="B81" s="48"/>
+      <c r="A81" s="60"/>
+      <c r="B81" s="60"/>
       <c r="C81" s="22" t="s">
         <v>121</v>
       </c>
@@ -8948,27 +9016,27 @@
       </c>
     </row>
     <row r="82" spans="1:17" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="46">
+      <c r="A82" s="59">
         <v>10</v>
       </c>
-      <c r="B82" s="46" t="s">
+      <c r="B82" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="C82" s="51" t="str">
+      <c r="C82" s="55" t="str">
         <f>IF(O76:O82="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N79&gt;3, N81&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D82" s="52"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="52"/>
-      <c r="G82" s="52"/>
-      <c r="H82" s="52"/>
-      <c r="I82" s="52"/>
-      <c r="J82" s="52"/>
-      <c r="K82" s="52"/>
-      <c r="L82" s="52"/>
+      <c r="D82" s="56"/>
+      <c r="E82" s="56"/>
+      <c r="F82" s="56"/>
+      <c r="G82" s="56"/>
+      <c r="H82" s="56"/>
+      <c r="I82" s="56"/>
+      <c r="J82" s="56"/>
+      <c r="K82" s="56"/>
+      <c r="L82" s="56"/>
       <c r="N82" s="29">
         <f>AVERAGE(D79:L81)</f>
         <v>4.2727272727272725</v>
@@ -8980,8 +9048,8 @@
       </c>
     </row>
     <row r="83" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="47"/>
-      <c r="B83" s="47"/>
+      <c r="A83" s="61"/>
+      <c r="B83" s="61"/>
       <c r="C83" s="22" t="s">
         <v>114</v>
       </c>
@@ -9022,8 +9090,8 @@
       </c>
     </row>
     <row r="84" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="47"/>
-      <c r="B84" s="47"/>
+      <c r="A84" s="61"/>
+      <c r="B84" s="61"/>
       <c r="C84" s="22" t="s">
         <v>116</v>
       </c>
@@ -9068,8 +9136,8 @@
       </c>
     </row>
     <row r="85" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="47"/>
-      <c r="B85" s="47"/>
+      <c r="A85" s="61"/>
+      <c r="B85" s="61"/>
       <c r="C85" s="22" t="s">
         <v>117</v>
       </c>
@@ -9114,8 +9182,8 @@
       </c>
     </row>
     <row r="86" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="47"/>
-      <c r="B86" s="47"/>
+      <c r="A86" s="61"/>
+      <c r="B86" s="61"/>
       <c r="C86" s="22" t="s">
         <v>118</v>
       </c>
@@ -9160,8 +9228,8 @@
       </c>
     </row>
     <row r="87" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="47"/>
-      <c r="B87" s="47"/>
+      <c r="A87" s="61"/>
+      <c r="B87" s="61"/>
       <c r="C87" s="22" t="s">
         <v>119</v>
       </c>
@@ -9210,8 +9278,8 @@
       </c>
     </row>
     <row r="88" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="47"/>
-      <c r="B88" s="47"/>
+      <c r="A88" s="61"/>
+      <c r="B88" s="61"/>
       <c r="C88" s="22" t="s">
         <v>120</v>
       </c>
@@ -9256,8 +9324,8 @@
       </c>
     </row>
     <row r="89" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="48"/>
-      <c r="B89" s="48"/>
+      <c r="A89" s="60"/>
+      <c r="B89" s="60"/>
       <c r="C89" s="22" t="s">
         <v>121</v>
       </c>
@@ -9302,27 +9370,27 @@
       </c>
     </row>
     <row r="90" spans="1:17" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="46">
+      <c r="A90" s="59">
         <v>11</v>
       </c>
-      <c r="B90" s="46" t="s">
+      <c r="B90" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="C90" s="51" t="str">
+      <c r="C90" s="55" t="str">
         <f>IF(O84:O90="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N87&gt;3, N89&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D90" s="52"/>
-      <c r="E90" s="52"/>
-      <c r="F90" s="52"/>
-      <c r="G90" s="52"/>
-      <c r="H90" s="52"/>
-      <c r="I90" s="52"/>
-      <c r="J90" s="52"/>
-      <c r="K90" s="52"/>
-      <c r="L90" s="52"/>
+      <c r="D90" s="56"/>
+      <c r="E90" s="56"/>
+      <c r="F90" s="56"/>
+      <c r="G90" s="56"/>
+      <c r="H90" s="56"/>
+      <c r="I90" s="56"/>
+      <c r="J90" s="56"/>
+      <c r="K90" s="56"/>
+      <c r="L90" s="56"/>
       <c r="N90" s="29">
         <f>AVERAGE(D87:L89)</f>
         <v>4.2727272727272725</v>
@@ -9334,8 +9402,8 @@
       </c>
     </row>
     <row r="91" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="47"/>
-      <c r="B91" s="47"/>
+      <c r="A91" s="61"/>
+      <c r="B91" s="61"/>
       <c r="C91" s="22" t="s">
         <v>114</v>
       </c>
@@ -9376,8 +9444,8 @@
       </c>
     </row>
     <row r="92" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="47"/>
-      <c r="B92" s="47"/>
+      <c r="A92" s="61"/>
+      <c r="B92" s="61"/>
       <c r="C92" s="22" t="s">
         <v>116</v>
       </c>
@@ -9422,8 +9490,8 @@
       </c>
     </row>
     <row r="93" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="47"/>
-      <c r="B93" s="47"/>
+      <c r="A93" s="61"/>
+      <c r="B93" s="61"/>
       <c r="C93" s="22" t="s">
         <v>117</v>
       </c>
@@ -9468,8 +9536,8 @@
       </c>
     </row>
     <row r="94" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="47"/>
-      <c r="B94" s="47"/>
+      <c r="A94" s="61"/>
+      <c r="B94" s="61"/>
       <c r="C94" s="22" t="s">
         <v>118</v>
       </c>
@@ -9514,8 +9582,8 @@
       </c>
     </row>
     <row r="95" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="47"/>
-      <c r="B95" s="47"/>
+      <c r="A95" s="61"/>
+      <c r="B95" s="61"/>
       <c r="C95" s="22" t="s">
         <v>119</v>
       </c>
@@ -9564,8 +9632,8 @@
       </c>
     </row>
     <row r="96" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="47"/>
-      <c r="B96" s="47"/>
+      <c r="A96" s="61"/>
+      <c r="B96" s="61"/>
       <c r="C96" s="22" t="s">
         <v>120</v>
       </c>
@@ -9610,8 +9678,8 @@
       </c>
     </row>
     <row r="97" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="48"/>
-      <c r="B97" s="48"/>
+      <c r="A97" s="60"/>
+      <c r="B97" s="60"/>
       <c r="C97" s="22" t="s">
         <v>121</v>
       </c>
@@ -9656,27 +9724,27 @@
       </c>
     </row>
     <row r="98" spans="1:17" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="46">
+      <c r="A98" s="59">
         <v>12</v>
       </c>
-      <c r="B98" s="46" t="s">
+      <c r="B98" s="59" t="s">
         <v>132</v>
       </c>
-      <c r="C98" s="51" t="str">
+      <c r="C98" s="55" t="str">
         <f>IF(O92:O98="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N95&gt;3, N97&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D98" s="52"/>
-      <c r="E98" s="52"/>
-      <c r="F98" s="52"/>
-      <c r="G98" s="52"/>
-      <c r="H98" s="52"/>
-      <c r="I98" s="52"/>
-      <c r="J98" s="52"/>
-      <c r="K98" s="52"/>
-      <c r="L98" s="52"/>
+      <c r="D98" s="56"/>
+      <c r="E98" s="56"/>
+      <c r="F98" s="56"/>
+      <c r="G98" s="56"/>
+      <c r="H98" s="56"/>
+      <c r="I98" s="56"/>
+      <c r="J98" s="56"/>
+      <c r="K98" s="56"/>
+      <c r="L98" s="56"/>
       <c r="N98" s="29">
         <f>AVERAGE(D95:L97)</f>
         <v>4</v>
@@ -9688,8 +9756,8 @@
       </c>
     </row>
     <row r="99" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="47"/>
-      <c r="B99" s="47"/>
+      <c r="A99" s="61"/>
+      <c r="B99" s="61"/>
       <c r="C99" s="22" t="s">
         <v>114</v>
       </c>
@@ -9730,8 +9798,8 @@
       </c>
     </row>
     <row r="100" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="47"/>
-      <c r="B100" s="47"/>
+      <c r="A100" s="61"/>
+      <c r="B100" s="61"/>
       <c r="C100" s="22" t="s">
         <v>116</v>
       </c>
@@ -9776,8 +9844,8 @@
       </c>
     </row>
     <row r="101" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
+      <c r="A101" s="61"/>
+      <c r="B101" s="61"/>
       <c r="C101" s="22" t="s">
         <v>117</v>
       </c>
@@ -9822,8 +9890,8 @@
       </c>
     </row>
     <row r="102" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="47"/>
-      <c r="B102" s="47"/>
+      <c r="A102" s="61"/>
+      <c r="B102" s="61"/>
       <c r="C102" s="22" t="s">
         <v>118</v>
       </c>
@@ -9868,8 +9936,8 @@
       </c>
     </row>
     <row r="103" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="47"/>
-      <c r="B103" s="47"/>
+      <c r="A103" s="61"/>
+      <c r="B103" s="61"/>
       <c r="C103" s="22" t="s">
         <v>119</v>
       </c>
@@ -9918,8 +9986,8 @@
       </c>
     </row>
     <row r="104" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="47"/>
-      <c r="B104" s="47"/>
+      <c r="A104" s="61"/>
+      <c r="B104" s="61"/>
       <c r="C104" s="22" t="s">
         <v>120</v>
       </c>
@@ -9964,8 +10032,8 @@
       </c>
     </row>
     <row r="105" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="48"/>
-      <c r="B105" s="48"/>
+      <c r="A105" s="60"/>
+      <c r="B105" s="60"/>
       <c r="C105" s="22" t="s">
         <v>121</v>
       </c>
@@ -10010,27 +10078,27 @@
       </c>
     </row>
     <row r="106" spans="1:17" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="46">
+      <c r="A106" s="59">
         <v>13</v>
       </c>
-      <c r="B106" s="46" t="s">
+      <c r="B106" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="C106" s="51" t="str">
+      <c r="C106" s="55" t="str">
         <f>IF(O100:O106="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N103&gt;3, N105&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D106" s="52"/>
-      <c r="E106" s="52"/>
-      <c r="F106" s="52"/>
-      <c r="G106" s="52"/>
-      <c r="H106" s="52"/>
-      <c r="I106" s="52"/>
-      <c r="J106" s="52"/>
-      <c r="K106" s="52"/>
-      <c r="L106" s="52"/>
+      <c r="D106" s="56"/>
+      <c r="E106" s="56"/>
+      <c r="F106" s="56"/>
+      <c r="G106" s="56"/>
+      <c r="H106" s="56"/>
+      <c r="I106" s="56"/>
+      <c r="J106" s="56"/>
+      <c r="K106" s="56"/>
+      <c r="L106" s="56"/>
       <c r="N106" s="29">
         <f>AVERAGE(D103:L105)</f>
         <v>4.2727272727272725</v>
@@ -10042,8 +10110,8 @@
       </c>
     </row>
     <row r="107" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="47"/>
-      <c r="B107" s="47"/>
+      <c r="A107" s="61"/>
+      <c r="B107" s="61"/>
       <c r="C107" s="22" t="s">
         <v>114</v>
       </c>
@@ -10084,8 +10152,8 @@
       </c>
     </row>
     <row r="108" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="47"/>
-      <c r="B108" s="47"/>
+      <c r="A108" s="61"/>
+      <c r="B108" s="61"/>
       <c r="C108" s="22" t="s">
         <v>116</v>
       </c>
@@ -10130,8 +10198,8 @@
       </c>
     </row>
     <row r="109" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="47"/>
-      <c r="B109" s="47"/>
+      <c r="A109" s="61"/>
+      <c r="B109" s="61"/>
       <c r="C109" s="22" t="s">
         <v>117</v>
       </c>
@@ -10176,8 +10244,8 @@
       </c>
     </row>
     <row r="110" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="47"/>
-      <c r="B110" s="47"/>
+      <c r="A110" s="61"/>
+      <c r="B110" s="61"/>
       <c r="C110" s="22" t="s">
         <v>118</v>
       </c>
@@ -10222,8 +10290,8 @@
       </c>
     </row>
     <row r="111" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="47"/>
-      <c r="B111" s="47"/>
+      <c r="A111" s="61"/>
+      <c r="B111" s="61"/>
       <c r="C111" s="22" t="s">
         <v>119</v>
       </c>
@@ -10272,8 +10340,8 @@
       </c>
     </row>
     <row r="112" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="47"/>
-      <c r="B112" s="47"/>
+      <c r="A112" s="61"/>
+      <c r="B112" s="61"/>
       <c r="C112" s="22" t="s">
         <v>120</v>
       </c>
@@ -10318,8 +10386,8 @@
       </c>
     </row>
     <row r="113" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="48"/>
-      <c r="B113" s="48"/>
+      <c r="A113" s="60"/>
+      <c r="B113" s="60"/>
       <c r="C113" s="22" t="s">
         <v>121</v>
       </c>
@@ -10364,27 +10432,27 @@
       </c>
     </row>
     <row r="114" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="46">
+      <c r="A114" s="59">
         <v>14</v>
       </c>
-      <c r="B114" s="46" t="s">
+      <c r="B114" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="C114" s="51" t="str">
+      <c r="C114" s="55" t="str">
         <f>IF(O108:O114="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N111&gt;3, N113&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D114" s="52"/>
-      <c r="E114" s="52"/>
-      <c r="F114" s="52"/>
-      <c r="G114" s="52"/>
-      <c r="H114" s="52"/>
-      <c r="I114" s="52"/>
-      <c r="J114" s="52"/>
-      <c r="K114" s="52"/>
-      <c r="L114" s="52"/>
+      <c r="D114" s="56"/>
+      <c r="E114" s="56"/>
+      <c r="F114" s="56"/>
+      <c r="G114" s="56"/>
+      <c r="H114" s="56"/>
+      <c r="I114" s="56"/>
+      <c r="J114" s="56"/>
+      <c r="K114" s="56"/>
+      <c r="L114" s="56"/>
       <c r="N114" s="29">
         <f>AVERAGE(D111:L113)</f>
         <v>5</v>
@@ -10396,8 +10464,8 @@
       </c>
     </row>
     <row r="115" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="47"/>
-      <c r="B115" s="47"/>
+      <c r="A115" s="61"/>
+      <c r="B115" s="61"/>
       <c r="C115" s="22" t="s">
         <v>114</v>
       </c>
@@ -10438,8 +10506,8 @@
       </c>
     </row>
     <row r="116" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="47"/>
-      <c r="B116" s="47"/>
+      <c r="A116" s="61"/>
+      <c r="B116" s="61"/>
       <c r="C116" s="22" t="s">
         <v>116</v>
       </c>
@@ -10484,8 +10552,8 @@
       </c>
     </row>
     <row r="117" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="47"/>
-      <c r="B117" s="47"/>
+      <c r="A117" s="61"/>
+      <c r="B117" s="61"/>
       <c r="C117" s="22" t="s">
         <v>117</v>
       </c>
@@ -10530,8 +10598,8 @@
       </c>
     </row>
     <row r="118" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="47"/>
-      <c r="B118" s="47"/>
+      <c r="A118" s="61"/>
+      <c r="B118" s="61"/>
       <c r="C118" s="22" t="s">
         <v>118</v>
       </c>
@@ -10576,8 +10644,8 @@
       </c>
     </row>
     <row r="119" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="47"/>
-      <c r="B119" s="47"/>
+      <c r="A119" s="61"/>
+      <c r="B119" s="61"/>
       <c r="C119" s="22" t="s">
         <v>119</v>
       </c>
@@ -10626,8 +10694,8 @@
       </c>
     </row>
     <row r="120" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="47"/>
-      <c r="B120" s="47"/>
+      <c r="A120" s="61"/>
+      <c r="B120" s="61"/>
       <c r="C120" s="22" t="s">
         <v>120</v>
       </c>
@@ -10672,8 +10740,8 @@
       </c>
     </row>
     <row r="121" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="48"/>
-      <c r="B121" s="48"/>
+      <c r="A121" s="60"/>
+      <c r="B121" s="60"/>
       <c r="C121" s="22" t="s">
         <v>121</v>
       </c>
@@ -10718,27 +10786,27 @@
       </c>
     </row>
     <row r="122" spans="1:17" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="46">
+      <c r="A122" s="59">
         <v>15</v>
       </c>
-      <c r="B122" s="46" t="s">
+      <c r="B122" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="C122" s="51" t="str">
+      <c r="C122" s="55" t="str">
         <f>IF(O116:O122="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N119&gt;3, N121&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D122" s="52"/>
-      <c r="E122" s="52"/>
-      <c r="F122" s="52"/>
-      <c r="G122" s="52"/>
-      <c r="H122" s="52"/>
-      <c r="I122" s="52"/>
-      <c r="J122" s="52"/>
-      <c r="K122" s="52"/>
-      <c r="L122" s="52"/>
+      <c r="D122" s="56"/>
+      <c r="E122" s="56"/>
+      <c r="F122" s="56"/>
+      <c r="G122" s="56"/>
+      <c r="H122" s="56"/>
+      <c r="I122" s="56"/>
+      <c r="J122" s="56"/>
+      <c r="K122" s="56"/>
+      <c r="L122" s="56"/>
       <c r="N122" s="29">
         <f>AVERAGE(D119:L121)</f>
         <v>4.1818181818181817</v>
@@ -10750,8 +10818,8 @@
       </c>
     </row>
     <row r="123" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="47"/>
-      <c r="B123" s="47"/>
+      <c r="A123" s="61"/>
+      <c r="B123" s="61"/>
       <c r="C123" s="22" t="s">
         <v>114</v>
       </c>
@@ -10792,8 +10860,8 @@
       </c>
     </row>
     <row r="124" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="47"/>
-      <c r="B124" s="47"/>
+      <c r="A124" s="61"/>
+      <c r="B124" s="61"/>
       <c r="C124" s="22" t="s">
         <v>116</v>
       </c>
@@ -10838,8 +10906,8 @@
       </c>
     </row>
     <row r="125" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="47"/>
-      <c r="B125" s="47"/>
+      <c r="A125" s="61"/>
+      <c r="B125" s="61"/>
       <c r="C125" s="22" t="s">
         <v>117</v>
       </c>
@@ -10884,8 +10952,8 @@
       </c>
     </row>
     <row r="126" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="47"/>
-      <c r="B126" s="47"/>
+      <c r="A126" s="61"/>
+      <c r="B126" s="61"/>
       <c r="C126" s="22" t="s">
         <v>118</v>
       </c>
@@ -10930,8 +10998,8 @@
       </c>
     </row>
     <row r="127" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="47"/>
-      <c r="B127" s="47"/>
+      <c r="A127" s="61"/>
+      <c r="B127" s="61"/>
       <c r="C127" s="22" t="s">
         <v>119</v>
       </c>
@@ -10980,8 +11048,8 @@
       </c>
     </row>
     <row r="128" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="47"/>
-      <c r="B128" s="47"/>
+      <c r="A128" s="61"/>
+      <c r="B128" s="61"/>
       <c r="C128" s="22" t="s">
         <v>120</v>
       </c>
@@ -11026,8 +11094,8 @@
       </c>
     </row>
     <row r="129" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="48"/>
-      <c r="B129" s="48"/>
+      <c r="A129" s="60"/>
+      <c r="B129" s="60"/>
       <c r="C129" s="22" t="s">
         <v>121</v>
       </c>
@@ -11072,27 +11140,27 @@
       </c>
     </row>
     <row r="130" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="46">
+      <c r="A130" s="59">
         <v>16</v>
       </c>
-      <c r="B130" s="46" t="s">
+      <c r="B130" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="C130" s="51" t="str">
+      <c r="C130" s="55" t="str">
         <f>IF(O124:O130="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N127&gt;3, N129&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D130" s="52"/>
-      <c r="E130" s="52"/>
-      <c r="F130" s="52"/>
-      <c r="G130" s="52"/>
-      <c r="H130" s="52"/>
-      <c r="I130" s="52"/>
-      <c r="J130" s="52"/>
-      <c r="K130" s="52"/>
-      <c r="L130" s="52"/>
+      <c r="D130" s="56"/>
+      <c r="E130" s="56"/>
+      <c r="F130" s="56"/>
+      <c r="G130" s="56"/>
+      <c r="H130" s="56"/>
+      <c r="I130" s="56"/>
+      <c r="J130" s="56"/>
+      <c r="K130" s="56"/>
+      <c r="L130" s="56"/>
       <c r="N130" s="29">
         <f>AVERAGE(D127:L129)</f>
         <v>5</v>
@@ -11104,8 +11172,8 @@
       </c>
     </row>
     <row r="131" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="47"/>
-      <c r="B131" s="47"/>
+      <c r="A131" s="61"/>
+      <c r="B131" s="61"/>
       <c r="C131" s="22" t="s">
         <v>114</v>
       </c>
@@ -11146,8 +11214,8 @@
       </c>
     </row>
     <row r="132" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="47"/>
-      <c r="B132" s="47"/>
+      <c r="A132" s="61"/>
+      <c r="B132" s="61"/>
       <c r="C132" s="22" t="s">
         <v>116</v>
       </c>
@@ -11192,8 +11260,8 @@
       </c>
     </row>
     <row r="133" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="47"/>
-      <c r="B133" s="47"/>
+      <c r="A133" s="61"/>
+      <c r="B133" s="61"/>
       <c r="C133" s="22" t="s">
         <v>117</v>
       </c>
@@ -11238,8 +11306,8 @@
       </c>
     </row>
     <row r="134" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="47"/>
-      <c r="B134" s="47"/>
+      <c r="A134" s="61"/>
+      <c r="B134" s="61"/>
       <c r="C134" s="22" t="s">
         <v>118</v>
       </c>
@@ -11284,8 +11352,8 @@
       </c>
     </row>
     <row r="135" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="47"/>
-      <c r="B135" s="47"/>
+      <c r="A135" s="61"/>
+      <c r="B135" s="61"/>
       <c r="C135" s="22" t="s">
         <v>119</v>
       </c>
@@ -11334,8 +11402,8 @@
       </c>
     </row>
     <row r="136" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="47"/>
-      <c r="B136" s="47"/>
+      <c r="A136" s="61"/>
+      <c r="B136" s="61"/>
       <c r="C136" s="22" t="s">
         <v>120</v>
       </c>
@@ -11380,8 +11448,8 @@
       </c>
     </row>
     <row r="137" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="48"/>
-      <c r="B137" s="48"/>
+      <c r="A137" s="60"/>
+      <c r="B137" s="60"/>
       <c r="C137" s="22" t="s">
         <v>121</v>
       </c>
@@ -11426,27 +11494,27 @@
       </c>
     </row>
     <row r="138" spans="1:17" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="46">
+      <c r="A138" s="59">
         <v>17</v>
       </c>
-      <c r="B138" s="46" t="s">
+      <c r="B138" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="51" t="str">
+      <c r="C138" s="55" t="str">
         <f>IF(O132:O138="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N135&gt;3, N137&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D138" s="52"/>
-      <c r="E138" s="52"/>
-      <c r="F138" s="52"/>
-      <c r="G138" s="52"/>
-      <c r="H138" s="52"/>
-      <c r="I138" s="52"/>
-      <c r="J138" s="52"/>
-      <c r="K138" s="52"/>
-      <c r="L138" s="52"/>
+      <c r="D138" s="56"/>
+      <c r="E138" s="56"/>
+      <c r="F138" s="56"/>
+      <c r="G138" s="56"/>
+      <c r="H138" s="56"/>
+      <c r="I138" s="56"/>
+      <c r="J138" s="56"/>
+      <c r="K138" s="56"/>
+      <c r="L138" s="56"/>
       <c r="N138" s="29">
         <f>AVERAGE(D135:L137)</f>
         <v>5</v>
@@ -11458,8 +11526,8 @@
       </c>
     </row>
     <row r="139" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="47"/>
-      <c r="B139" s="47"/>
+      <c r="A139" s="61"/>
+      <c r="B139" s="61"/>
       <c r="C139" s="22" t="s">
         <v>114</v>
       </c>
@@ -11500,8 +11568,8 @@
       </c>
     </row>
     <row r="140" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="47"/>
-      <c r="B140" s="47"/>
+      <c r="A140" s="61"/>
+      <c r="B140" s="61"/>
       <c r="C140" s="22" t="s">
         <v>116</v>
       </c>
@@ -11546,8 +11614,8 @@
       </c>
     </row>
     <row r="141" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="47"/>
-      <c r="B141" s="47"/>
+      <c r="A141" s="61"/>
+      <c r="B141" s="61"/>
       <c r="C141" s="22" t="s">
         <v>117</v>
       </c>
@@ -11592,8 +11660,8 @@
       </c>
     </row>
     <row r="142" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="47"/>
-      <c r="B142" s="47"/>
+      <c r="A142" s="61"/>
+      <c r="B142" s="61"/>
       <c r="C142" s="22" t="s">
         <v>118</v>
       </c>
@@ -11638,8 +11706,8 @@
       </c>
     </row>
     <row r="143" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="47"/>
-      <c r="B143" s="47"/>
+      <c r="A143" s="61"/>
+      <c r="B143" s="61"/>
       <c r="C143" s="22" t="s">
         <v>119</v>
       </c>
@@ -11688,8 +11756,8 @@
       </c>
     </row>
     <row r="144" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="47"/>
-      <c r="B144" s="47"/>
+      <c r="A144" s="61"/>
+      <c r="B144" s="61"/>
       <c r="C144" s="22" t="s">
         <v>120</v>
       </c>
@@ -11734,8 +11802,8 @@
       </c>
     </row>
     <row r="145" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="48"/>
-      <c r="B145" s="48"/>
+      <c r="A145" s="60"/>
+      <c r="B145" s="60"/>
       <c r="C145" s="22" t="s">
         <v>121</v>
       </c>
@@ -11780,27 +11848,27 @@
       </c>
     </row>
     <row r="146" spans="1:17" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="46">
+      <c r="A146" s="59">
         <v>18</v>
       </c>
-      <c r="B146" s="46" t="s">
+      <c r="B146" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="C146" s="51" t="str">
+      <c r="C146" s="55" t="str">
         <f>IF(O140:O146="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N143&gt;3, N145&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D146" s="52"/>
-      <c r="E146" s="52"/>
-      <c r="F146" s="52"/>
-      <c r="G146" s="52"/>
-      <c r="H146" s="52"/>
-      <c r="I146" s="52"/>
-      <c r="J146" s="52"/>
-      <c r="K146" s="52"/>
-      <c r="L146" s="52"/>
+      <c r="D146" s="56"/>
+      <c r="E146" s="56"/>
+      <c r="F146" s="56"/>
+      <c r="G146" s="56"/>
+      <c r="H146" s="56"/>
+      <c r="I146" s="56"/>
+      <c r="J146" s="56"/>
+      <c r="K146" s="56"/>
+      <c r="L146" s="56"/>
       <c r="N146" s="29">
         <f>AVERAGE(D143:L145)</f>
         <v>5</v>
@@ -11812,8 +11880,8 @@
       </c>
     </row>
     <row r="147" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="47"/>
-      <c r="B147" s="47"/>
+      <c r="A147" s="61"/>
+      <c r="B147" s="61"/>
       <c r="C147" s="22" t="s">
         <v>114</v>
       </c>
@@ -11846,8 +11914,8 @@
       </c>
     </row>
     <row r="148" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="47"/>
-      <c r="B148" s="47"/>
+      <c r="A148" s="61"/>
+      <c r="B148" s="61"/>
       <c r="C148" s="22" t="s">
         <v>116</v>
       </c>
@@ -11884,8 +11952,8 @@
       </c>
     </row>
     <row r="149" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="47"/>
-      <c r="B149" s="47"/>
+      <c r="A149" s="61"/>
+      <c r="B149" s="61"/>
       <c r="C149" s="22" t="s">
         <v>117</v>
       </c>
@@ -11922,8 +11990,8 @@
       </c>
     </row>
     <row r="150" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="47"/>
-      <c r="B150" s="47"/>
+      <c r="A150" s="61"/>
+      <c r="B150" s="61"/>
       <c r="C150" s="22" t="s">
         <v>118</v>
       </c>
@@ -11968,8 +12036,8 @@
       </c>
     </row>
     <row r="151" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="47"/>
-      <c r="B151" s="47"/>
+      <c r="A151" s="61"/>
+      <c r="B151" s="61"/>
       <c r="C151" s="22" t="s">
         <v>119</v>
       </c>
@@ -12018,8 +12086,8 @@
       </c>
     </row>
     <row r="152" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="47"/>
-      <c r="B152" s="47"/>
+      <c r="A152" s="61"/>
+      <c r="B152" s="61"/>
       <c r="C152" s="22" t="s">
         <v>120</v>
       </c>
@@ -12064,8 +12132,8 @@
       </c>
     </row>
     <row r="153" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="48"/>
-      <c r="B153" s="48"/>
+      <c r="A153" s="60"/>
+      <c r="B153" s="60"/>
       <c r="C153" s="22" t="s">
         <v>121</v>
       </c>
@@ -12110,27 +12178,27 @@
       </c>
     </row>
     <row r="154" spans="1:17" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="46">
+      <c r="A154" s="59">
         <v>19</v>
       </c>
-      <c r="B154" s="46" t="s">
+      <c r="B154" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="C154" s="51" t="str">
+      <c r="C154" s="55" t="str">
         <f>IF(O148:O154="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N151&gt;3, N153&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D154" s="52"/>
-      <c r="E154" s="52"/>
-      <c r="F154" s="52"/>
-      <c r="G154" s="52"/>
-      <c r="H154" s="52"/>
-      <c r="I154" s="52"/>
-      <c r="J154" s="52"/>
-      <c r="K154" s="52"/>
-      <c r="L154" s="52"/>
+      <c r="D154" s="56"/>
+      <c r="E154" s="56"/>
+      <c r="F154" s="56"/>
+      <c r="G154" s="56"/>
+      <c r="H154" s="56"/>
+      <c r="I154" s="56"/>
+      <c r="J154" s="56"/>
+      <c r="K154" s="56"/>
+      <c r="L154" s="56"/>
       <c r="N154" s="29">
         <f>AVERAGE(D151:L153)</f>
         <v>5</v>
@@ -12142,8 +12210,8 @@
       </c>
     </row>
     <row r="155" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="47"/>
-      <c r="B155" s="47"/>
+      <c r="A155" s="61"/>
+      <c r="B155" s="61"/>
       <c r="C155" s="22" t="s">
         <v>114</v>
       </c>
@@ -12184,8 +12252,8 @@
       </c>
     </row>
     <row r="156" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="47"/>
-      <c r="B156" s="47"/>
+      <c r="A156" s="61"/>
+      <c r="B156" s="61"/>
       <c r="C156" s="22" t="s">
         <v>116</v>
       </c>
@@ -12230,8 +12298,8 @@
       </c>
     </row>
     <row r="157" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="47"/>
-      <c r="B157" s="47"/>
+      <c r="A157" s="61"/>
+      <c r="B157" s="61"/>
       <c r="C157" s="22" t="s">
         <v>117</v>
       </c>
@@ -12276,8 +12344,8 @@
       </c>
     </row>
     <row r="158" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="47"/>
-      <c r="B158" s="47"/>
+      <c r="A158" s="61"/>
+      <c r="B158" s="61"/>
       <c r="C158" s="22" t="s">
         <v>118</v>
       </c>
@@ -12322,8 +12390,8 @@
       </c>
     </row>
     <row r="159" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="47"/>
-      <c r="B159" s="47"/>
+      <c r="A159" s="61"/>
+      <c r="B159" s="61"/>
       <c r="C159" s="22" t="s">
         <v>119</v>
       </c>
@@ -12372,8 +12440,8 @@
       </c>
     </row>
     <row r="160" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="47"/>
-      <c r="B160" s="47"/>
+      <c r="A160" s="61"/>
+      <c r="B160" s="61"/>
       <c r="C160" s="22" t="s">
         <v>120</v>
       </c>
@@ -12418,8 +12486,8 @@
       </c>
     </row>
     <row r="161" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="48"/>
-      <c r="B161" s="48"/>
+      <c r="A161" s="60"/>
+      <c r="B161" s="60"/>
       <c r="C161" s="22" t="s">
         <v>121</v>
       </c>
@@ -12464,27 +12532,27 @@
       </c>
     </row>
     <row r="162" spans="1:17" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="46">
+      <c r="A162" s="59">
         <v>20</v>
       </c>
-      <c r="B162" s="46" t="s">
+      <c r="B162" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="C162" s="51" t="str">
+      <c r="C162" s="55" t="str">
         <f>IF(O156:O162="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N159&gt;3, N161&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D162" s="52"/>
-      <c r="E162" s="52"/>
-      <c r="F162" s="52"/>
-      <c r="G162" s="52"/>
-      <c r="H162" s="52"/>
-      <c r="I162" s="52"/>
-      <c r="J162" s="52"/>
-      <c r="K162" s="52"/>
-      <c r="L162" s="52"/>
+      <c r="D162" s="56"/>
+      <c r="E162" s="56"/>
+      <c r="F162" s="56"/>
+      <c r="G162" s="56"/>
+      <c r="H162" s="56"/>
+      <c r="I162" s="56"/>
+      <c r="J162" s="56"/>
+      <c r="K162" s="56"/>
+      <c r="L162" s="56"/>
       <c r="N162" s="29">
         <f>AVERAGE(D159:L161)</f>
         <v>5</v>
@@ -12496,8 +12564,8 @@
       </c>
     </row>
     <row r="163" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="47"/>
-      <c r="B163" s="47"/>
+      <c r="A163" s="61"/>
+      <c r="B163" s="61"/>
       <c r="C163" s="22" t="s">
         <v>114</v>
       </c>
@@ -12538,8 +12606,8 @@
       </c>
     </row>
     <row r="164" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="47"/>
-      <c r="B164" s="47"/>
+      <c r="A164" s="61"/>
+      <c r="B164" s="61"/>
       <c r="C164" s="22" t="s">
         <v>116</v>
       </c>
@@ -12584,8 +12652,8 @@
       </c>
     </row>
     <row r="165" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="47"/>
-      <c r="B165" s="47"/>
+      <c r="A165" s="61"/>
+      <c r="B165" s="61"/>
       <c r="C165" s="22" t="s">
         <v>117</v>
       </c>
@@ -12630,8 +12698,8 @@
       </c>
     </row>
     <row r="166" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="47"/>
-      <c r="B166" s="47"/>
+      <c r="A166" s="61"/>
+      <c r="B166" s="61"/>
       <c r="C166" s="22" t="s">
         <v>118</v>
       </c>
@@ -12676,8 +12744,8 @@
       </c>
     </row>
     <row r="167" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="47"/>
-      <c r="B167" s="47"/>
+      <c r="A167" s="61"/>
+      <c r="B167" s="61"/>
       <c r="C167" s="22" t="s">
         <v>119</v>
       </c>
@@ -12722,8 +12790,8 @@
       </c>
     </row>
     <row r="168" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="47"/>
-      <c r="B168" s="47"/>
+      <c r="A168" s="61"/>
+      <c r="B168" s="61"/>
       <c r="C168" s="22" t="s">
         <v>120</v>
       </c>
@@ -12772,8 +12840,8 @@
       </c>
     </row>
     <row r="169" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="48"/>
-      <c r="B169" s="48"/>
+      <c r="A169" s="60"/>
+      <c r="B169" s="60"/>
       <c r="C169" s="22" t="s">
         <v>121</v>
       </c>
@@ -12818,27 +12886,27 @@
       </c>
     </row>
     <row r="170" spans="1:17" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="46">
+      <c r="A170" s="59">
         <v>21</v>
       </c>
-      <c r="B170" s="46" t="s">
+      <c r="B170" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="C170" s="51" t="str">
+      <c r="C170" s="55" t="str">
         <f>IF(O164:O170="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N167&gt;3, N169&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D170" s="52"/>
-      <c r="E170" s="52"/>
-      <c r="F170" s="52"/>
-      <c r="G170" s="52"/>
-      <c r="H170" s="52"/>
-      <c r="I170" s="52"/>
-      <c r="J170" s="52"/>
-      <c r="K170" s="52"/>
-      <c r="L170" s="52"/>
+      <c r="D170" s="56"/>
+      <c r="E170" s="56"/>
+      <c r="F170" s="56"/>
+      <c r="G170" s="56"/>
+      <c r="H170" s="56"/>
+      <c r="I170" s="56"/>
+      <c r="J170" s="56"/>
+      <c r="K170" s="56"/>
+      <c r="L170" s="56"/>
       <c r="N170" s="29">
         <f>AVERAGE(D167:L169)</f>
         <v>4.4545454545454541</v>
@@ -12850,8 +12918,8 @@
       </c>
     </row>
     <row r="171" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="47"/>
-      <c r="B171" s="47"/>
+      <c r="A171" s="61"/>
+      <c r="B171" s="61"/>
       <c r="C171" s="22" t="s">
         <v>114</v>
       </c>
@@ -12892,8 +12960,8 @@
       </c>
     </row>
     <row r="172" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="47"/>
-      <c r="B172" s="47"/>
+      <c r="A172" s="61"/>
+      <c r="B172" s="61"/>
       <c r="C172" s="22" t="s">
         <v>116</v>
       </c>
@@ -12938,8 +13006,8 @@
       </c>
     </row>
     <row r="173" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="47"/>
-      <c r="B173" s="47"/>
+      <c r="A173" s="61"/>
+      <c r="B173" s="61"/>
       <c r="C173" s="22" t="s">
         <v>117</v>
       </c>
@@ -12976,8 +13044,8 @@
       </c>
     </row>
     <row r="174" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="47"/>
-      <c r="B174" s="47"/>
+      <c r="A174" s="61"/>
+      <c r="B174" s="61"/>
       <c r="C174" s="22" t="s">
         <v>118</v>
       </c>
@@ -13014,8 +13082,8 @@
       </c>
     </row>
     <row r="175" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="47"/>
-      <c r="B175" s="47"/>
+      <c r="A175" s="61"/>
+      <c r="B175" s="61"/>
       <c r="C175" s="22" t="s">
         <v>119</v>
       </c>
@@ -13064,8 +13132,8 @@
       </c>
     </row>
     <row r="176" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="47"/>
-      <c r="B176" s="47"/>
+      <c r="A176" s="61"/>
+      <c r="B176" s="61"/>
       <c r="C176" s="22" t="s">
         <v>120</v>
       </c>
@@ -13102,8 +13170,8 @@
       </c>
     </row>
     <row r="177" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="48"/>
-      <c r="B177" s="48"/>
+      <c r="A177" s="60"/>
+      <c r="B177" s="60"/>
       <c r="C177" s="22" t="s">
         <v>121</v>
       </c>
@@ -13140,27 +13208,27 @@
       </c>
     </row>
     <row r="178" spans="1:17" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="46">
+      <c r="A178" s="59">
         <v>22</v>
       </c>
-      <c r="B178" s="46" t="s">
+      <c r="B178" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="C178" s="51" t="str">
+      <c r="C178" s="55" t="str">
         <f>IF(O172:O178="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N175&gt;3, N177&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D178" s="52"/>
-      <c r="E178" s="52"/>
-      <c r="F178" s="52"/>
-      <c r="G178" s="52"/>
-      <c r="H178" s="52"/>
-      <c r="I178" s="52"/>
-      <c r="J178" s="52"/>
-      <c r="K178" s="52"/>
-      <c r="L178" s="52"/>
+      <c r="D178" s="56"/>
+      <c r="E178" s="56"/>
+      <c r="F178" s="56"/>
+      <c r="G178" s="56"/>
+      <c r="H178" s="56"/>
+      <c r="I178" s="56"/>
+      <c r="J178" s="56"/>
+      <c r="K178" s="56"/>
+      <c r="L178" s="56"/>
       <c r="N178" s="29">
         <f>AVERAGE(D172:L177)</f>
         <v>4.7</v>
@@ -13172,8 +13240,8 @@
       </c>
     </row>
     <row r="179" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="47"/>
-      <c r="B179" s="47"/>
+      <c r="A179" s="61"/>
+      <c r="B179" s="61"/>
       <c r="C179" s="22" t="s">
         <v>114</v>
       </c>
@@ -13214,8 +13282,8 @@
       </c>
     </row>
     <row r="180" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="47"/>
-      <c r="B180" s="47"/>
+      <c r="A180" s="61"/>
+      <c r="B180" s="61"/>
       <c r="C180" s="22" t="s">
         <v>116</v>
       </c>
@@ -13260,8 +13328,8 @@
       </c>
     </row>
     <row r="181" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="47"/>
-      <c r="B181" s="47"/>
+      <c r="A181" s="61"/>
+      <c r="B181" s="61"/>
       <c r="C181" s="22" t="s">
         <v>117</v>
       </c>
@@ -13306,8 +13374,8 @@
       </c>
     </row>
     <row r="182" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="47"/>
-      <c r="B182" s="47"/>
+      <c r="A182" s="61"/>
+      <c r="B182" s="61"/>
       <c r="C182" s="22" t="s">
         <v>118</v>
       </c>
@@ -13352,8 +13420,8 @@
       </c>
     </row>
     <row r="183" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="47"/>
-      <c r="B183" s="47"/>
+      <c r="A183" s="61"/>
+      <c r="B183" s="61"/>
       <c r="C183" s="22" t="s">
         <v>119</v>
       </c>
@@ -13402,8 +13470,8 @@
       </c>
     </row>
     <row r="184" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="47"/>
-      <c r="B184" s="47"/>
+      <c r="A184" s="61"/>
+      <c r="B184" s="61"/>
       <c r="C184" s="22" t="s">
         <v>120</v>
       </c>
@@ -13448,8 +13516,8 @@
       </c>
     </row>
     <row r="185" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="48"/>
-      <c r="B185" s="48"/>
+      <c r="A185" s="60"/>
+      <c r="B185" s="60"/>
       <c r="C185" s="22" t="s">
         <v>121</v>
       </c>
@@ -13494,27 +13562,27 @@
       </c>
     </row>
     <row r="186" spans="1:17" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="46">
+      <c r="A186" s="59">
         <v>23</v>
       </c>
-      <c r="B186" s="46" t="s">
+      <c r="B186" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="C186" s="51" t="str">
+      <c r="C186" s="55" t="str">
         <f>IF(O180:O186="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N183&gt;3, N185&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D186" s="52"/>
-      <c r="E186" s="52"/>
-      <c r="F186" s="52"/>
-      <c r="G186" s="52"/>
-      <c r="H186" s="52"/>
-      <c r="I186" s="52"/>
-      <c r="J186" s="52"/>
-      <c r="K186" s="52"/>
-      <c r="L186" s="52"/>
+      <c r="D186" s="56"/>
+      <c r="E186" s="56"/>
+      <c r="F186" s="56"/>
+      <c r="G186" s="56"/>
+      <c r="H186" s="56"/>
+      <c r="I186" s="56"/>
+      <c r="J186" s="56"/>
+      <c r="K186" s="56"/>
+      <c r="L186" s="56"/>
       <c r="N186" s="29">
         <f>AVERAGE(D183:L185)</f>
         <v>5</v>
@@ -13526,8 +13594,8 @@
       </c>
     </row>
     <row r="187" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="47"/>
-      <c r="B187" s="47"/>
+      <c r="A187" s="61"/>
+      <c r="B187" s="61"/>
       <c r="C187" s="22" t="s">
         <v>114</v>
       </c>
@@ -13568,8 +13636,8 @@
       </c>
     </row>
     <row r="188" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="47"/>
-      <c r="B188" s="47"/>
+      <c r="A188" s="61"/>
+      <c r="B188" s="61"/>
       <c r="C188" s="22" t="s">
         <v>116</v>
       </c>
@@ -13614,8 +13682,8 @@
       </c>
     </row>
     <row r="189" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="47"/>
-      <c r="B189" s="47"/>
+      <c r="A189" s="61"/>
+      <c r="B189" s="61"/>
       <c r="C189" s="22" t="s">
         <v>117</v>
       </c>
@@ -13660,8 +13728,8 @@
       </c>
     </row>
     <row r="190" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="47"/>
-      <c r="B190" s="47"/>
+      <c r="A190" s="61"/>
+      <c r="B190" s="61"/>
       <c r="C190" s="22" t="s">
         <v>118</v>
       </c>
@@ -13706,8 +13774,8 @@
       </c>
     </row>
     <row r="191" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="47"/>
-      <c r="B191" s="47"/>
+      <c r="A191" s="61"/>
+      <c r="B191" s="61"/>
       <c r="C191" s="22" t="s">
         <v>119</v>
       </c>
@@ -13756,8 +13824,8 @@
       </c>
     </row>
     <row r="192" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="47"/>
-      <c r="B192" s="47"/>
+      <c r="A192" s="61"/>
+      <c r="B192" s="61"/>
       <c r="C192" s="22" t="s">
         <v>120</v>
       </c>
@@ -13802,8 +13870,8 @@
       </c>
     </row>
     <row r="193" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="48"/>
-      <c r="B193" s="48"/>
+      <c r="A193" s="60"/>
+      <c r="B193" s="60"/>
       <c r="C193" s="22" t="s">
         <v>121</v>
       </c>
@@ -13848,27 +13916,27 @@
       </c>
     </row>
     <row r="194" spans="1:17" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="46">
+      <c r="A194" s="59">
         <v>24</v>
       </c>
-      <c r="B194" s="46" t="s">
+      <c r="B194" s="59" t="s">
         <v>144</v>
       </c>
-      <c r="C194" s="51" t="str">
+      <c r="C194" s="55" t="str">
         <f>IF(O188:O194="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N191&gt;3, N193&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D194" s="52"/>
-      <c r="E194" s="52"/>
-      <c r="F194" s="52"/>
-      <c r="G194" s="52"/>
-      <c r="H194" s="52"/>
-      <c r="I194" s="52"/>
-      <c r="J194" s="52"/>
-      <c r="K194" s="52"/>
-      <c r="L194" s="52"/>
+      <c r="D194" s="56"/>
+      <c r="E194" s="56"/>
+      <c r="F194" s="56"/>
+      <c r="G194" s="56"/>
+      <c r="H194" s="56"/>
+      <c r="I194" s="56"/>
+      <c r="J194" s="56"/>
+      <c r="K194" s="56"/>
+      <c r="L194" s="56"/>
       <c r="N194" s="29">
         <f>AVERAGE(D191:L193)</f>
         <v>4.0909090909090908</v>
@@ -13880,8 +13948,8 @@
       </c>
     </row>
     <row r="195" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="47"/>
-      <c r="B195" s="47"/>
+      <c r="A195" s="61"/>
+      <c r="B195" s="61"/>
       <c r="C195" s="22" t="s">
         <v>114</v>
       </c>
@@ -13922,8 +13990,8 @@
       </c>
     </row>
     <row r="196" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="47"/>
-      <c r="B196" s="47"/>
+      <c r="A196" s="61"/>
+      <c r="B196" s="61"/>
       <c r="C196" s="22" t="s">
         <v>116</v>
       </c>
@@ -13968,8 +14036,8 @@
       </c>
     </row>
     <row r="197" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="47"/>
-      <c r="B197" s="47"/>
+      <c r="A197" s="61"/>
+      <c r="B197" s="61"/>
       <c r="C197" s="22" t="s">
         <v>117</v>
       </c>
@@ -14014,8 +14082,8 @@
       </c>
     </row>
     <row r="198" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="47"/>
-      <c r="B198" s="47"/>
+      <c r="A198" s="61"/>
+      <c r="B198" s="61"/>
       <c r="C198" s="22" t="s">
         <v>118</v>
       </c>
@@ -14060,8 +14128,8 @@
       </c>
     </row>
     <row r="199" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="47"/>
-      <c r="B199" s="47"/>
+      <c r="A199" s="61"/>
+      <c r="B199" s="61"/>
       <c r="C199" s="22" t="s">
         <v>119</v>
       </c>
@@ -14110,8 +14178,8 @@
       </c>
     </row>
     <row r="200" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="47"/>
-      <c r="B200" s="47"/>
+      <c r="A200" s="61"/>
+      <c r="B200" s="61"/>
       <c r="C200" s="22" t="s">
         <v>120</v>
       </c>
@@ -14156,8 +14224,8 @@
       </c>
     </row>
     <row r="201" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="48"/>
-      <c r="B201" s="48"/>
+      <c r="A201" s="60"/>
+      <c r="B201" s="60"/>
       <c r="C201" s="22" t="s">
         <v>121</v>
       </c>
@@ -14202,27 +14270,27 @@
       </c>
     </row>
     <row r="202" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="46">
+      <c r="A202" s="59">
         <v>25</v>
       </c>
-      <c r="B202" s="46" t="s">
+      <c r="B202" s="59" t="s">
         <v>145</v>
       </c>
-      <c r="C202" s="51" t="str">
+      <c r="C202" s="55" t="str">
         <f>IF(O196:O202="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N199&gt;3, N201&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D202" s="52"/>
-      <c r="E202" s="52"/>
-      <c r="F202" s="52"/>
-      <c r="G202" s="52"/>
-      <c r="H202" s="52"/>
-      <c r="I202" s="52"/>
-      <c r="J202" s="52"/>
-      <c r="K202" s="52"/>
-      <c r="L202" s="52"/>
+      <c r="D202" s="56"/>
+      <c r="E202" s="56"/>
+      <c r="F202" s="56"/>
+      <c r="G202" s="56"/>
+      <c r="H202" s="56"/>
+      <c r="I202" s="56"/>
+      <c r="J202" s="56"/>
+      <c r="K202" s="56"/>
+      <c r="L202" s="56"/>
       <c r="N202" s="29">
         <f>AVERAGE(D199:L201)</f>
         <v>5</v>
@@ -14234,8 +14302,8 @@
       </c>
     </row>
     <row r="203" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="47"/>
-      <c r="B203" s="47"/>
+      <c r="A203" s="61"/>
+      <c r="B203" s="61"/>
       <c r="C203" s="22" t="s">
         <v>114</v>
       </c>
@@ -14276,8 +14344,8 @@
       </c>
     </row>
     <row r="204" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="47"/>
-      <c r="B204" s="47"/>
+      <c r="A204" s="61"/>
+      <c r="B204" s="61"/>
       <c r="C204" s="22" t="s">
         <v>116</v>
       </c>
@@ -14322,8 +14390,8 @@
       </c>
     </row>
     <row r="205" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="47"/>
-      <c r="B205" s="47"/>
+      <c r="A205" s="61"/>
+      <c r="B205" s="61"/>
       <c r="C205" s="22" t="s">
         <v>117</v>
       </c>
@@ -14368,8 +14436,8 @@
       </c>
     </row>
     <row r="206" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="47"/>
-      <c r="B206" s="47"/>
+      <c r="A206" s="61"/>
+      <c r="B206" s="61"/>
       <c r="C206" s="22" t="s">
         <v>118</v>
       </c>
@@ -14414,8 +14482,8 @@
       </c>
     </row>
     <row r="207" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="47"/>
-      <c r="B207" s="47"/>
+      <c r="A207" s="61"/>
+      <c r="B207" s="61"/>
       <c r="C207" s="22" t="s">
         <v>119</v>
       </c>
@@ -14464,8 +14532,8 @@
       </c>
     </row>
     <row r="208" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="47"/>
-      <c r="B208" s="47"/>
+      <c r="A208" s="61"/>
+      <c r="B208" s="61"/>
       <c r="C208" s="22" t="s">
         <v>120</v>
       </c>
@@ -14510,8 +14578,8 @@
       </c>
     </row>
     <row r="209" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="48"/>
-      <c r="B209" s="47"/>
+      <c r="A209" s="60"/>
+      <c r="B209" s="61"/>
       <c r="C209" s="35" t="s">
         <v>121</v>
       </c>
@@ -14574,24 +14642,24 @@
       <c r="A211" s="31">
         <v>26</v>
       </c>
-      <c r="B211" s="47" t="s">
+      <c r="B211" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="C211" s="51" t="str">
+      <c r="C211" s="55" t="str">
         <f>IF(O205:O211="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N208&gt;3, N210&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D211" s="52"/>
-      <c r="E211" s="52"/>
-      <c r="F211" s="52"/>
-      <c r="G211" s="52"/>
-      <c r="H211" s="52"/>
-      <c r="I211" s="52"/>
-      <c r="J211" s="52"/>
-      <c r="K211" s="52"/>
-      <c r="L211" s="52"/>
+      <c r="D211" s="56"/>
+      <c r="E211" s="56"/>
+      <c r="F211" s="56"/>
+      <c r="G211" s="56"/>
+      <c r="H211" s="56"/>
+      <c r="I211" s="56"/>
+      <c r="J211" s="56"/>
+      <c r="K211" s="56"/>
+      <c r="L211" s="56"/>
       <c r="N211" s="29">
         <f>AVERAGE(D207:L209)</f>
         <v>4.1818181818181817</v>
@@ -14604,7 +14672,7 @@
     </row>
     <row r="212" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="32"/>
-      <c r="B212" s="47"/>
+      <c r="B212" s="61"/>
       <c r="C212" s="22" t="s">
         <v>114</v>
       </c>
@@ -14646,7 +14714,7 @@
     </row>
     <row r="213" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="32"/>
-      <c r="B213" s="47"/>
+      <c r="B213" s="61"/>
       <c r="C213" s="22" t="s">
         <v>116</v>
       </c>
@@ -14693,7 +14761,7 @@
     </row>
     <row r="214" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="32"/>
-      <c r="B214" s="47"/>
+      <c r="B214" s="61"/>
       <c r="C214" s="22" t="s">
         <v>117</v>
       </c>
@@ -14740,7 +14808,7 @@
     </row>
     <row r="215" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="32"/>
-      <c r="B215" s="47"/>
+      <c r="B215" s="61"/>
       <c r="C215" s="22" t="s">
         <v>118</v>
       </c>
@@ -14786,7 +14854,7 @@
     </row>
     <row r="216" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="32"/>
-      <c r="B216" s="47"/>
+      <c r="B216" s="61"/>
       <c r="C216" s="22" t="s">
         <v>119</v>
       </c>
@@ -14836,7 +14904,7 @@
     </row>
     <row r="217" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="32"/>
-      <c r="B217" s="47"/>
+      <c r="B217" s="61"/>
       <c r="C217" s="22" t="s">
         <v>120</v>
       </c>
@@ -14874,7 +14942,7 @@
     </row>
     <row r="218" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="33"/>
-      <c r="B218" s="48"/>
+      <c r="B218" s="60"/>
       <c r="C218" s="22" t="s">
         <v>121</v>
       </c>
@@ -14911,21 +14979,21 @@
       </c>
     </row>
     <row r="219" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C219" s="51" t="str">
+      <c r="C219" s="55" t="str">
         <f>IF(O213:O219="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N216&gt;3, N218&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D219" s="52"/>
-      <c r="E219" s="52"/>
-      <c r="F219" s="52"/>
-      <c r="G219" s="52"/>
-      <c r="H219" s="52"/>
-      <c r="I219" s="52"/>
-      <c r="J219" s="52"/>
-      <c r="K219" s="52"/>
-      <c r="L219" s="52"/>
+      <c r="D219" s="56"/>
+      <c r="E219" s="56"/>
+      <c r="F219" s="56"/>
+      <c r="G219" s="56"/>
+      <c r="H219" s="56"/>
+      <c r="I219" s="56"/>
+      <c r="J219" s="56"/>
+      <c r="K219" s="56"/>
+      <c r="L219" s="56"/>
       <c r="N219" s="29">
         <f>SUM(N216)</f>
         <v>0</v>
@@ -14983,33 +15051,57 @@
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="C211:L211"/>
-    <mergeCell ref="C219:L219"/>
-    <mergeCell ref="C170:L170"/>
-    <mergeCell ref="C178:L178"/>
-    <mergeCell ref="C186:L186"/>
-    <mergeCell ref="C194:L194"/>
-    <mergeCell ref="C202:L202"/>
-    <mergeCell ref="C130:L130"/>
-    <mergeCell ref="C138:L138"/>
-    <mergeCell ref="C146:L146"/>
-    <mergeCell ref="C154:L154"/>
-    <mergeCell ref="C162:L162"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C106:L106"/>
-    <mergeCell ref="C114:L114"/>
-    <mergeCell ref="C122:L122"/>
-    <mergeCell ref="C50:L50"/>
-    <mergeCell ref="C58:L58"/>
-    <mergeCell ref="C66:L66"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C82:L82"/>
-    <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C10:L10"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="C34:L34"/>
-    <mergeCell ref="C42:L42"/>
+    <mergeCell ref="A202:A209"/>
+    <mergeCell ref="B202:B209"/>
+    <mergeCell ref="B211:B218"/>
+    <mergeCell ref="A178:A185"/>
+    <mergeCell ref="B178:B185"/>
+    <mergeCell ref="A186:A193"/>
+    <mergeCell ref="B186:B193"/>
+    <mergeCell ref="A194:A201"/>
+    <mergeCell ref="B194:B201"/>
+    <mergeCell ref="A154:A161"/>
+    <mergeCell ref="B154:B161"/>
+    <mergeCell ref="A162:A169"/>
+    <mergeCell ref="B162:B169"/>
+    <mergeCell ref="A170:A177"/>
+    <mergeCell ref="B170:B177"/>
+    <mergeCell ref="A130:A137"/>
+    <mergeCell ref="B130:B137"/>
+    <mergeCell ref="A138:A145"/>
+    <mergeCell ref="B138:B145"/>
+    <mergeCell ref="A146:A153"/>
+    <mergeCell ref="B146:B153"/>
+    <mergeCell ref="A106:A113"/>
+    <mergeCell ref="B106:B113"/>
+    <mergeCell ref="A114:A121"/>
+    <mergeCell ref="B114:B121"/>
+    <mergeCell ref="A122:A129"/>
+    <mergeCell ref="B122:B129"/>
+    <mergeCell ref="A82:A89"/>
+    <mergeCell ref="B82:B89"/>
+    <mergeCell ref="A90:A97"/>
+    <mergeCell ref="B90:B97"/>
+    <mergeCell ref="A98:A105"/>
+    <mergeCell ref="B98:B105"/>
+    <mergeCell ref="A58:A65"/>
+    <mergeCell ref="B58:B65"/>
+    <mergeCell ref="A66:A73"/>
+    <mergeCell ref="B66:B73"/>
+    <mergeCell ref="A74:A81"/>
+    <mergeCell ref="B74:B81"/>
+    <mergeCell ref="A34:A41"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="A42:A49"/>
+    <mergeCell ref="B42:B49"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="B50:B57"/>
+    <mergeCell ref="A10:A17"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="A18:A25"/>
+    <mergeCell ref="B18:B25"/>
+    <mergeCell ref="A26:A33"/>
+    <mergeCell ref="B26:B33"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="H8:H9"/>
     <mergeCell ref="J8:J9"/>
@@ -15019,57 +15111,33 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A10:A17"/>
-    <mergeCell ref="B10:B17"/>
-    <mergeCell ref="A18:A25"/>
-    <mergeCell ref="B18:B25"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="A34:A41"/>
-    <mergeCell ref="B34:B41"/>
-    <mergeCell ref="A42:A49"/>
-    <mergeCell ref="B42:B49"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="B50:B57"/>
-    <mergeCell ref="A58:A65"/>
-    <mergeCell ref="B58:B65"/>
-    <mergeCell ref="A66:A73"/>
-    <mergeCell ref="B66:B73"/>
-    <mergeCell ref="A74:A81"/>
-    <mergeCell ref="B74:B81"/>
-    <mergeCell ref="A82:A89"/>
-    <mergeCell ref="B82:B89"/>
-    <mergeCell ref="A90:A97"/>
-    <mergeCell ref="B90:B97"/>
-    <mergeCell ref="A98:A105"/>
-    <mergeCell ref="B98:B105"/>
-    <mergeCell ref="A106:A113"/>
-    <mergeCell ref="B106:B113"/>
-    <mergeCell ref="A114:A121"/>
-    <mergeCell ref="B114:B121"/>
-    <mergeCell ref="A122:A129"/>
-    <mergeCell ref="B122:B129"/>
-    <mergeCell ref="A130:A137"/>
-    <mergeCell ref="B130:B137"/>
-    <mergeCell ref="A138:A145"/>
-    <mergeCell ref="B138:B145"/>
-    <mergeCell ref="A146:A153"/>
-    <mergeCell ref="B146:B153"/>
-    <mergeCell ref="A154:A161"/>
-    <mergeCell ref="B154:B161"/>
-    <mergeCell ref="A162:A169"/>
-    <mergeCell ref="B162:B169"/>
-    <mergeCell ref="A170:A177"/>
-    <mergeCell ref="B170:B177"/>
-    <mergeCell ref="A202:A209"/>
-    <mergeCell ref="B202:B209"/>
-    <mergeCell ref="B211:B218"/>
-    <mergeCell ref="A178:A185"/>
-    <mergeCell ref="B178:B185"/>
-    <mergeCell ref="A186:A193"/>
-    <mergeCell ref="B186:B193"/>
-    <mergeCell ref="A194:A201"/>
-    <mergeCell ref="B194:B201"/>
+    <mergeCell ref="C18:L18"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C42:L42"/>
+    <mergeCell ref="C50:L50"/>
+    <mergeCell ref="C58:L58"/>
+    <mergeCell ref="C66:L66"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C106:L106"/>
+    <mergeCell ref="C114:L114"/>
+    <mergeCell ref="C122:L122"/>
+    <mergeCell ref="C130:L130"/>
+    <mergeCell ref="C138:L138"/>
+    <mergeCell ref="C146:L146"/>
+    <mergeCell ref="C154:L154"/>
+    <mergeCell ref="C162:L162"/>
+    <mergeCell ref="C211:L211"/>
+    <mergeCell ref="C219:L219"/>
+    <mergeCell ref="C170:L170"/>
+    <mergeCell ref="C178:L178"/>
+    <mergeCell ref="C186:L186"/>
+    <mergeCell ref="C194:L194"/>
+    <mergeCell ref="C202:L202"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/reiting.xlsx
+++ b/reiting.xlsx
@@ -1118,11 +1118,18 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1131,18 +1138,11 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1559,43 +1559,43 @@
       <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54" t="s">
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="54" t="s">
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="54"/>
-      <c r="V3" s="54"/>
-      <c r="W3" s="54"/>
-      <c r="X3" s="54"/>
-      <c r="Y3" s="54"/>
-      <c r="Z3" s="54"/>
-      <c r="AA3" s="54" t="s">
+      <c r="U3" s="56"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="56"/>
+      <c r="Y3" s="56"/>
+      <c r="Z3" s="56"/>
+      <c r="AA3" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="AB3" s="54"/>
-      <c r="AC3" s="54"/>
-      <c r="AD3" s="54"/>
-      <c r="AE3" s="54"/>
+      <c r="AB3" s="56"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="56"/>
     </row>
     <row r="4" spans="1:32" s="2" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
@@ -2740,10 +2740,12 @@
       <c r="AD1" s="3"/>
     </row>
     <row r="2" spans="1:30" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="63"/>
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -2772,10 +2774,12 @@
       <c r="AD2" s="3"/>
     </row>
     <row r="3" spans="1:30" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="63"/>
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -2805,7 +2809,7 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="45" t="s">
         <v>153</v>
@@ -2875,7 +2879,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="45" t="s">
         <v>154</v>
@@ -2939,7 +2943,7 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="45" t="s">
         <v>155</v>
@@ -3001,7 +3005,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="45" t="s">
         <v>156</v>
@@ -3065,7 +3069,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="47" t="s">
         <v>157</v>
@@ -3129,7 +3133,7 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="45" t="s">
         <v>158</v>
@@ -3193,7 +3197,7 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="47" t="s">
         <v>159</v>
@@ -3257,7 +3261,7 @@
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="45" t="s">
         <v>160</v>
@@ -3321,7 +3325,7 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="45" t="s">
         <v>161</v>
@@ -3385,7 +3389,7 @@
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="48" t="s">
         <v>162</v>
@@ -3449,7 +3453,7 @@
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="49" t="s">
         <v>163</v>
@@ -3513,7 +3517,7 @@
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="47" t="s">
         <v>164</v>
@@ -3577,7 +3581,7 @@
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="47" t="s">
         <v>165</v>
@@ -3641,7 +3645,7 @@
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="47" t="s">
         <v>166</v>
@@ -3705,7 +3709,7 @@
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" s="50" t="s">
         <v>167</v>
@@ -3769,7 +3773,7 @@
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="47" t="s">
         <v>168</v>
@@ -3833,7 +3837,7 @@
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="45" t="s">
         <v>169</v>
@@ -3897,7 +3901,7 @@
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="45" t="s">
         <v>171</v>
@@ -3961,7 +3965,7 @@
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" s="47" t="s">
         <v>173</v>
@@ -4025,7 +4029,7 @@
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" s="49" t="s">
         <v>174</v>
@@ -4089,7 +4093,7 @@
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B24" s="45" t="s">
         <v>176</v>
@@ -4153,7 +4157,7 @@
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="45" t="s">
         <v>177</v>
@@ -4217,7 +4221,7 @@
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B26" s="47" t="s">
         <v>178</v>
@@ -4281,7 +4285,7 @@
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B27" s="47" t="s">
         <v>179</v>
@@ -4345,7 +4349,7 @@
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" s="45" t="s">
         <v>180</v>
@@ -4409,7 +4413,7 @@
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" s="47" t="s">
         <v>181</v>
@@ -4473,7 +4477,7 @@
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B30" s="45" t="s">
         <v>182</v>
@@ -4537,7 +4541,7 @@
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" s="45" t="s">
         <v>184</v>
@@ -4601,7 +4605,7 @@
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" s="45" t="s">
         <v>185</v>
@@ -4665,7 +4669,7 @@
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" s="45" t="s">
         <v>187</v>
@@ -4729,7 +4733,7 @@
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34" s="45" t="s">
         <v>188</v>
@@ -4793,7 +4797,7 @@
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35" s="45" t="s">
         <v>189</v>
@@ -4857,7 +4861,7 @@
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B36" s="45" t="s">
         <v>190</v>
@@ -4921,7 +4925,7 @@
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" s="45" t="s">
         <v>191</v>
@@ -4985,7 +4989,7 @@
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="45" t="s">
         <v>193</v>
@@ -5048,9 +5052,6 @@
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
-        <v>36</v>
-      </c>
       <c r="B39" s="45" t="s">
         <v>195</v>
       </c>
@@ -5112,9 +5113,6 @@
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
-        <v>37</v>
-      </c>
       <c r="B40" s="45" t="s">
         <v>197</v>
       </c>
@@ -5805,84 +5803,84 @@
     </row>
     <row r="7" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="8" spans="1:18" ht="56.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="57" t="s">
         <v>103</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="57" t="s">
+      <c r="E8" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="57" t="s">
+      <c r="F8" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="57" t="s">
+      <c r="G8" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="H8" s="57" t="s">
+      <c r="H8" s="60" t="s">
         <v>107</v>
       </c>
       <c r="I8" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="J8" s="57" t="s">
+      <c r="J8" s="60" t="s">
         <v>5</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="L8" s="57" t="s">
+      <c r="L8" s="60" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
       <c r="I9" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="J9" s="58"/>
+      <c r="J9" s="61"/>
       <c r="K9" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="L9" s="58"/>
+      <c r="L9" s="61"/>
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="59">
+      <c r="A10" s="57">
         <v>1</v>
       </c>
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="63"/>
     </row>
     <row r="11" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="61"/>
-      <c r="B11" s="61"/>
+      <c r="A11" s="58"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="22" t="s">
         <v>114</v>
       </c>
@@ -5924,8 +5922,8 @@
       <c r="P11" s="4"/>
     </row>
     <row r="12" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="61"/>
-      <c r="B12" s="61"/>
+      <c r="A12" s="58"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="22" t="s">
         <v>116</v>
       </c>
@@ -5971,8 +5969,8 @@
       <c r="P12" s="4"/>
     </row>
     <row r="13" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="61"/>
-      <c r="B13" s="61"/>
+      <c r="A13" s="58"/>
+      <c r="B13" s="58"/>
       <c r="C13" s="22" t="s">
         <v>117</v>
       </c>
@@ -6017,8 +6015,8 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="61"/>
-      <c r="B14" s="61"/>
+      <c r="A14" s="58"/>
+      <c r="B14" s="58"/>
       <c r="C14" s="22" t="s">
         <v>118</v>
       </c>
@@ -6063,8 +6061,8 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="61"/>
-      <c r="B15" s="61"/>
+      <c r="A15" s="58"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="22" t="s">
         <v>119</v>
       </c>
@@ -6114,8 +6112,8 @@
       <c r="R15" s="39"/>
     </row>
     <row r="16" spans="1:18" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="61"/>
-      <c r="B16" s="61"/>
+      <c r="A16" s="58"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="22" t="s">
         <v>120</v>
       </c>
@@ -6161,8 +6159,8 @@
       <c r="R16" s="39"/>
     </row>
     <row r="17" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="60"/>
-      <c r="B17" s="60"/>
+      <c r="A17" s="59"/>
+      <c r="B17" s="59"/>
       <c r="C17" s="22" t="s">
         <v>121</v>
       </c>
@@ -6213,27 +6211,27 @@
       </c>
     </row>
     <row r="18" spans="1:17" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="59">
+      <c r="A18" s="57">
         <v>2</v>
       </c>
-      <c r="B18" s="59" t="s">
+      <c r="B18" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="55" t="str">
+      <c r="C18" s="62" t="str">
         <f>IF(O12:O18="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N15&gt;3, N17&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="56"/>
-      <c r="K18" s="56"/>
-      <c r="L18" s="56"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="63"/>
       <c r="N18" s="29">
         <v>3</v>
       </c>
@@ -6250,8 +6248,8 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="61"/>
-      <c r="B19" s="61"/>
+      <c r="A19" s="58"/>
+      <c r="B19" s="58"/>
       <c r="C19" s="22" t="s">
         <v>114</v>
       </c>
@@ -6292,8 +6290,8 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="61"/>
-      <c r="B20" s="61"/>
+      <c r="A20" s="58"/>
+      <c r="B20" s="58"/>
       <c r="C20" s="22" t="s">
         <v>116</v>
       </c>
@@ -6338,8 +6336,8 @@
       </c>
     </row>
     <row r="21" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="61"/>
-      <c r="B21" s="61"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
       <c r="C21" s="22" t="s">
         <v>117</v>
       </c>
@@ -6384,8 +6382,8 @@
       </c>
     </row>
     <row r="22" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="61"/>
-      <c r="B22" s="61"/>
+      <c r="A22" s="58"/>
+      <c r="B22" s="58"/>
       <c r="C22" s="22" t="s">
         <v>118</v>
       </c>
@@ -6430,8 +6428,8 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="61"/>
-      <c r="B23" s="61"/>
+      <c r="A23" s="58"/>
+      <c r="B23" s="58"/>
       <c r="C23" s="22" t="s">
         <v>119</v>
       </c>
@@ -6480,8 +6478,8 @@
       </c>
     </row>
     <row r="24" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="61"/>
-      <c r="B24" s="61"/>
+      <c r="A24" s="58"/>
+      <c r="B24" s="58"/>
       <c r="C24" s="22" t="s">
         <v>120</v>
       </c>
@@ -6526,8 +6524,8 @@
       </c>
     </row>
     <row r="25" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="60"/>
-      <c r="B25" s="60"/>
+      <c r="A25" s="59"/>
+      <c r="B25" s="59"/>
       <c r="C25" s="22" t="s">
         <v>121</v>
       </c>
@@ -6572,27 +6570,27 @@
       </c>
     </row>
     <row r="26" spans="1:17" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="59">
+      <c r="A26" s="57">
         <v>3</v>
       </c>
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="55" t="str">
+      <c r="C26" s="62" t="str">
         <f>IF(O20:O26="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N23&gt;3, N25&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="56"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="63"/>
+      <c r="L26" s="63"/>
       <c r="N26" s="29">
         <f>AVERAGE(D23:L25)</f>
         <v>5</v>
@@ -6604,8 +6602,8 @@
       </c>
     </row>
     <row r="27" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="61"/>
-      <c r="B27" s="61"/>
+      <c r="A27" s="58"/>
+      <c r="B27" s="58"/>
       <c r="C27" s="22" t="s">
         <v>114</v>
       </c>
@@ -6646,8 +6644,8 @@
       </c>
     </row>
     <row r="28" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="61"/>
-      <c r="B28" s="61"/>
+      <c r="A28" s="58"/>
+      <c r="B28" s="58"/>
       <c r="C28" s="22" t="s">
         <v>116</v>
       </c>
@@ -6692,8 +6690,8 @@
       </c>
     </row>
     <row r="29" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="61"/>
-      <c r="B29" s="61"/>
+      <c r="A29" s="58"/>
+      <c r="B29" s="58"/>
       <c r="C29" s="22" t="s">
         <v>117</v>
       </c>
@@ -6738,8 +6736,8 @@
       </c>
     </row>
     <row r="30" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="61"/>
-      <c r="B30" s="61"/>
+      <c r="A30" s="58"/>
+      <c r="B30" s="58"/>
       <c r="C30" s="22" t="s">
         <v>118</v>
       </c>
@@ -6784,8 +6782,8 @@
       </c>
     </row>
     <row r="31" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="61"/>
-      <c r="B31" s="61"/>
+      <c r="A31" s="58"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="22" t="s">
         <v>119</v>
       </c>
@@ -6834,8 +6832,8 @@
       </c>
     </row>
     <row r="32" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="61"/>
-      <c r="B32" s="61"/>
+      <c r="A32" s="58"/>
+      <c r="B32" s="58"/>
       <c r="C32" s="22" t="s">
         <v>120</v>
       </c>
@@ -6880,8 +6878,8 @@
       </c>
     </row>
     <row r="33" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="60"/>
-      <c r="B33" s="60"/>
+      <c r="A33" s="59"/>
+      <c r="B33" s="59"/>
       <c r="C33" s="22" t="s">
         <v>121</v>
       </c>
@@ -6926,27 +6924,27 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="59">
-        <v>4</v>
-      </c>
-      <c r="B34" s="59" t="s">
+      <c r="A34" s="57">
+        <v>4</v>
+      </c>
+      <c r="B34" s="57" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="55" t="str">
+      <c r="C34" s="62" t="str">
         <f>IF(O28:O34="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N31&gt;3, N33&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="56"/>
-      <c r="L34" s="56"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="63"/>
+      <c r="J34" s="63"/>
+      <c r="K34" s="63"/>
+      <c r="L34" s="63"/>
       <c r="N34" s="27">
         <f>AVERAGE(D31:L33)</f>
         <v>5</v>
@@ -6958,8 +6956,8 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="61"/>
-      <c r="B35" s="61"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
       <c r="C35" s="22" t="s">
         <v>114</v>
       </c>
@@ -6994,8 +6992,8 @@
       <c r="O35" s="28"/>
     </row>
     <row r="36" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="61"/>
-      <c r="B36" s="61"/>
+      <c r="A36" s="58"/>
+      <c r="B36" s="58"/>
       <c r="C36" s="22" t="s">
         <v>116</v>
       </c>
@@ -7033,8 +7031,8 @@
       </c>
     </row>
     <row r="37" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="61"/>
-      <c r="B37" s="61"/>
+      <c r="A37" s="58"/>
+      <c r="B37" s="58"/>
       <c r="C37" s="22" t="s">
         <v>117</v>
       </c>
@@ -7079,8 +7077,8 @@
       </c>
     </row>
     <row r="38" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="61"/>
-      <c r="B38" s="61"/>
+      <c r="A38" s="58"/>
+      <c r="B38" s="58"/>
       <c r="C38" s="22" t="s">
         <v>118</v>
       </c>
@@ -7118,8 +7116,8 @@
       </c>
     </row>
     <row r="39" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="61"/>
-      <c r="B39" s="61"/>
+      <c r="A39" s="58"/>
+      <c r="B39" s="58"/>
       <c r="C39" s="22" t="s">
         <v>119</v>
       </c>
@@ -7168,8 +7166,8 @@
       </c>
     </row>
     <row r="40" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="61"/>
-      <c r="B40" s="61"/>
+      <c r="A40" s="58"/>
+      <c r="B40" s="58"/>
       <c r="C40" s="22" t="s">
         <v>120</v>
       </c>
@@ -7207,8 +7205,8 @@
       </c>
     </row>
     <row r="41" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="60"/>
-      <c r="B41" s="60"/>
+      <c r="A41" s="59"/>
+      <c r="B41" s="59"/>
       <c r="C41" s="22" t="s">
         <v>121</v>
       </c>
@@ -7246,27 +7244,27 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="59">
-        <v>5</v>
-      </c>
-      <c r="B42" s="59" t="s">
+      <c r="A42" s="57">
+        <v>5</v>
+      </c>
+      <c r="B42" s="57" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="55" t="str">
+      <c r="C42" s="62" t="str">
         <f>IF(O36:O42="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N39&gt;3, N41&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="56"/>
-      <c r="K42" s="56"/>
-      <c r="L42" s="56"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
+      <c r="K42" s="63"/>
+      <c r="L42" s="63"/>
       <c r="N42" s="29">
         <f>AVERAGE(D39:L41)</f>
         <v>3.8888888888888888</v>
@@ -7278,8 +7276,8 @@
       </c>
     </row>
     <row r="43" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="61"/>
-      <c r="B43" s="61"/>
+      <c r="A43" s="58"/>
+      <c r="B43" s="58"/>
       <c r="C43" s="22" t="s">
         <v>114</v>
       </c>
@@ -7320,8 +7318,8 @@
       </c>
     </row>
     <row r="44" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="61"/>
-      <c r="B44" s="61"/>
+      <c r="A44" s="58"/>
+      <c r="B44" s="58"/>
       <c r="C44" s="22" t="s">
         <v>116</v>
       </c>
@@ -7366,8 +7364,8 @@
       </c>
     </row>
     <row r="45" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="61"/>
-      <c r="B45" s="61"/>
+      <c r="A45" s="58"/>
+      <c r="B45" s="58"/>
       <c r="C45" s="22" t="s">
         <v>117</v>
       </c>
@@ -7412,8 +7410,8 @@
       </c>
     </row>
     <row r="46" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="61"/>
-      <c r="B46" s="61"/>
+      <c r="A46" s="58"/>
+      <c r="B46" s="58"/>
       <c r="C46" s="22" t="s">
         <v>118</v>
       </c>
@@ -7458,8 +7456,8 @@
       </c>
     </row>
     <row r="47" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="61"/>
-      <c r="B47" s="61"/>
+      <c r="A47" s="58"/>
+      <c r="B47" s="58"/>
       <c r="C47" s="22" t="s">
         <v>119</v>
       </c>
@@ -7508,8 +7506,8 @@
       </c>
     </row>
     <row r="48" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="61"/>
-      <c r="B48" s="61"/>
+      <c r="A48" s="58"/>
+      <c r="B48" s="58"/>
       <c r="C48" s="22" t="s">
         <v>120</v>
       </c>
@@ -7554,8 +7552,8 @@
       </c>
     </row>
     <row r="49" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="60"/>
-      <c r="B49" s="60"/>
+      <c r="A49" s="59"/>
+      <c r="B49" s="59"/>
       <c r="C49" s="22" t="s">
         <v>121</v>
       </c>
@@ -7600,27 +7598,27 @@
       </c>
     </row>
     <row r="50" spans="1:17" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="59">
+      <c r="A50" s="57">
         <v>6</v>
       </c>
-      <c r="B50" s="59" t="s">
+      <c r="B50" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="C50" s="55" t="str">
+      <c r="C50" s="62" t="str">
         <f>IF(O44:O50="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N47&gt;3, N49&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D50" s="56"/>
-      <c r="E50" s="56"/>
-      <c r="F50" s="56"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="56"/>
-      <c r="I50" s="56"/>
-      <c r="J50" s="56"/>
-      <c r="K50" s="56"/>
-      <c r="L50" s="56"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="63"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="63"/>
+      <c r="J50" s="63"/>
+      <c r="K50" s="63"/>
+      <c r="L50" s="63"/>
       <c r="N50" s="29">
         <f>AVERAGE(D47:L49)</f>
         <v>5</v>
@@ -7632,8 +7630,8 @@
       </c>
     </row>
     <row r="51" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="61"/>
-      <c r="B51" s="61"/>
+      <c r="A51" s="58"/>
+      <c r="B51" s="58"/>
       <c r="C51" s="22" t="s">
         <v>114</v>
       </c>
@@ -7674,8 +7672,8 @@
       </c>
     </row>
     <row r="52" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="61"/>
-      <c r="B52" s="61"/>
+      <c r="A52" s="58"/>
+      <c r="B52" s="58"/>
       <c r="C52" s="22" t="s">
         <v>116</v>
       </c>
@@ -7720,8 +7718,8 @@
       </c>
     </row>
     <row r="53" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="61"/>
-      <c r="B53" s="61"/>
+      <c r="A53" s="58"/>
+      <c r="B53" s="58"/>
       <c r="C53" s="22" t="s">
         <v>117</v>
       </c>
@@ -7766,8 +7764,8 @@
       </c>
     </row>
     <row r="54" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="61"/>
-      <c r="B54" s="61"/>
+      <c r="A54" s="58"/>
+      <c r="B54" s="58"/>
       <c r="C54" s="22" t="s">
         <v>118</v>
       </c>
@@ -7812,8 +7810,8 @@
       </c>
     </row>
     <row r="55" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="61"/>
-      <c r="B55" s="61"/>
+      <c r="A55" s="58"/>
+      <c r="B55" s="58"/>
       <c r="C55" s="22" t="s">
         <v>119</v>
       </c>
@@ -7862,8 +7860,8 @@
       </c>
     </row>
     <row r="56" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="61"/>
-      <c r="B56" s="61"/>
+      <c r="A56" s="58"/>
+      <c r="B56" s="58"/>
       <c r="C56" s="22" t="s">
         <v>120</v>
       </c>
@@ -7908,8 +7906,8 @@
       </c>
     </row>
     <row r="57" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="60"/>
-      <c r="B57" s="60"/>
+      <c r="A57" s="59"/>
+      <c r="B57" s="59"/>
       <c r="C57" s="22" t="s">
         <v>121</v>
       </c>
@@ -7954,27 +7952,27 @@
       </c>
     </row>
     <row r="58" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="59">
+      <c r="A58" s="57">
         <v>7</v>
       </c>
-      <c r="B58" s="59" t="s">
+      <c r="B58" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="C58" s="55" t="str">
+      <c r="C58" s="62" t="str">
         <f>IF(O52:O58="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N55&gt;3, N57&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="56"/>
-      <c r="I58" s="56"/>
-      <c r="J58" s="56"/>
-      <c r="K58" s="56"/>
-      <c r="L58" s="56"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
+      <c r="F58" s="63"/>
+      <c r="G58" s="63"/>
+      <c r="H58" s="63"/>
+      <c r="I58" s="63"/>
+      <c r="J58" s="63"/>
+      <c r="K58" s="63"/>
+      <c r="L58" s="63"/>
       <c r="N58" s="29">
         <f>AVERAGE(D55:L57)</f>
         <v>5</v>
@@ -7986,8 +7984,8 @@
       </c>
     </row>
     <row r="59" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="61"/>
-      <c r="B59" s="61"/>
+      <c r="A59" s="58"/>
+      <c r="B59" s="58"/>
       <c r="C59" s="22" t="s">
         <v>114</v>
       </c>
@@ -8028,8 +8026,8 @@
       </c>
     </row>
     <row r="60" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="61"/>
-      <c r="B60" s="61"/>
+      <c r="A60" s="58"/>
+      <c r="B60" s="58"/>
       <c r="C60" s="22" t="s">
         <v>116</v>
       </c>
@@ -8074,8 +8072,8 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="61"/>
-      <c r="B61" s="61"/>
+      <c r="A61" s="58"/>
+      <c r="B61" s="58"/>
       <c r="C61" s="22" t="s">
         <v>117</v>
       </c>
@@ -8120,8 +8118,8 @@
       </c>
     </row>
     <row r="62" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="61"/>
-      <c r="B62" s="61"/>
+      <c r="A62" s="58"/>
+      <c r="B62" s="58"/>
       <c r="C62" s="22" t="s">
         <v>118</v>
       </c>
@@ -8166,8 +8164,8 @@
       </c>
     </row>
     <row r="63" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="61"/>
-      <c r="B63" s="61"/>
+      <c r="A63" s="58"/>
+      <c r="B63" s="58"/>
       <c r="C63" s="22" t="s">
         <v>119</v>
       </c>
@@ -8216,8 +8214,8 @@
       </c>
     </row>
     <row r="64" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="61"/>
-      <c r="B64" s="61"/>
+      <c r="A64" s="58"/>
+      <c r="B64" s="58"/>
       <c r="C64" s="22" t="s">
         <v>120</v>
       </c>
@@ -8262,8 +8260,8 @@
       </c>
     </row>
     <row r="65" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="60"/>
-      <c r="B65" s="60"/>
+      <c r="A65" s="59"/>
+      <c r="B65" s="59"/>
       <c r="C65" s="22" t="s">
         <v>121</v>
       </c>
@@ -8308,27 +8306,27 @@
       </c>
     </row>
     <row r="66" spans="1:17" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="59">
+      <c r="A66" s="57">
         <v>8</v>
       </c>
-      <c r="B66" s="59" t="s">
+      <c r="B66" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="C66" s="55" t="str">
+      <c r="C66" s="62" t="str">
         <f>IF(O60:O66="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N63&gt;3, N65&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D66" s="56"/>
-      <c r="E66" s="56"/>
-      <c r="F66" s="56"/>
-      <c r="G66" s="56"/>
-      <c r="H66" s="56"/>
-      <c r="I66" s="56"/>
-      <c r="J66" s="56"/>
-      <c r="K66" s="56"/>
-      <c r="L66" s="56"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="63"/>
+      <c r="F66" s="63"/>
+      <c r="G66" s="63"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="63"/>
+      <c r="J66" s="63"/>
+      <c r="K66" s="63"/>
+      <c r="L66" s="63"/>
       <c r="N66" s="29">
         <f>AVERAGE(D63:L65)</f>
         <v>4</v>
@@ -8340,8 +8338,8 @@
       </c>
     </row>
     <row r="67" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="61"/>
-      <c r="B67" s="61"/>
+      <c r="A67" s="58"/>
+      <c r="B67" s="58"/>
       <c r="C67" s="22" t="s">
         <v>114</v>
       </c>
@@ -8382,8 +8380,8 @@
       </c>
     </row>
     <row r="68" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="61"/>
-      <c r="B68" s="61"/>
+      <c r="A68" s="58"/>
+      <c r="B68" s="58"/>
       <c r="C68" s="22" t="s">
         <v>116</v>
       </c>
@@ -8428,8 +8426,8 @@
       </c>
     </row>
     <row r="69" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="61"/>
-      <c r="B69" s="61"/>
+      <c r="A69" s="58"/>
+      <c r="B69" s="58"/>
       <c r="C69" s="22" t="s">
         <v>117</v>
       </c>
@@ -8474,8 +8472,8 @@
       </c>
     </row>
     <row r="70" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="61"/>
-      <c r="B70" s="61"/>
+      <c r="A70" s="58"/>
+      <c r="B70" s="58"/>
       <c r="C70" s="22" t="s">
         <v>118</v>
       </c>
@@ -8520,8 +8518,8 @@
       </c>
     </row>
     <row r="71" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="61"/>
-      <c r="B71" s="61"/>
+      <c r="A71" s="58"/>
+      <c r="B71" s="58"/>
       <c r="C71" s="22" t="s">
         <v>119</v>
       </c>
@@ -8570,8 +8568,8 @@
       </c>
     </row>
     <row r="72" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="61"/>
-      <c r="B72" s="61"/>
+      <c r="A72" s="58"/>
+      <c r="B72" s="58"/>
       <c r="C72" s="22" t="s">
         <v>120</v>
       </c>
@@ -8616,8 +8614,8 @@
       </c>
     </row>
     <row r="73" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="60"/>
-      <c r="B73" s="60"/>
+      <c r="A73" s="59"/>
+      <c r="B73" s="59"/>
       <c r="C73" s="22" t="s">
         <v>121</v>
       </c>
@@ -8662,27 +8660,27 @@
       </c>
     </row>
     <row r="74" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="59">
+      <c r="A74" s="57">
         <v>9</v>
       </c>
-      <c r="B74" s="59" t="s">
+      <c r="B74" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="C74" s="55" t="str">
+      <c r="C74" s="62" t="str">
         <f>IF(O68:O74="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N71&gt;3, N73&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D74" s="56"/>
-      <c r="E74" s="56"/>
-      <c r="F74" s="56"/>
-      <c r="G74" s="56"/>
-      <c r="H74" s="56"/>
-      <c r="I74" s="56"/>
-      <c r="J74" s="56"/>
-      <c r="K74" s="56"/>
-      <c r="L74" s="56"/>
+      <c r="D74" s="63"/>
+      <c r="E74" s="63"/>
+      <c r="F74" s="63"/>
+      <c r="G74" s="63"/>
+      <c r="H74" s="63"/>
+      <c r="I74" s="63"/>
+      <c r="J74" s="63"/>
+      <c r="K74" s="63"/>
+      <c r="L74" s="63"/>
       <c r="N74" s="29">
         <f>AVERAGE(D71:L73)</f>
         <v>5</v>
@@ -8694,8 +8692,8 @@
       </c>
     </row>
     <row r="75" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="61"/>
-      <c r="B75" s="61"/>
+      <c r="A75" s="58"/>
+      <c r="B75" s="58"/>
       <c r="C75" s="22" t="s">
         <v>114</v>
       </c>
@@ -8736,8 +8734,8 @@
       </c>
     </row>
     <row r="76" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="61"/>
-      <c r="B76" s="61"/>
+      <c r="A76" s="58"/>
+      <c r="B76" s="58"/>
       <c r="C76" s="22" t="s">
         <v>116</v>
       </c>
@@ -8782,8 +8780,8 @@
       </c>
     </row>
     <row r="77" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="61"/>
-      <c r="B77" s="61"/>
+      <c r="A77" s="58"/>
+      <c r="B77" s="58"/>
       <c r="C77" s="22" t="s">
         <v>117</v>
       </c>
@@ -8828,8 +8826,8 @@
       </c>
     </row>
     <row r="78" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="61"/>
-      <c r="B78" s="61"/>
+      <c r="A78" s="58"/>
+      <c r="B78" s="58"/>
       <c r="C78" s="22" t="s">
         <v>118</v>
       </c>
@@ -8874,8 +8872,8 @@
       </c>
     </row>
     <row r="79" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="61"/>
-      <c r="B79" s="61"/>
+      <c r="A79" s="58"/>
+      <c r="B79" s="58"/>
       <c r="C79" s="22" t="s">
         <v>119</v>
       </c>
@@ -8924,8 +8922,8 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="61"/>
-      <c r="B80" s="61"/>
+      <c r="A80" s="58"/>
+      <c r="B80" s="58"/>
       <c r="C80" s="22" t="s">
         <v>120</v>
       </c>
@@ -8970,8 +8968,8 @@
       </c>
     </row>
     <row r="81" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="60"/>
-      <c r="B81" s="60"/>
+      <c r="A81" s="59"/>
+      <c r="B81" s="59"/>
       <c r="C81" s="22" t="s">
         <v>121</v>
       </c>
@@ -9016,27 +9014,27 @@
       </c>
     </row>
     <row r="82" spans="1:17" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="59">
+      <c r="A82" s="57">
         <v>10</v>
       </c>
-      <c r="B82" s="59" t="s">
+      <c r="B82" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="C82" s="55" t="str">
+      <c r="C82" s="62" t="str">
         <f>IF(O76:O82="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N79&gt;3, N81&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D82" s="56"/>
-      <c r="E82" s="56"/>
-      <c r="F82" s="56"/>
-      <c r="G82" s="56"/>
-      <c r="H82" s="56"/>
-      <c r="I82" s="56"/>
-      <c r="J82" s="56"/>
-      <c r="K82" s="56"/>
-      <c r="L82" s="56"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="63"/>
+      <c r="I82" s="63"/>
+      <c r="J82" s="63"/>
+      <c r="K82" s="63"/>
+      <c r="L82" s="63"/>
       <c r="N82" s="29">
         <f>AVERAGE(D79:L81)</f>
         <v>4.2727272727272725</v>
@@ -9048,8 +9046,8 @@
       </c>
     </row>
     <row r="83" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="61"/>
-      <c r="B83" s="61"/>
+      <c r="A83" s="58"/>
+      <c r="B83" s="58"/>
       <c r="C83" s="22" t="s">
         <v>114</v>
       </c>
@@ -9090,8 +9088,8 @@
       </c>
     </row>
     <row r="84" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="61"/>
-      <c r="B84" s="61"/>
+      <c r="A84" s="58"/>
+      <c r="B84" s="58"/>
       <c r="C84" s="22" t="s">
         <v>116</v>
       </c>
@@ -9136,8 +9134,8 @@
       </c>
     </row>
     <row r="85" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="61"/>
-      <c r="B85" s="61"/>
+      <c r="A85" s="58"/>
+      <c r="B85" s="58"/>
       <c r="C85" s="22" t="s">
         <v>117</v>
       </c>
@@ -9182,8 +9180,8 @@
       </c>
     </row>
     <row r="86" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="61"/>
-      <c r="B86" s="61"/>
+      <c r="A86" s="58"/>
+      <c r="B86" s="58"/>
       <c r="C86" s="22" t="s">
         <v>118</v>
       </c>
@@ -9228,8 +9226,8 @@
       </c>
     </row>
     <row r="87" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="61"/>
-      <c r="B87" s="61"/>
+      <c r="A87" s="58"/>
+      <c r="B87" s="58"/>
       <c r="C87" s="22" t="s">
         <v>119</v>
       </c>
@@ -9278,8 +9276,8 @@
       </c>
     </row>
     <row r="88" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="61"/>
-      <c r="B88" s="61"/>
+      <c r="A88" s="58"/>
+      <c r="B88" s="58"/>
       <c r="C88" s="22" t="s">
         <v>120</v>
       </c>
@@ -9324,8 +9322,8 @@
       </c>
     </row>
     <row r="89" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="60"/>
-      <c r="B89" s="60"/>
+      <c r="A89" s="59"/>
+      <c r="B89" s="59"/>
       <c r="C89" s="22" t="s">
         <v>121</v>
       </c>
@@ -9370,27 +9368,27 @@
       </c>
     </row>
     <row r="90" spans="1:17" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="59">
+      <c r="A90" s="57">
         <v>11</v>
       </c>
-      <c r="B90" s="59" t="s">
+      <c r="B90" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="C90" s="55" t="str">
+      <c r="C90" s="62" t="str">
         <f>IF(O84:O90="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N87&gt;3, N89&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D90" s="56"/>
-      <c r="E90" s="56"/>
-      <c r="F90" s="56"/>
-      <c r="G90" s="56"/>
-      <c r="H90" s="56"/>
-      <c r="I90" s="56"/>
-      <c r="J90" s="56"/>
-      <c r="K90" s="56"/>
-      <c r="L90" s="56"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="63"/>
+      <c r="F90" s="63"/>
+      <c r="G90" s="63"/>
+      <c r="H90" s="63"/>
+      <c r="I90" s="63"/>
+      <c r="J90" s="63"/>
+      <c r="K90" s="63"/>
+      <c r="L90" s="63"/>
       <c r="N90" s="29">
         <f>AVERAGE(D87:L89)</f>
         <v>4.2727272727272725</v>
@@ -9402,8 +9400,8 @@
       </c>
     </row>
     <row r="91" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="61"/>
-      <c r="B91" s="61"/>
+      <c r="A91" s="58"/>
+      <c r="B91" s="58"/>
       <c r="C91" s="22" t="s">
         <v>114</v>
       </c>
@@ -9444,8 +9442,8 @@
       </c>
     </row>
     <row r="92" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="61"/>
-      <c r="B92" s="61"/>
+      <c r="A92" s="58"/>
+      <c r="B92" s="58"/>
       <c r="C92" s="22" t="s">
         <v>116</v>
       </c>
@@ -9490,8 +9488,8 @@
       </c>
     </row>
     <row r="93" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="61"/>
-      <c r="B93" s="61"/>
+      <c r="A93" s="58"/>
+      <c r="B93" s="58"/>
       <c r="C93" s="22" t="s">
         <v>117</v>
       </c>
@@ -9536,8 +9534,8 @@
       </c>
     </row>
     <row r="94" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="61"/>
-      <c r="B94" s="61"/>
+      <c r="A94" s="58"/>
+      <c r="B94" s="58"/>
       <c r="C94" s="22" t="s">
         <v>118</v>
       </c>
@@ -9582,8 +9580,8 @@
       </c>
     </row>
     <row r="95" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="61"/>
-      <c r="B95" s="61"/>
+      <c r="A95" s="58"/>
+      <c r="B95" s="58"/>
       <c r="C95" s="22" t="s">
         <v>119</v>
       </c>
@@ -9632,8 +9630,8 @@
       </c>
     </row>
     <row r="96" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="61"/>
-      <c r="B96" s="61"/>
+      <c r="A96" s="58"/>
+      <c r="B96" s="58"/>
       <c r="C96" s="22" t="s">
         <v>120</v>
       </c>
@@ -9678,8 +9676,8 @@
       </c>
     </row>
     <row r="97" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="60"/>
-      <c r="B97" s="60"/>
+      <c r="A97" s="59"/>
+      <c r="B97" s="59"/>
       <c r="C97" s="22" t="s">
         <v>121</v>
       </c>
@@ -9724,27 +9722,27 @@
       </c>
     </row>
     <row r="98" spans="1:17" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="59">
+      <c r="A98" s="57">
         <v>12</v>
       </c>
-      <c r="B98" s="59" t="s">
+      <c r="B98" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="C98" s="55" t="str">
+      <c r="C98" s="62" t="str">
         <f>IF(O92:O98="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N95&gt;3, N97&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D98" s="56"/>
-      <c r="E98" s="56"/>
-      <c r="F98" s="56"/>
-      <c r="G98" s="56"/>
-      <c r="H98" s="56"/>
-      <c r="I98" s="56"/>
-      <c r="J98" s="56"/>
-      <c r="K98" s="56"/>
-      <c r="L98" s="56"/>
+      <c r="D98" s="63"/>
+      <c r="E98" s="63"/>
+      <c r="F98" s="63"/>
+      <c r="G98" s="63"/>
+      <c r="H98" s="63"/>
+      <c r="I98" s="63"/>
+      <c r="J98" s="63"/>
+      <c r="K98" s="63"/>
+      <c r="L98" s="63"/>
       <c r="N98" s="29">
         <f>AVERAGE(D95:L97)</f>
         <v>4</v>
@@ -9756,8 +9754,8 @@
       </c>
     </row>
     <row r="99" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="61"/>
-      <c r="B99" s="61"/>
+      <c r="A99" s="58"/>
+      <c r="B99" s="58"/>
       <c r="C99" s="22" t="s">
         <v>114</v>
       </c>
@@ -9798,8 +9796,8 @@
       </c>
     </row>
     <row r="100" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="61"/>
-      <c r="B100" s="61"/>
+      <c r="A100" s="58"/>
+      <c r="B100" s="58"/>
       <c r="C100" s="22" t="s">
         <v>116</v>
       </c>
@@ -9844,8 +9842,8 @@
       </c>
     </row>
     <row r="101" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="61"/>
-      <c r="B101" s="61"/>
+      <c r="A101" s="58"/>
+      <c r="B101" s="58"/>
       <c r="C101" s="22" t="s">
         <v>117</v>
       </c>
@@ -9890,8 +9888,8 @@
       </c>
     </row>
     <row r="102" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="61"/>
-      <c r="B102" s="61"/>
+      <c r="A102" s="58"/>
+      <c r="B102" s="58"/>
       <c r="C102" s="22" t="s">
         <v>118</v>
       </c>
@@ -9936,8 +9934,8 @@
       </c>
     </row>
     <row r="103" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="61"/>
-      <c r="B103" s="61"/>
+      <c r="A103" s="58"/>
+      <c r="B103" s="58"/>
       <c r="C103" s="22" t="s">
         <v>119</v>
       </c>
@@ -9986,8 +9984,8 @@
       </c>
     </row>
     <row r="104" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="61"/>
-      <c r="B104" s="61"/>
+      <c r="A104" s="58"/>
+      <c r="B104" s="58"/>
       <c r="C104" s="22" t="s">
         <v>120</v>
       </c>
@@ -10032,8 +10030,8 @@
       </c>
     </row>
     <row r="105" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="60"/>
-      <c r="B105" s="60"/>
+      <c r="A105" s="59"/>
+      <c r="B105" s="59"/>
       <c r="C105" s="22" t="s">
         <v>121</v>
       </c>
@@ -10078,27 +10076,27 @@
       </c>
     </row>
     <row r="106" spans="1:17" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="59">
+      <c r="A106" s="57">
         <v>13</v>
       </c>
-      <c r="B106" s="59" t="s">
+      <c r="B106" s="57" t="s">
         <v>133</v>
       </c>
-      <c r="C106" s="55" t="str">
+      <c r="C106" s="62" t="str">
         <f>IF(O100:O106="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N103&gt;3, N105&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D106" s="56"/>
-      <c r="E106" s="56"/>
-      <c r="F106" s="56"/>
-      <c r="G106" s="56"/>
-      <c r="H106" s="56"/>
-      <c r="I106" s="56"/>
-      <c r="J106" s="56"/>
-      <c r="K106" s="56"/>
-      <c r="L106" s="56"/>
+      <c r="D106" s="63"/>
+      <c r="E106" s="63"/>
+      <c r="F106" s="63"/>
+      <c r="G106" s="63"/>
+      <c r="H106" s="63"/>
+      <c r="I106" s="63"/>
+      <c r="J106" s="63"/>
+      <c r="K106" s="63"/>
+      <c r="L106" s="63"/>
       <c r="N106" s="29">
         <f>AVERAGE(D103:L105)</f>
         <v>4.2727272727272725</v>
@@ -10110,8 +10108,8 @@
       </c>
     </row>
     <row r="107" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="61"/>
-      <c r="B107" s="61"/>
+      <c r="A107" s="58"/>
+      <c r="B107" s="58"/>
       <c r="C107" s="22" t="s">
         <v>114</v>
       </c>
@@ -10152,8 +10150,8 @@
       </c>
     </row>
     <row r="108" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="61"/>
-      <c r="B108" s="61"/>
+      <c r="A108" s="58"/>
+      <c r="B108" s="58"/>
       <c r="C108" s="22" t="s">
         <v>116</v>
       </c>
@@ -10198,8 +10196,8 @@
       </c>
     </row>
     <row r="109" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="61"/>
-      <c r="B109" s="61"/>
+      <c r="A109" s="58"/>
+      <c r="B109" s="58"/>
       <c r="C109" s="22" t="s">
         <v>117</v>
       </c>
@@ -10244,8 +10242,8 @@
       </c>
     </row>
     <row r="110" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="61"/>
-      <c r="B110" s="61"/>
+      <c r="A110" s="58"/>
+      <c r="B110" s="58"/>
       <c r="C110" s="22" t="s">
         <v>118</v>
       </c>
@@ -10290,8 +10288,8 @@
       </c>
     </row>
     <row r="111" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="61"/>
-      <c r="B111" s="61"/>
+      <c r="A111" s="58"/>
+      <c r="B111" s="58"/>
       <c r="C111" s="22" t="s">
         <v>119</v>
       </c>
@@ -10340,8 +10338,8 @@
       </c>
     </row>
     <row r="112" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="61"/>
-      <c r="B112" s="61"/>
+      <c r="A112" s="58"/>
+      <c r="B112" s="58"/>
       <c r="C112" s="22" t="s">
         <v>120</v>
       </c>
@@ -10386,8 +10384,8 @@
       </c>
     </row>
     <row r="113" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="60"/>
-      <c r="B113" s="60"/>
+      <c r="A113" s="59"/>
+      <c r="B113" s="59"/>
       <c r="C113" s="22" t="s">
         <v>121</v>
       </c>
@@ -10432,27 +10430,27 @@
       </c>
     </row>
     <row r="114" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="59">
+      <c r="A114" s="57">
         <v>14</v>
       </c>
-      <c r="B114" s="59" t="s">
+      <c r="B114" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="C114" s="55" t="str">
+      <c r="C114" s="62" t="str">
         <f>IF(O108:O114="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N111&gt;3, N113&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D114" s="56"/>
-      <c r="E114" s="56"/>
-      <c r="F114" s="56"/>
-      <c r="G114" s="56"/>
-      <c r="H114" s="56"/>
-      <c r="I114" s="56"/>
-      <c r="J114" s="56"/>
-      <c r="K114" s="56"/>
-      <c r="L114" s="56"/>
+      <c r="D114" s="63"/>
+      <c r="E114" s="63"/>
+      <c r="F114" s="63"/>
+      <c r="G114" s="63"/>
+      <c r="H114" s="63"/>
+      <c r="I114" s="63"/>
+      <c r="J114" s="63"/>
+      <c r="K114" s="63"/>
+      <c r="L114" s="63"/>
       <c r="N114" s="29">
         <f>AVERAGE(D111:L113)</f>
         <v>5</v>
@@ -10464,8 +10462,8 @@
       </c>
     </row>
     <row r="115" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="61"/>
-      <c r="B115" s="61"/>
+      <c r="A115" s="58"/>
+      <c r="B115" s="58"/>
       <c r="C115" s="22" t="s">
         <v>114</v>
       </c>
@@ -10506,8 +10504,8 @@
       </c>
     </row>
     <row r="116" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="61"/>
-      <c r="B116" s="61"/>
+      <c r="A116" s="58"/>
+      <c r="B116" s="58"/>
       <c r="C116" s="22" t="s">
         <v>116</v>
       </c>
@@ -10552,8 +10550,8 @@
       </c>
     </row>
     <row r="117" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="61"/>
-      <c r="B117" s="61"/>
+      <c r="A117" s="58"/>
+      <c r="B117" s="58"/>
       <c r="C117" s="22" t="s">
         <v>117</v>
       </c>
@@ -10598,8 +10596,8 @@
       </c>
     </row>
     <row r="118" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="61"/>
-      <c r="B118" s="61"/>
+      <c r="A118" s="58"/>
+      <c r="B118" s="58"/>
       <c r="C118" s="22" t="s">
         <v>118</v>
       </c>
@@ -10644,8 +10642,8 @@
       </c>
     </row>
     <row r="119" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="61"/>
-      <c r="B119" s="61"/>
+      <c r="A119" s="58"/>
+      <c r="B119" s="58"/>
       <c r="C119" s="22" t="s">
         <v>119</v>
       </c>
@@ -10694,8 +10692,8 @@
       </c>
     </row>
     <row r="120" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="61"/>
-      <c r="B120" s="61"/>
+      <c r="A120" s="58"/>
+      <c r="B120" s="58"/>
       <c r="C120" s="22" t="s">
         <v>120</v>
       </c>
@@ -10740,8 +10738,8 @@
       </c>
     </row>
     <row r="121" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="60"/>
-      <c r="B121" s="60"/>
+      <c r="A121" s="59"/>
+      <c r="B121" s="59"/>
       <c r="C121" s="22" t="s">
         <v>121</v>
       </c>
@@ -10786,27 +10784,27 @@
       </c>
     </row>
     <row r="122" spans="1:17" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="59">
+      <c r="A122" s="57">
         <v>15</v>
       </c>
-      <c r="B122" s="59" t="s">
+      <c r="B122" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="C122" s="55" t="str">
+      <c r="C122" s="62" t="str">
         <f>IF(O116:O122="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N119&gt;3, N121&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D122" s="56"/>
-      <c r="E122" s="56"/>
-      <c r="F122" s="56"/>
-      <c r="G122" s="56"/>
-      <c r="H122" s="56"/>
-      <c r="I122" s="56"/>
-      <c r="J122" s="56"/>
-      <c r="K122" s="56"/>
-      <c r="L122" s="56"/>
+      <c r="D122" s="63"/>
+      <c r="E122" s="63"/>
+      <c r="F122" s="63"/>
+      <c r="G122" s="63"/>
+      <c r="H122" s="63"/>
+      <c r="I122" s="63"/>
+      <c r="J122" s="63"/>
+      <c r="K122" s="63"/>
+      <c r="L122" s="63"/>
       <c r="N122" s="29">
         <f>AVERAGE(D119:L121)</f>
         <v>4.1818181818181817</v>
@@ -10818,8 +10816,8 @@
       </c>
     </row>
     <row r="123" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="61"/>
-      <c r="B123" s="61"/>
+      <c r="A123" s="58"/>
+      <c r="B123" s="58"/>
       <c r="C123" s="22" t="s">
         <v>114</v>
       </c>
@@ -10860,8 +10858,8 @@
       </c>
     </row>
     <row r="124" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="61"/>
-      <c r="B124" s="61"/>
+      <c r="A124" s="58"/>
+      <c r="B124" s="58"/>
       <c r="C124" s="22" t="s">
         <v>116</v>
       </c>
@@ -10906,8 +10904,8 @@
       </c>
     </row>
     <row r="125" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="61"/>
-      <c r="B125" s="61"/>
+      <c r="A125" s="58"/>
+      <c r="B125" s="58"/>
       <c r="C125" s="22" t="s">
         <v>117</v>
       </c>
@@ -10952,8 +10950,8 @@
       </c>
     </row>
     <row r="126" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="61"/>
-      <c r="B126" s="61"/>
+      <c r="A126" s="58"/>
+      <c r="B126" s="58"/>
       <c r="C126" s="22" t="s">
         <v>118</v>
       </c>
@@ -10998,8 +10996,8 @@
       </c>
     </row>
     <row r="127" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="61"/>
-      <c r="B127" s="61"/>
+      <c r="A127" s="58"/>
+      <c r="B127" s="58"/>
       <c r="C127" s="22" t="s">
         <v>119</v>
       </c>
@@ -11048,8 +11046,8 @@
       </c>
     </row>
     <row r="128" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="61"/>
-      <c r="B128" s="61"/>
+      <c r="A128" s="58"/>
+      <c r="B128" s="58"/>
       <c r="C128" s="22" t="s">
         <v>120</v>
       </c>
@@ -11094,8 +11092,8 @@
       </c>
     </row>
     <row r="129" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="60"/>
-      <c r="B129" s="60"/>
+      <c r="A129" s="59"/>
+      <c r="B129" s="59"/>
       <c r="C129" s="22" t="s">
         <v>121</v>
       </c>
@@ -11140,27 +11138,27 @@
       </c>
     </row>
     <row r="130" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="59">
+      <c r="A130" s="57">
         <v>16</v>
       </c>
-      <c r="B130" s="59" t="s">
+      <c r="B130" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="C130" s="55" t="str">
+      <c r="C130" s="62" t="str">
         <f>IF(O124:O130="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N127&gt;3, N129&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D130" s="56"/>
-      <c r="E130" s="56"/>
-      <c r="F130" s="56"/>
-      <c r="G130" s="56"/>
-      <c r="H130" s="56"/>
-      <c r="I130" s="56"/>
-      <c r="J130" s="56"/>
-      <c r="K130" s="56"/>
-      <c r="L130" s="56"/>
+      <c r="D130" s="63"/>
+      <c r="E130" s="63"/>
+      <c r="F130" s="63"/>
+      <c r="G130" s="63"/>
+      <c r="H130" s="63"/>
+      <c r="I130" s="63"/>
+      <c r="J130" s="63"/>
+      <c r="K130" s="63"/>
+      <c r="L130" s="63"/>
       <c r="N130" s="29">
         <f>AVERAGE(D127:L129)</f>
         <v>5</v>
@@ -11172,8 +11170,8 @@
       </c>
     </row>
     <row r="131" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="61"/>
-      <c r="B131" s="61"/>
+      <c r="A131" s="58"/>
+      <c r="B131" s="58"/>
       <c r="C131" s="22" t="s">
         <v>114</v>
       </c>
@@ -11214,8 +11212,8 @@
       </c>
     </row>
     <row r="132" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="61"/>
-      <c r="B132" s="61"/>
+      <c r="A132" s="58"/>
+      <c r="B132" s="58"/>
       <c r="C132" s="22" t="s">
         <v>116</v>
       </c>
@@ -11260,8 +11258,8 @@
       </c>
     </row>
     <row r="133" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="61"/>
-      <c r="B133" s="61"/>
+      <c r="A133" s="58"/>
+      <c r="B133" s="58"/>
       <c r="C133" s="22" t="s">
         <v>117</v>
       </c>
@@ -11306,8 +11304,8 @@
       </c>
     </row>
     <row r="134" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="61"/>
-      <c r="B134" s="61"/>
+      <c r="A134" s="58"/>
+      <c r="B134" s="58"/>
       <c r="C134" s="22" t="s">
         <v>118</v>
       </c>
@@ -11352,8 +11350,8 @@
       </c>
     </row>
     <row r="135" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="61"/>
-      <c r="B135" s="61"/>
+      <c r="A135" s="58"/>
+      <c r="B135" s="58"/>
       <c r="C135" s="22" t="s">
         <v>119</v>
       </c>
@@ -11402,8 +11400,8 @@
       </c>
     </row>
     <row r="136" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="61"/>
-      <c r="B136" s="61"/>
+      <c r="A136" s="58"/>
+      <c r="B136" s="58"/>
       <c r="C136" s="22" t="s">
         <v>120</v>
       </c>
@@ -11448,8 +11446,8 @@
       </c>
     </row>
     <row r="137" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="60"/>
-      <c r="B137" s="60"/>
+      <c r="A137" s="59"/>
+      <c r="B137" s="59"/>
       <c r="C137" s="22" t="s">
         <v>121</v>
       </c>
@@ -11494,27 +11492,27 @@
       </c>
     </row>
     <row r="138" spans="1:17" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="59">
+      <c r="A138" s="57">
         <v>17</v>
       </c>
-      <c r="B138" s="59" t="s">
+      <c r="B138" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="55" t="str">
+      <c r="C138" s="62" t="str">
         <f>IF(O132:O138="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N135&gt;3, N137&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D138" s="56"/>
-      <c r="E138" s="56"/>
-      <c r="F138" s="56"/>
-      <c r="G138" s="56"/>
-      <c r="H138" s="56"/>
-      <c r="I138" s="56"/>
-      <c r="J138" s="56"/>
-      <c r="K138" s="56"/>
-      <c r="L138" s="56"/>
+      <c r="D138" s="63"/>
+      <c r="E138" s="63"/>
+      <c r="F138" s="63"/>
+      <c r="G138" s="63"/>
+      <c r="H138" s="63"/>
+      <c r="I138" s="63"/>
+      <c r="J138" s="63"/>
+      <c r="K138" s="63"/>
+      <c r="L138" s="63"/>
       <c r="N138" s="29">
         <f>AVERAGE(D135:L137)</f>
         <v>5</v>
@@ -11526,8 +11524,8 @@
       </c>
     </row>
     <row r="139" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="61"/>
-      <c r="B139" s="61"/>
+      <c r="A139" s="58"/>
+      <c r="B139" s="58"/>
       <c r="C139" s="22" t="s">
         <v>114</v>
       </c>
@@ -11568,8 +11566,8 @@
       </c>
     </row>
     <row r="140" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="61"/>
-      <c r="B140" s="61"/>
+      <c r="A140" s="58"/>
+      <c r="B140" s="58"/>
       <c r="C140" s="22" t="s">
         <v>116</v>
       </c>
@@ -11614,8 +11612,8 @@
       </c>
     </row>
     <row r="141" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="61"/>
-      <c r="B141" s="61"/>
+      <c r="A141" s="58"/>
+      <c r="B141" s="58"/>
       <c r="C141" s="22" t="s">
         <v>117</v>
       </c>
@@ -11660,8 +11658,8 @@
       </c>
     </row>
     <row r="142" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="61"/>
-      <c r="B142" s="61"/>
+      <c r="A142" s="58"/>
+      <c r="B142" s="58"/>
       <c r="C142" s="22" t="s">
         <v>118</v>
       </c>
@@ -11706,8 +11704,8 @@
       </c>
     </row>
     <row r="143" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="61"/>
-      <c r="B143" s="61"/>
+      <c r="A143" s="58"/>
+      <c r="B143" s="58"/>
       <c r="C143" s="22" t="s">
         <v>119</v>
       </c>
@@ -11756,8 +11754,8 @@
       </c>
     </row>
     <row r="144" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="61"/>
-      <c r="B144" s="61"/>
+      <c r="A144" s="58"/>
+      <c r="B144" s="58"/>
       <c r="C144" s="22" t="s">
         <v>120</v>
       </c>
@@ -11802,8 +11800,8 @@
       </c>
     </row>
     <row r="145" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="60"/>
-      <c r="B145" s="60"/>
+      <c r="A145" s="59"/>
+      <c r="B145" s="59"/>
       <c r="C145" s="22" t="s">
         <v>121</v>
       </c>
@@ -11848,27 +11846,27 @@
       </c>
     </row>
     <row r="146" spans="1:17" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="59">
+      <c r="A146" s="57">
         <v>18</v>
       </c>
-      <c r="B146" s="59" t="s">
+      <c r="B146" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="C146" s="55" t="str">
+      <c r="C146" s="62" t="str">
         <f>IF(O140:O146="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N143&gt;3, N145&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D146" s="56"/>
-      <c r="E146" s="56"/>
-      <c r="F146" s="56"/>
-      <c r="G146" s="56"/>
-      <c r="H146" s="56"/>
-      <c r="I146" s="56"/>
-      <c r="J146" s="56"/>
-      <c r="K146" s="56"/>
-      <c r="L146" s="56"/>
+      <c r="D146" s="63"/>
+      <c r="E146" s="63"/>
+      <c r="F146" s="63"/>
+      <c r="G146" s="63"/>
+      <c r="H146" s="63"/>
+      <c r="I146" s="63"/>
+      <c r="J146" s="63"/>
+      <c r="K146" s="63"/>
+      <c r="L146" s="63"/>
       <c r="N146" s="29">
         <f>AVERAGE(D143:L145)</f>
         <v>5</v>
@@ -11880,8 +11878,8 @@
       </c>
     </row>
     <row r="147" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="61"/>
-      <c r="B147" s="61"/>
+      <c r="A147" s="58"/>
+      <c r="B147" s="58"/>
       <c r="C147" s="22" t="s">
         <v>114</v>
       </c>
@@ -11914,8 +11912,8 @@
       </c>
     </row>
     <row r="148" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="61"/>
-      <c r="B148" s="61"/>
+      <c r="A148" s="58"/>
+      <c r="B148" s="58"/>
       <c r="C148" s="22" t="s">
         <v>116</v>
       </c>
@@ -11952,8 +11950,8 @@
       </c>
     </row>
     <row r="149" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="61"/>
-      <c r="B149" s="61"/>
+      <c r="A149" s="58"/>
+      <c r="B149" s="58"/>
       <c r="C149" s="22" t="s">
         <v>117</v>
       </c>
@@ -11990,8 +11988,8 @@
       </c>
     </row>
     <row r="150" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="61"/>
-      <c r="B150" s="61"/>
+      <c r="A150" s="58"/>
+      <c r="B150" s="58"/>
       <c r="C150" s="22" t="s">
         <v>118</v>
       </c>
@@ -12036,8 +12034,8 @@
       </c>
     </row>
     <row r="151" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="61"/>
-      <c r="B151" s="61"/>
+      <c r="A151" s="58"/>
+      <c r="B151" s="58"/>
       <c r="C151" s="22" t="s">
         <v>119</v>
       </c>
@@ -12086,8 +12084,8 @@
       </c>
     </row>
     <row r="152" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="61"/>
-      <c r="B152" s="61"/>
+      <c r="A152" s="58"/>
+      <c r="B152" s="58"/>
       <c r="C152" s="22" t="s">
         <v>120</v>
       </c>
@@ -12132,8 +12130,8 @@
       </c>
     </row>
     <row r="153" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="60"/>
-      <c r="B153" s="60"/>
+      <c r="A153" s="59"/>
+      <c r="B153" s="59"/>
       <c r="C153" s="22" t="s">
         <v>121</v>
       </c>
@@ -12178,27 +12176,27 @@
       </c>
     </row>
     <row r="154" spans="1:17" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="59">
+      <c r="A154" s="57">
         <v>19</v>
       </c>
-      <c r="B154" s="59" t="s">
+      <c r="B154" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="C154" s="55" t="str">
+      <c r="C154" s="62" t="str">
         <f>IF(O148:O154="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N151&gt;3, N153&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D154" s="56"/>
-      <c r="E154" s="56"/>
-      <c r="F154" s="56"/>
-      <c r="G154" s="56"/>
-      <c r="H154" s="56"/>
-      <c r="I154" s="56"/>
-      <c r="J154" s="56"/>
-      <c r="K154" s="56"/>
-      <c r="L154" s="56"/>
+      <c r="D154" s="63"/>
+      <c r="E154" s="63"/>
+      <c r="F154" s="63"/>
+      <c r="G154" s="63"/>
+      <c r="H154" s="63"/>
+      <c r="I154" s="63"/>
+      <c r="J154" s="63"/>
+      <c r="K154" s="63"/>
+      <c r="L154" s="63"/>
       <c r="N154" s="29">
         <f>AVERAGE(D151:L153)</f>
         <v>5</v>
@@ -12210,8 +12208,8 @@
       </c>
     </row>
     <row r="155" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="61"/>
-      <c r="B155" s="61"/>
+      <c r="A155" s="58"/>
+      <c r="B155" s="58"/>
       <c r="C155" s="22" t="s">
         <v>114</v>
       </c>
@@ -12252,8 +12250,8 @@
       </c>
     </row>
     <row r="156" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="61"/>
-      <c r="B156" s="61"/>
+      <c r="A156" s="58"/>
+      <c r="B156" s="58"/>
       <c r="C156" s="22" t="s">
         <v>116</v>
       </c>
@@ -12298,8 +12296,8 @@
       </c>
     </row>
     <row r="157" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="61"/>
-      <c r="B157" s="61"/>
+      <c r="A157" s="58"/>
+      <c r="B157" s="58"/>
       <c r="C157" s="22" t="s">
         <v>117</v>
       </c>
@@ -12344,8 +12342,8 @@
       </c>
     </row>
     <row r="158" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="61"/>
-      <c r="B158" s="61"/>
+      <c r="A158" s="58"/>
+      <c r="B158" s="58"/>
       <c r="C158" s="22" t="s">
         <v>118</v>
       </c>
@@ -12390,8 +12388,8 @@
       </c>
     </row>
     <row r="159" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="61"/>
-      <c r="B159" s="61"/>
+      <c r="A159" s="58"/>
+      <c r="B159" s="58"/>
       <c r="C159" s="22" t="s">
         <v>119</v>
       </c>
@@ -12440,8 +12438,8 @@
       </c>
     </row>
     <row r="160" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="61"/>
-      <c r="B160" s="61"/>
+      <c r="A160" s="58"/>
+      <c r="B160" s="58"/>
       <c r="C160" s="22" t="s">
         <v>120</v>
       </c>
@@ -12486,8 +12484,8 @@
       </c>
     </row>
     <row r="161" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="60"/>
-      <c r="B161" s="60"/>
+      <c r="A161" s="59"/>
+      <c r="B161" s="59"/>
       <c r="C161" s="22" t="s">
         <v>121</v>
       </c>
@@ -12532,27 +12530,27 @@
       </c>
     </row>
     <row r="162" spans="1:17" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="59">
+      <c r="A162" s="57">
         <v>20</v>
       </c>
-      <c r="B162" s="59" t="s">
+      <c r="B162" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="C162" s="55" t="str">
+      <c r="C162" s="62" t="str">
         <f>IF(O156:O162="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N159&gt;3, N161&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D162" s="56"/>
-      <c r="E162" s="56"/>
-      <c r="F162" s="56"/>
-      <c r="G162" s="56"/>
-      <c r="H162" s="56"/>
-      <c r="I162" s="56"/>
-      <c r="J162" s="56"/>
-      <c r="K162" s="56"/>
-      <c r="L162" s="56"/>
+      <c r="D162" s="63"/>
+      <c r="E162" s="63"/>
+      <c r="F162" s="63"/>
+      <c r="G162" s="63"/>
+      <c r="H162" s="63"/>
+      <c r="I162" s="63"/>
+      <c r="J162" s="63"/>
+      <c r="K162" s="63"/>
+      <c r="L162" s="63"/>
       <c r="N162" s="29">
         <f>AVERAGE(D159:L161)</f>
         <v>5</v>
@@ -12564,8 +12562,8 @@
       </c>
     </row>
     <row r="163" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="61"/>
-      <c r="B163" s="61"/>
+      <c r="A163" s="58"/>
+      <c r="B163" s="58"/>
       <c r="C163" s="22" t="s">
         <v>114</v>
       </c>
@@ -12606,8 +12604,8 @@
       </c>
     </row>
     <row r="164" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="61"/>
-      <c r="B164" s="61"/>
+      <c r="A164" s="58"/>
+      <c r="B164" s="58"/>
       <c r="C164" s="22" t="s">
         <v>116</v>
       </c>
@@ -12652,8 +12650,8 @@
       </c>
     </row>
     <row r="165" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="61"/>
-      <c r="B165" s="61"/>
+      <c r="A165" s="58"/>
+      <c r="B165" s="58"/>
       <c r="C165" s="22" t="s">
         <v>117</v>
       </c>
@@ -12698,8 +12696,8 @@
       </c>
     </row>
     <row r="166" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="61"/>
-      <c r="B166" s="61"/>
+      <c r="A166" s="58"/>
+      <c r="B166" s="58"/>
       <c r="C166" s="22" t="s">
         <v>118</v>
       </c>
@@ -12744,8 +12742,8 @@
       </c>
     </row>
     <row r="167" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="61"/>
-      <c r="B167" s="61"/>
+      <c r="A167" s="58"/>
+      <c r="B167" s="58"/>
       <c r="C167" s="22" t="s">
         <v>119</v>
       </c>
@@ -12790,8 +12788,8 @@
       </c>
     </row>
     <row r="168" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="61"/>
-      <c r="B168" s="61"/>
+      <c r="A168" s="58"/>
+      <c r="B168" s="58"/>
       <c r="C168" s="22" t="s">
         <v>120</v>
       </c>
@@ -12840,8 +12838,8 @@
       </c>
     </row>
     <row r="169" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="60"/>
-      <c r="B169" s="60"/>
+      <c r="A169" s="59"/>
+      <c r="B169" s="59"/>
       <c r="C169" s="22" t="s">
         <v>121</v>
       </c>
@@ -12886,27 +12884,27 @@
       </c>
     </row>
     <row r="170" spans="1:17" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="59">
+      <c r="A170" s="57">
         <v>21</v>
       </c>
-      <c r="B170" s="59" t="s">
+      <c r="B170" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="C170" s="55" t="str">
+      <c r="C170" s="62" t="str">
         <f>IF(O164:O170="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N167&gt;3, N169&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D170" s="56"/>
-      <c r="E170" s="56"/>
-      <c r="F170" s="56"/>
-      <c r="G170" s="56"/>
-      <c r="H170" s="56"/>
-      <c r="I170" s="56"/>
-      <c r="J170" s="56"/>
-      <c r="K170" s="56"/>
-      <c r="L170" s="56"/>
+      <c r="D170" s="63"/>
+      <c r="E170" s="63"/>
+      <c r="F170" s="63"/>
+      <c r="G170" s="63"/>
+      <c r="H170" s="63"/>
+      <c r="I170" s="63"/>
+      <c r="J170" s="63"/>
+      <c r="K170" s="63"/>
+      <c r="L170" s="63"/>
       <c r="N170" s="29">
         <f>AVERAGE(D167:L169)</f>
         <v>4.4545454545454541</v>
@@ -12918,8 +12916,8 @@
       </c>
     </row>
     <row r="171" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="61"/>
-      <c r="B171" s="61"/>
+      <c r="A171" s="58"/>
+      <c r="B171" s="58"/>
       <c r="C171" s="22" t="s">
         <v>114</v>
       </c>
@@ -12960,8 +12958,8 @@
       </c>
     </row>
     <row r="172" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="61"/>
-      <c r="B172" s="61"/>
+      <c r="A172" s="58"/>
+      <c r="B172" s="58"/>
       <c r="C172" s="22" t="s">
         <v>116</v>
       </c>
@@ -13006,8 +13004,8 @@
       </c>
     </row>
     <row r="173" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="61"/>
-      <c r="B173" s="61"/>
+      <c r="A173" s="58"/>
+      <c r="B173" s="58"/>
       <c r="C173" s="22" t="s">
         <v>117</v>
       </c>
@@ -13044,8 +13042,8 @@
       </c>
     </row>
     <row r="174" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="61"/>
-      <c r="B174" s="61"/>
+      <c r="A174" s="58"/>
+      <c r="B174" s="58"/>
       <c r="C174" s="22" t="s">
         <v>118</v>
       </c>
@@ -13082,8 +13080,8 @@
       </c>
     </row>
     <row r="175" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="61"/>
-      <c r="B175" s="61"/>
+      <c r="A175" s="58"/>
+      <c r="B175" s="58"/>
       <c r="C175" s="22" t="s">
         <v>119</v>
       </c>
@@ -13132,8 +13130,8 @@
       </c>
     </row>
     <row r="176" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="61"/>
-      <c r="B176" s="61"/>
+      <c r="A176" s="58"/>
+      <c r="B176" s="58"/>
       <c r="C176" s="22" t="s">
         <v>120</v>
       </c>
@@ -13170,8 +13168,8 @@
       </c>
     </row>
     <row r="177" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="60"/>
-      <c r="B177" s="60"/>
+      <c r="A177" s="59"/>
+      <c r="B177" s="59"/>
       <c r="C177" s="22" t="s">
         <v>121</v>
       </c>
@@ -13208,27 +13206,27 @@
       </c>
     </row>
     <row r="178" spans="1:17" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="59">
+      <c r="A178" s="57">
         <v>22</v>
       </c>
-      <c r="B178" s="59" t="s">
+      <c r="B178" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="C178" s="55" t="str">
+      <c r="C178" s="62" t="str">
         <f>IF(O172:O178="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N175&gt;3, N177&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D178" s="56"/>
-      <c r="E178" s="56"/>
-      <c r="F178" s="56"/>
-      <c r="G178" s="56"/>
-      <c r="H178" s="56"/>
-      <c r="I178" s="56"/>
-      <c r="J178" s="56"/>
-      <c r="K178" s="56"/>
-      <c r="L178" s="56"/>
+      <c r="D178" s="63"/>
+      <c r="E178" s="63"/>
+      <c r="F178" s="63"/>
+      <c r="G178" s="63"/>
+      <c r="H178" s="63"/>
+      <c r="I178" s="63"/>
+      <c r="J178" s="63"/>
+      <c r="K178" s="63"/>
+      <c r="L178" s="63"/>
       <c r="N178" s="29">
         <f>AVERAGE(D172:L177)</f>
         <v>4.7</v>
@@ -13240,8 +13238,8 @@
       </c>
     </row>
     <row r="179" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="61"/>
-      <c r="B179" s="61"/>
+      <c r="A179" s="58"/>
+      <c r="B179" s="58"/>
       <c r="C179" s="22" t="s">
         <v>114</v>
       </c>
@@ -13282,8 +13280,8 @@
       </c>
     </row>
     <row r="180" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="61"/>
-      <c r="B180" s="61"/>
+      <c r="A180" s="58"/>
+      <c r="B180" s="58"/>
       <c r="C180" s="22" t="s">
         <v>116</v>
       </c>
@@ -13328,8 +13326,8 @@
       </c>
     </row>
     <row r="181" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="61"/>
-      <c r="B181" s="61"/>
+      <c r="A181" s="58"/>
+      <c r="B181" s="58"/>
       <c r="C181" s="22" t="s">
         <v>117</v>
       </c>
@@ -13374,8 +13372,8 @@
       </c>
     </row>
     <row r="182" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="61"/>
-      <c r="B182" s="61"/>
+      <c r="A182" s="58"/>
+      <c r="B182" s="58"/>
       <c r="C182" s="22" t="s">
         <v>118</v>
       </c>
@@ -13420,8 +13418,8 @@
       </c>
     </row>
     <row r="183" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="61"/>
-      <c r="B183" s="61"/>
+      <c r="A183" s="58"/>
+      <c r="B183" s="58"/>
       <c r="C183" s="22" t="s">
         <v>119</v>
       </c>
@@ -13470,8 +13468,8 @@
       </c>
     </row>
     <row r="184" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="61"/>
-      <c r="B184" s="61"/>
+      <c r="A184" s="58"/>
+      <c r="B184" s="58"/>
       <c r="C184" s="22" t="s">
         <v>120</v>
       </c>
@@ -13516,8 +13514,8 @@
       </c>
     </row>
     <row r="185" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="60"/>
-      <c r="B185" s="60"/>
+      <c r="A185" s="59"/>
+      <c r="B185" s="59"/>
       <c r="C185" s="22" t="s">
         <v>121</v>
       </c>
@@ -13562,27 +13560,27 @@
       </c>
     </row>
     <row r="186" spans="1:17" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="59">
+      <c r="A186" s="57">
         <v>23</v>
       </c>
-      <c r="B186" s="59" t="s">
+      <c r="B186" s="57" t="s">
         <v>143</v>
       </c>
-      <c r="C186" s="55" t="str">
+      <c r="C186" s="62" t="str">
         <f>IF(O180:O186="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N183&gt;3, N185&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D186" s="56"/>
-      <c r="E186" s="56"/>
-      <c r="F186" s="56"/>
-      <c r="G186" s="56"/>
-      <c r="H186" s="56"/>
-      <c r="I186" s="56"/>
-      <c r="J186" s="56"/>
-      <c r="K186" s="56"/>
-      <c r="L186" s="56"/>
+      <c r="D186" s="63"/>
+      <c r="E186" s="63"/>
+      <c r="F186" s="63"/>
+      <c r="G186" s="63"/>
+      <c r="H186" s="63"/>
+      <c r="I186" s="63"/>
+      <c r="J186" s="63"/>
+      <c r="K186" s="63"/>
+      <c r="L186" s="63"/>
       <c r="N186" s="29">
         <f>AVERAGE(D183:L185)</f>
         <v>5</v>
@@ -13594,8 +13592,8 @@
       </c>
     </row>
     <row r="187" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="61"/>
-      <c r="B187" s="61"/>
+      <c r="A187" s="58"/>
+      <c r="B187" s="58"/>
       <c r="C187" s="22" t="s">
         <v>114</v>
       </c>
@@ -13636,8 +13634,8 @@
       </c>
     </row>
     <row r="188" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="61"/>
-      <c r="B188" s="61"/>
+      <c r="A188" s="58"/>
+      <c r="B188" s="58"/>
       <c r="C188" s="22" t="s">
         <v>116</v>
       </c>
@@ -13682,8 +13680,8 @@
       </c>
     </row>
     <row r="189" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="61"/>
-      <c r="B189" s="61"/>
+      <c r="A189" s="58"/>
+      <c r="B189" s="58"/>
       <c r="C189" s="22" t="s">
         <v>117</v>
       </c>
@@ -13728,8 +13726,8 @@
       </c>
     </row>
     <row r="190" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="61"/>
-      <c r="B190" s="61"/>
+      <c r="A190" s="58"/>
+      <c r="B190" s="58"/>
       <c r="C190" s="22" t="s">
         <v>118</v>
       </c>
@@ -13774,8 +13772,8 @@
       </c>
     </row>
     <row r="191" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="61"/>
-      <c r="B191" s="61"/>
+      <c r="A191" s="58"/>
+      <c r="B191" s="58"/>
       <c r="C191" s="22" t="s">
         <v>119</v>
       </c>
@@ -13824,8 +13822,8 @@
       </c>
     </row>
     <row r="192" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="61"/>
-      <c r="B192" s="61"/>
+      <c r="A192" s="58"/>
+      <c r="B192" s="58"/>
       <c r="C192" s="22" t="s">
         <v>120</v>
       </c>
@@ -13870,8 +13868,8 @@
       </c>
     </row>
     <row r="193" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="60"/>
-      <c r="B193" s="60"/>
+      <c r="A193" s="59"/>
+      <c r="B193" s="59"/>
       <c r="C193" s="22" t="s">
         <v>121</v>
       </c>
@@ -13916,27 +13914,27 @@
       </c>
     </row>
     <row r="194" spans="1:17" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="59">
+      <c r="A194" s="57">
         <v>24</v>
       </c>
-      <c r="B194" s="59" t="s">
+      <c r="B194" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="C194" s="55" t="str">
+      <c r="C194" s="62" t="str">
         <f>IF(O188:O194="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N191&gt;3, N193&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D194" s="56"/>
-      <c r="E194" s="56"/>
-      <c r="F194" s="56"/>
-      <c r="G194" s="56"/>
-      <c r="H194" s="56"/>
-      <c r="I194" s="56"/>
-      <c r="J194" s="56"/>
-      <c r="K194" s="56"/>
-      <c r="L194" s="56"/>
+      <c r="D194" s="63"/>
+      <c r="E194" s="63"/>
+      <c r="F194" s="63"/>
+      <c r="G194" s="63"/>
+      <c r="H194" s="63"/>
+      <c r="I194" s="63"/>
+      <c r="J194" s="63"/>
+      <c r="K194" s="63"/>
+      <c r="L194" s="63"/>
       <c r="N194" s="29">
         <f>AVERAGE(D191:L193)</f>
         <v>4.0909090909090908</v>
@@ -13948,8 +13946,8 @@
       </c>
     </row>
     <row r="195" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="61"/>
-      <c r="B195" s="61"/>
+      <c r="A195" s="58"/>
+      <c r="B195" s="58"/>
       <c r="C195" s="22" t="s">
         <v>114</v>
       </c>
@@ -13990,8 +13988,8 @@
       </c>
     </row>
     <row r="196" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="61"/>
-      <c r="B196" s="61"/>
+      <c r="A196" s="58"/>
+      <c r="B196" s="58"/>
       <c r="C196" s="22" t="s">
         <v>116</v>
       </c>
@@ -14036,8 +14034,8 @@
       </c>
     </row>
     <row r="197" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="61"/>
-      <c r="B197" s="61"/>
+      <c r="A197" s="58"/>
+      <c r="B197" s="58"/>
       <c r="C197" s="22" t="s">
         <v>117</v>
       </c>
@@ -14082,8 +14080,8 @@
       </c>
     </row>
     <row r="198" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="61"/>
-      <c r="B198" s="61"/>
+      <c r="A198" s="58"/>
+      <c r="B198" s="58"/>
       <c r="C198" s="22" t="s">
         <v>118</v>
       </c>
@@ -14128,8 +14126,8 @@
       </c>
     </row>
     <row r="199" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="61"/>
-      <c r="B199" s="61"/>
+      <c r="A199" s="58"/>
+      <c r="B199" s="58"/>
       <c r="C199" s="22" t="s">
         <v>119</v>
       </c>
@@ -14178,8 +14176,8 @@
       </c>
     </row>
     <row r="200" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="61"/>
-      <c r="B200" s="61"/>
+      <c r="A200" s="58"/>
+      <c r="B200" s="58"/>
       <c r="C200" s="22" t="s">
         <v>120</v>
       </c>
@@ -14224,8 +14222,8 @@
       </c>
     </row>
     <row r="201" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="60"/>
-      <c r="B201" s="60"/>
+      <c r="A201" s="59"/>
+      <c r="B201" s="59"/>
       <c r="C201" s="22" t="s">
         <v>121</v>
       </c>
@@ -14270,27 +14268,27 @@
       </c>
     </row>
     <row r="202" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="59">
+      <c r="A202" s="57">
         <v>25</v>
       </c>
-      <c r="B202" s="59" t="s">
+      <c r="B202" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="C202" s="55" t="str">
+      <c r="C202" s="62" t="str">
         <f>IF(O196:O202="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N199&gt;3, N201&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру</v>
       </c>
-      <c r="D202" s="56"/>
-      <c r="E202" s="56"/>
-      <c r="F202" s="56"/>
-      <c r="G202" s="56"/>
-      <c r="H202" s="56"/>
-      <c r="I202" s="56"/>
-      <c r="J202" s="56"/>
-      <c r="K202" s="56"/>
-      <c r="L202" s="56"/>
+      <c r="D202" s="63"/>
+      <c r="E202" s="63"/>
+      <c r="F202" s="63"/>
+      <c r="G202" s="63"/>
+      <c r="H202" s="63"/>
+      <c r="I202" s="63"/>
+      <c r="J202" s="63"/>
+      <c r="K202" s="63"/>
+      <c r="L202" s="63"/>
       <c r="N202" s="29">
         <f>AVERAGE(D199:L201)</f>
         <v>5</v>
@@ -14302,8 +14300,8 @@
       </c>
     </row>
     <row r="203" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="61"/>
-      <c r="B203" s="61"/>
+      <c r="A203" s="58"/>
+      <c r="B203" s="58"/>
       <c r="C203" s="22" t="s">
         <v>114</v>
       </c>
@@ -14344,8 +14342,8 @@
       </c>
     </row>
     <row r="204" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A204" s="61"/>
-      <c r="B204" s="61"/>
+      <c r="A204" s="58"/>
+      <c r="B204" s="58"/>
       <c r="C204" s="22" t="s">
         <v>116</v>
       </c>
@@ -14390,8 +14388,8 @@
       </c>
     </row>
     <row r="205" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A205" s="61"/>
-      <c r="B205" s="61"/>
+      <c r="A205" s="58"/>
+      <c r="B205" s="58"/>
       <c r="C205" s="22" t="s">
         <v>117</v>
       </c>
@@ -14436,8 +14434,8 @@
       </c>
     </row>
     <row r="206" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A206" s="61"/>
-      <c r="B206" s="61"/>
+      <c r="A206" s="58"/>
+      <c r="B206" s="58"/>
       <c r="C206" s="22" t="s">
         <v>118</v>
       </c>
@@ -14482,8 +14480,8 @@
       </c>
     </row>
     <row r="207" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A207" s="61"/>
-      <c r="B207" s="61"/>
+      <c r="A207" s="58"/>
+      <c r="B207" s="58"/>
       <c r="C207" s="22" t="s">
         <v>119</v>
       </c>
@@ -14532,8 +14530,8 @@
       </c>
     </row>
     <row r="208" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A208" s="61"/>
-      <c r="B208" s="61"/>
+      <c r="A208" s="58"/>
+      <c r="B208" s="58"/>
       <c r="C208" s="22" t="s">
         <v>120</v>
       </c>
@@ -14578,8 +14576,8 @@
       </c>
     </row>
     <row r="209" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A209" s="60"/>
-      <c r="B209" s="61"/>
+      <c r="A209" s="59"/>
+      <c r="B209" s="58"/>
       <c r="C209" s="35" t="s">
         <v>121</v>
       </c>
@@ -14642,24 +14640,24 @@
       <c r="A211" s="31">
         <v>26</v>
       </c>
-      <c r="B211" s="61" t="s">
+      <c r="B211" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="C211" s="55" t="str">
+      <c r="C211" s="62" t="str">
         <f>IF(O205:O211="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N208&gt;3, N210&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D211" s="56"/>
-      <c r="E211" s="56"/>
-      <c r="F211" s="56"/>
-      <c r="G211" s="56"/>
-      <c r="H211" s="56"/>
-      <c r="I211" s="56"/>
-      <c r="J211" s="56"/>
-      <c r="K211" s="56"/>
-      <c r="L211" s="56"/>
+      <c r="D211" s="63"/>
+      <c r="E211" s="63"/>
+      <c r="F211" s="63"/>
+      <c r="G211" s="63"/>
+      <c r="H211" s="63"/>
+      <c r="I211" s="63"/>
+      <c r="J211" s="63"/>
+      <c r="K211" s="63"/>
+      <c r="L211" s="63"/>
       <c r="N211" s="29">
         <f>AVERAGE(D207:L209)</f>
         <v>4.1818181818181817</v>
@@ -14672,7 +14670,7 @@
     </row>
     <row r="212" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="32"/>
-      <c r="B212" s="61"/>
+      <c r="B212" s="58"/>
       <c r="C212" s="22" t="s">
         <v>114</v>
       </c>
@@ -14714,7 +14712,7 @@
     </row>
     <row r="213" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="32"/>
-      <c r="B213" s="61"/>
+      <c r="B213" s="58"/>
       <c r="C213" s="22" t="s">
         <v>116</v>
       </c>
@@ -14761,7 +14759,7 @@
     </row>
     <row r="214" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="32"/>
-      <c r="B214" s="61"/>
+      <c r="B214" s="58"/>
       <c r="C214" s="22" t="s">
         <v>117</v>
       </c>
@@ -14808,7 +14806,7 @@
     </row>
     <row r="215" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="32"/>
-      <c r="B215" s="61"/>
+      <c r="B215" s="58"/>
       <c r="C215" s="22" t="s">
         <v>118</v>
       </c>
@@ -14854,7 +14852,7 @@
     </row>
     <row r="216" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="32"/>
-      <c r="B216" s="61"/>
+      <c r="B216" s="58"/>
       <c r="C216" s="22" t="s">
         <v>119</v>
       </c>
@@ -14904,7 +14902,7 @@
     </row>
     <row r="217" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="32"/>
-      <c r="B217" s="61"/>
+      <c r="B217" s="58"/>
       <c r="C217" s="22" t="s">
         <v>120</v>
       </c>
@@ -14942,7 +14940,7 @@
     </row>
     <row r="218" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="33"/>
-      <c r="B218" s="60"/>
+      <c r="B218" s="59"/>
       <c r="C218" s="22" t="s">
         <v>121</v>
       </c>
@@ -14979,21 +14977,21 @@
       </c>
     </row>
     <row r="219" spans="1:17" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C219" s="55" t="str">
+      <c r="C219" s="62" t="str">
         <f>IF(O213:O219="Ынта төмендеді","1. Жеке тапсырма беру; 2. Практикалық мысалдар келтіру; 3. Шағын мақсаттар қою; 4. Оқушының пікірін сұрау; 5. Ойын элементтерін қосу",
 IF(AND(N216&gt;3, N218&gt;3), "1. Базалық білімді қалпына келтіру; 2. Қосымша сабақтар; 3. Жеңіл тапсырмалар арқылы сәттілік сезімін ояту; 4. Ата-анамен байланыс; 5. Пәнді өмірмен байланыстыру",
  "Ынта қалыпты, ынталандыруды жалғастыру"))</f>
         <v>Ынта қалыпты, ынталандыруды жалғастыру</v>
       </c>
-      <c r="D219" s="56"/>
-      <c r="E219" s="56"/>
-      <c r="F219" s="56"/>
-      <c r="G219" s="56"/>
-      <c r="H219" s="56"/>
-      <c r="I219" s="56"/>
-      <c r="J219" s="56"/>
-      <c r="K219" s="56"/>
-      <c r="L219" s="56"/>
+      <c r="D219" s="63"/>
+      <c r="E219" s="63"/>
+      <c r="F219" s="63"/>
+      <c r="G219" s="63"/>
+      <c r="H219" s="63"/>
+      <c r="I219" s="63"/>
+      <c r="J219" s="63"/>
+      <c r="K219" s="63"/>
+      <c r="L219" s="63"/>
       <c r="N219" s="29">
         <f>SUM(N216)</f>
         <v>0</v>
@@ -15051,6 +15049,84 @@
     </row>
   </sheetData>
   <mergeCells count="87">
+    <mergeCell ref="C211:L211"/>
+    <mergeCell ref="C219:L219"/>
+    <mergeCell ref="C170:L170"/>
+    <mergeCell ref="C178:L178"/>
+    <mergeCell ref="C186:L186"/>
+    <mergeCell ref="C194:L194"/>
+    <mergeCell ref="C202:L202"/>
+    <mergeCell ref="C130:L130"/>
+    <mergeCell ref="C138:L138"/>
+    <mergeCell ref="C146:L146"/>
+    <mergeCell ref="C154:L154"/>
+    <mergeCell ref="C162:L162"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C106:L106"/>
+    <mergeCell ref="C114:L114"/>
+    <mergeCell ref="C122:L122"/>
+    <mergeCell ref="C50:L50"/>
+    <mergeCell ref="C58:L58"/>
+    <mergeCell ref="C66:L66"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C18:L18"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C42:L42"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A10:A17"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="A18:A25"/>
+    <mergeCell ref="B18:B25"/>
+    <mergeCell ref="A26:A33"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="A34:A41"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="A42:A49"/>
+    <mergeCell ref="B42:B49"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="B50:B57"/>
+    <mergeCell ref="A58:A65"/>
+    <mergeCell ref="B58:B65"/>
+    <mergeCell ref="A66:A73"/>
+    <mergeCell ref="B66:B73"/>
+    <mergeCell ref="A74:A81"/>
+    <mergeCell ref="B74:B81"/>
+    <mergeCell ref="A82:A89"/>
+    <mergeCell ref="B82:B89"/>
+    <mergeCell ref="A90:A97"/>
+    <mergeCell ref="B90:B97"/>
+    <mergeCell ref="A98:A105"/>
+    <mergeCell ref="B98:B105"/>
+    <mergeCell ref="A106:A113"/>
+    <mergeCell ref="B106:B113"/>
+    <mergeCell ref="A114:A121"/>
+    <mergeCell ref="B114:B121"/>
+    <mergeCell ref="A122:A129"/>
+    <mergeCell ref="B122:B129"/>
+    <mergeCell ref="A130:A137"/>
+    <mergeCell ref="B130:B137"/>
+    <mergeCell ref="A138:A145"/>
+    <mergeCell ref="B138:B145"/>
+    <mergeCell ref="A146:A153"/>
+    <mergeCell ref="B146:B153"/>
+    <mergeCell ref="A154:A161"/>
+    <mergeCell ref="B154:B161"/>
+    <mergeCell ref="A162:A169"/>
+    <mergeCell ref="B162:B169"/>
+    <mergeCell ref="A170:A177"/>
+    <mergeCell ref="B170:B177"/>
     <mergeCell ref="A202:A209"/>
     <mergeCell ref="B202:B209"/>
     <mergeCell ref="B211:B218"/>
@@ -15060,84 +15136,6 @@
     <mergeCell ref="B186:B193"/>
     <mergeCell ref="A194:A201"/>
     <mergeCell ref="B194:B201"/>
-    <mergeCell ref="A154:A161"/>
-    <mergeCell ref="B154:B161"/>
-    <mergeCell ref="A162:A169"/>
-    <mergeCell ref="B162:B169"/>
-    <mergeCell ref="A170:A177"/>
-    <mergeCell ref="B170:B177"/>
-    <mergeCell ref="A130:A137"/>
-    <mergeCell ref="B130:B137"/>
-    <mergeCell ref="A138:A145"/>
-    <mergeCell ref="B138:B145"/>
-    <mergeCell ref="A146:A153"/>
-    <mergeCell ref="B146:B153"/>
-    <mergeCell ref="A106:A113"/>
-    <mergeCell ref="B106:B113"/>
-    <mergeCell ref="A114:A121"/>
-    <mergeCell ref="B114:B121"/>
-    <mergeCell ref="A122:A129"/>
-    <mergeCell ref="B122:B129"/>
-    <mergeCell ref="A82:A89"/>
-    <mergeCell ref="B82:B89"/>
-    <mergeCell ref="A90:A97"/>
-    <mergeCell ref="B90:B97"/>
-    <mergeCell ref="A98:A105"/>
-    <mergeCell ref="B98:B105"/>
-    <mergeCell ref="A58:A65"/>
-    <mergeCell ref="B58:B65"/>
-    <mergeCell ref="A66:A73"/>
-    <mergeCell ref="B66:B73"/>
-    <mergeCell ref="A74:A81"/>
-    <mergeCell ref="B74:B81"/>
-    <mergeCell ref="A34:A41"/>
-    <mergeCell ref="B34:B41"/>
-    <mergeCell ref="A42:A49"/>
-    <mergeCell ref="B42:B49"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="B50:B57"/>
-    <mergeCell ref="A10:A17"/>
-    <mergeCell ref="B10:B17"/>
-    <mergeCell ref="A18:A25"/>
-    <mergeCell ref="B18:B25"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C10:L10"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="C34:L34"/>
-    <mergeCell ref="C42:L42"/>
-    <mergeCell ref="C50:L50"/>
-    <mergeCell ref="C58:L58"/>
-    <mergeCell ref="C66:L66"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C82:L82"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C106:L106"/>
-    <mergeCell ref="C114:L114"/>
-    <mergeCell ref="C122:L122"/>
-    <mergeCell ref="C130:L130"/>
-    <mergeCell ref="C138:L138"/>
-    <mergeCell ref="C146:L146"/>
-    <mergeCell ref="C154:L154"/>
-    <mergeCell ref="C162:L162"/>
-    <mergeCell ref="C211:L211"/>
-    <mergeCell ref="C219:L219"/>
-    <mergeCell ref="C170:L170"/>
-    <mergeCell ref="C178:L178"/>
-    <mergeCell ref="C186:L186"/>
-    <mergeCell ref="C194:L194"/>
-    <mergeCell ref="C202:L202"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/reiting.xlsx
+++ b/reiting.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="114">
   <si>
     <t>Школа</t>
   </si>
@@ -364,6 +364,9 @@
   </si>
   <si>
     <t>Волонтерство. Общественные работы</t>
+  </si>
+  <si>
+    <t>Завуч</t>
   </si>
 </sst>
 </file>
@@ -626,7 +629,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -645,6 +647,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -994,43 +997,43 @@
       <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26" t="s">
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26" t="s">
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26" t="s">
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
-      <c r="AA3" s="26" t="s">
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+      <c r="AA3" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="AB3" s="26"/>
-      <c r="AC3" s="26"/>
-      <c r="AD3" s="26"/>
-      <c r="AE3" s="26"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
     </row>
     <row r="4" spans="1:32" s="1" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
@@ -2074,7 +2077,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="3" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="6" max="9" width="11.140625" customWidth="1"/>
     <col min="11" max="11" width="13.85546875" customWidth="1"/>
@@ -2097,43 +2101,43 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="L1" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="M1" s="32" t="s">
+      <c r="M1" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="N1" s="32" t="s">
+      <c r="N1" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="O1" s="32" t="s">
+      <c r="O1" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="32" t="s">
+      <c r="P1" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="Q1" s="32" t="s">
+      <c r="Q1" s="31" t="s">
         <v>110</v>
       </c>
       <c r="R1" s="7" t="s">
@@ -2360,15 +2364,15 @@
         <v>0</v>
       </c>
       <c r="Z5" s="10">
-        <f t="shared" ref="Z4:Z16" si="3">SUM(J5)</f>
+        <f t="shared" ref="Z5:Z16" si="3">SUM(J5)</f>
         <v>12.5</v>
       </c>
       <c r="AA5" s="11">
-        <f t="shared" ref="AA4:AA16" si="4">SUM(R5)</f>
+        <f t="shared" ref="AA5:AA16" si="4">SUM(R5)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="12">
-        <f t="shared" ref="AB4:AB16" si="5">SUM(Y5)</f>
+        <f t="shared" ref="AB5:AB16" si="5">SUM(Y5)</f>
         <v>0</v>
       </c>
       <c r="AC5" s="14">
@@ -2383,7 +2387,9 @@
       <c r="B6" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="16"/>
+      <c r="C6" s="16" t="s">
+        <v>113</v>
+      </c>
       <c r="D6" s="22">
         <v>0.1</v>
       </c>

--- a/reiting.xlsx
+++ b/reiting.xlsx
@@ -2283,21 +2283,25 @@
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
+      <c r="P4" s="9">
+        <v>5</v>
+      </c>
       <c r="Q4" s="9"/>
       <c r="R4" s="11">
         <f>SUM(K4+L4+M4+N4+O4+P4+Q4)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
+      <c r="W4" s="9">
+        <v>4</v>
+      </c>
       <c r="X4" s="9"/>
       <c r="Y4" s="12">
         <f>SUM(S4+T4+U4+V4+W4+X4)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z4" s="10">
         <f>SUM(J4)</f>
@@ -2305,15 +2309,15 @@
       </c>
       <c r="AA4" s="11">
         <f>SUM(R4)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB4" s="12">
         <f>SUM(Y4)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC4" s="14">
         <f>SUM(J4+R4+Y4)</f>
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
